--- a/languages/pt/output/import/葡萄牙语专八高阶.xlsx
+++ b/languages/pt/output/import/葡萄牙语专八高阶.xlsx
@@ -41815,7 +41815,7 @@
       </c>
       <c r="B1297" s="1" t="inlineStr">
         <is>
-          <t>[[ˌalaˈbɐma]] 阿拉巴马州&lt;名&gt;</t>
+          <t>[ˌalaˈbɐma] 阿拉巴马州&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1297" s="1" t="inlineStr">

--- a/languages/pt/output/import/葡萄牙语专八高阶.xlsx
+++ b/languages/pt/output/import/葡萄牙语专八高阶.xlsx
@@ -1323,7 +1323,7 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>[ˈksi] CSI&lt;名&gt;</t>
+          <t>[ˈksi] 犯罪现场调查；刑侦检验&lt;名&gt;</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>CSI</t>
+          <t>犯罪现场调查</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
@@ -31471,7 +31471,7 @@
       </c>
       <c r="B973" s="1" t="inlineStr">
         <is>
-          <t>[ˌto.du.po.deˈɾo.zu] all-powerful&lt;名&gt;</t>
+          <t>[ˌto.du.po.deˈɾo.zu] 全能的；万能的；全能上帝&lt;名/形&gt;</t>
         </is>
       </c>
       <c r="C973" s="1" t="inlineStr">
@@ -31481,7 +31481,7 @@
       </c>
       <c r="D973" s="1" t="inlineStr">
         <is>
-          <t>all-powerful</t>
+          <t>全能的</t>
         </is>
       </c>
       <c r="E973" s="1" t="inlineStr">
@@ -80079,7 +80079,7 @@
       </c>
       <c r="B2495" s="1" t="inlineStr">
         <is>
-          <t>[ˈɛ.li ˈɛ.si ˈde] LSD&lt;名&gt;</t>
+          <t>[ˈɛ.li ˈɛ.si ˈde] 麦角酸二乙酰胺；致幻剂LSD&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2495" s="1" t="inlineStr">
@@ -80089,7 +80089,7 @@
       </c>
       <c r="D2495" s="1" t="inlineStr">
         <is>
-          <t>LSD</t>
+          <t>致幻剂LSD</t>
         </is>
       </c>
       <c r="E2495" s="1" t="inlineStr">

--- a/languages/pt/output/import/葡萄牙语专八高阶.xlsx
+++ b/languages/pt/output/import/葡萄牙语专八高阶.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -696,7 +696,7 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>pa.ˈga.ɾãʊ̃</t>
+          <t>/pa.ˈga.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
@@ -723,17 +723,17 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>[ˈgʊ] 去&lt;名&gt;</t>
+          <t>[ˈgʊ] 围棋&lt;名&gt;</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>ˈgʊ</t>
+          <t>/ˈgʊ/</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>去</t>
+          <t>围棋</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>[ˈpɔs.t͡ʃi] 帖子&lt;名&gt;</t>
+          <t>[ˈpɔs.t͡ʃi] 柱子；杆；球门柱&lt;名&gt;</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>帖子</t>
+          <t>柱子；杆；球门柱</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
@@ -1043,13 +1043,17 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>p。&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr"/>
+          <t>页&lt;名&gt;</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>/ˈpe/</t>
+        </is>
+      </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>p。</t>
+          <t>页</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
@@ -1106,7 +1110,11 @@
           <t>嘿&lt;动&gt;</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr"/>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>/ˈe/</t>
+        </is>
+      </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
           <t>嘿</t>
@@ -1392,7 +1400,7 @@
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>toɣ.ˈna.ɾãʊ̃</t>
+          <t>/toɣ.ˈna.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
@@ -1648,7 +1656,7 @@
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>ko.lo.ˈka.ɾãʊ̃</t>
+          <t>/ko.lo.ˈka.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
@@ -1867,7 +1875,7 @@
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>[ˈõ.mi] 家&lt;名&gt;</t>
+          <t>[/ˈõ.mi/] 男人；人类&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
@@ -1877,7 +1885,7 @@
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>家</t>
+          <t>男人；人类</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
@@ -2027,7 +2035,7 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>[ˈtɾi.plu] 三重&lt;名&gt;</t>
+          <t>[/ˈtɾi.plu/] 三倍的；三重的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
@@ -2037,7 +2045,7 @@
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>三重</t>
+          <t>三倍的；三重的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E51" s="1" t="inlineStr">
@@ -2096,7 +2104,7 @@
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>ko.ˈxe.ɾãʊ̃</t>
+          <t>/ko.ˈxe.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
@@ -2416,7 +2424,7 @@
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>ˈsɔ.zĩ.ɲʊ</t>
+          <t>/ˈsɔ.zĩ.ɲʊ/</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
@@ -2731,7 +2739,7 @@
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>[plɐ̃ˈta(ʁ)] 植物&lt;动&gt;</t>
+          <t>[plɐ̃ˈta(ʁ)] 种植；栽培&lt;动&gt;</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
@@ -2741,7 +2749,7 @@
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>植物</t>
+          <t>种植；栽培</t>
         </is>
       </c>
       <c r="E73" s="1" t="inlineStr">
@@ -2827,7 +2835,7 @@
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>[ĩ.vẽˈta.ɾju] 库存&lt;名&gt;</t>
+          <t>[/ĩ.vẽˈta.ɾju/] 清单；财产目录&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
@@ -2837,7 +2845,7 @@
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>库存</t>
+          <t>清单；财产目录</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
@@ -2891,7 +2899,7 @@
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>[sa.seʁˈdɔ.t͡ʃi] 牧师&lt;名&gt;</t>
+          <t>[/sa.seʁˈdɔ.t͡ʃi/] 神父；司铎&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
@@ -2901,7 +2909,7 @@
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>牧师</t>
+          <t>神父；司铎</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
@@ -4299,7 +4307,7 @@
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>[suˈʒa(ʁ)] 肮脏的&lt;动&gt;</t>
+          <t>[suˈʒa(ʁ)] 弄脏；玷污&lt;动&gt;</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
@@ -4309,7 +4317,7 @@
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
-          <t>肮脏的</t>
+          <t>弄脏；玷污</t>
         </is>
       </c>
       <c r="E122" s="1" t="inlineStr">
@@ -4459,7 +4467,7 @@
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>[a.maˈʁa(ʁ)] 领带&lt;动&gt;</t>
+          <t>[a.maˈʁa(ʁ)] 绑；系；捆&lt;动&gt;</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
@@ -4469,7 +4477,7 @@
       </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
-          <t>领带</t>
+          <t>绑；系；捆</t>
         </is>
       </c>
       <c r="E127" s="1" t="inlineStr">
@@ -4555,7 +4563,7 @@
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>[sus.pejˈta(ʁ)] 嫌疑人&lt;动&gt;</t>
+          <t>[sus.pejˈta(ʁ)] 怀疑；猜疑&lt;动&gt;</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
@@ -4565,7 +4573,7 @@
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
-          <t>嫌疑人</t>
+          <t>怀疑；猜疑</t>
         </is>
       </c>
       <c r="E130" s="1" t="inlineStr">
@@ -4683,7 +4691,7 @@
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>[mo.t͡ʃi.vaˈsɐ̃w̃] 动机&lt;名&gt;</t>
+          <t>[/mo.t͡ʃi.vaˈsɐ̃w̃/] 动力；激励&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
@@ -4693,7 +4701,7 @@
       </c>
       <c r="D134" s="1" t="inlineStr">
         <is>
-          <t>动机</t>
+          <t>动力；激励&lt;名&gt;</t>
         </is>
       </c>
       <c r="E134" s="1" t="inlineStr">
@@ -4782,7 +4790,11 @@
           <t>电子邮件&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C137" s="1" t="inlineStr"/>
+      <c r="C137" s="1" t="inlineStr">
+        <is>
+          <t>/iˈmɛjw/</t>
+        </is>
+      </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
           <t>电子邮件</t>
@@ -4903,7 +4915,7 @@
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>[aʁˈbus.tu] 布什&lt;名&gt;</t>
+          <t>[aʁˈbus.tu] 灌木；灌木丛&lt;名&gt;</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
@@ -4913,7 +4925,7 @@
       </c>
       <c r="D141" s="1" t="inlineStr">
         <is>
-          <t>布什</t>
+          <t>灌木；灌木丛</t>
         </is>
       </c>
       <c r="E141" s="1" t="inlineStr">
@@ -4999,7 +5011,7 @@
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>[o(w)ˈtɾɔ.ɾɐ] 一次&lt;副&gt;</t>
+          <t>[o(w)ˈtɾɔ.ɾɐ] 从前；昔日&lt;副&gt;</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
@@ -5009,7 +5021,7 @@
       </c>
       <c r="D144" s="1" t="inlineStr">
         <is>
-          <t>一次</t>
+          <t>从前；昔日</t>
         </is>
       </c>
       <c r="E144" s="1" t="inlineStr">
@@ -5127,7 +5139,7 @@
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>[is.tɾaˈi(ʁ)] 提取物&lt;动&gt;</t>
+          <t>[is.tɾaˈi(ʁ)] 提取；拔出；抽出&lt;动&gt;</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
@@ -5137,7 +5149,7 @@
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
-          <t>提取物</t>
+          <t>提取；拔出；抽出</t>
         </is>
       </c>
       <c r="E148" s="1" t="inlineStr">
@@ -5228,7 +5240,7 @@
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>is.to.ˈɾi.ə</t>
+          <t>/is.to.ˈɾi.ə/</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr">
@@ -5420,7 +5432,7 @@
       </c>
       <c r="C157" s="1" t="inlineStr">
         <is>
-          <t>tɾa.ba.ˈʎa.ɾãʊ̃</t>
+          <t>/tɾa.ba.ˈʎa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D157" s="1" t="inlineStr">
@@ -5543,7 +5555,7 @@
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>[is.taˈtaw] 状态&lt;名&gt;</t>
+          <t>[is.taˈtaw] 国家的；国有的；国营的&lt;名&gt;</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
@@ -5553,7 +5565,7 @@
       </c>
       <c r="D161" s="1" t="inlineStr">
         <is>
-          <t>状态</t>
+          <t>国家的；国有的；国营的</t>
         </is>
       </c>
       <c r="E161" s="1" t="inlineStr">
@@ -5607,7 +5619,7 @@
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>[ˈsu.bi] 子&lt;名&gt;</t>
+          <t>[ˈsu.bi] 子；次；下级；潜水艇&lt;名&gt;</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
@@ -5617,7 +5629,7 @@
       </c>
       <c r="D163" s="1" t="inlineStr">
         <is>
-          <t>子</t>
+          <t>子；次；下级；潜水艇</t>
         </is>
       </c>
       <c r="E163" s="1" t="inlineStr">
@@ -5772,7 +5784,7 @@
       </c>
       <c r="C168" s="1" t="inlineStr">
         <is>
-          <t>ˈpɔ.lʊ</t>
+          <t>/ˈpɔ.lʊ/</t>
         </is>
       </c>
       <c r="D168" s="1" t="inlineStr">
@@ -6151,7 +6163,7 @@
       </c>
       <c r="B180" s="1" t="inlineStr">
         <is>
-          <t>[kaˈlu.dɐ] 卡卢达&lt;叹&gt;</t>
+          <t>[kaˈlu.dɐ] 哀歌；悲叹&lt;叹&gt;</t>
         </is>
       </c>
       <c r="C180" s="1" t="inlineStr">
@@ -6161,7 +6173,7 @@
       </c>
       <c r="D180" s="1" t="inlineStr">
         <is>
-          <t>卡卢达</t>
+          <t>哀歌；悲叹</t>
         </is>
       </c>
       <c r="E180" s="1" t="inlineStr">
@@ -6471,7 +6483,7 @@
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>[pɾo.viˈzɐ̃w̃] 规定&lt;名&gt;</t>
+          <t>[/pɾo.viˈzɐ̃w̃/] 供应；储备；条款&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
@@ -6481,7 +6493,7 @@
       </c>
       <c r="D190" s="1" t="inlineStr">
         <is>
-          <t>规定</t>
+          <t>供应；储备；条款&lt;名&gt;</t>
         </is>
       </c>
       <c r="E190" s="1" t="inlineStr">
@@ -6602,7 +6614,11 @@
           <t>她&lt;代&gt;</t>
         </is>
       </c>
-      <c r="C194" s="1" t="inlineStr"/>
+      <c r="C194" s="1" t="inlineStr">
+        <is>
+          <t>/ˈɛ.lɐ/</t>
+        </is>
+      </c>
       <c r="D194" s="1" t="inlineStr">
         <is>
           <t>她</t>
@@ -7043,17 +7059,17 @@
       </c>
       <c r="B208" s="1" t="inlineStr">
         <is>
-          <t>[se.ˈɾi.ʊ] 认真地&lt;形&gt;</t>
+          <t>[se.ˈɾi.ʊ] 严肃的；认真的；严重的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C208" s="1" t="inlineStr">
         <is>
-          <t>se.ˈɾi.ʊ</t>
+          <t>/se.ˈɾi.ʊ/</t>
         </is>
       </c>
       <c r="D208" s="1" t="inlineStr">
         <is>
-          <t>认真地</t>
+          <t>严肃的；认真的；严重的</t>
         </is>
       </c>
       <c r="E208" s="1" t="inlineStr">
@@ -7080,7 +7096,7 @@
       </c>
       <c r="C209" s="1" t="inlineStr">
         <is>
-          <t>ẽ.tẽ.ˈde.ɾãʊ̃</t>
+          <t>/ẽ.tẽ.ˈde.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D209" s="1" t="inlineStr">
@@ -7331,7 +7347,7 @@
       </c>
       <c r="B217" s="1" t="inlineStr">
         <is>
-          <t>[ˈʃi] 气&lt;名&gt;</t>
+          <t>[ˈʃi] 咦；呸（表示厌恶）&lt;名&gt;</t>
         </is>
       </c>
       <c r="C217" s="1" t="inlineStr">
@@ -7341,7 +7357,7 @@
       </c>
       <c r="D217" s="1" t="inlineStr">
         <is>
-          <t>气</t>
+          <t>咦；呸（表示厌恶）</t>
         </is>
       </c>
       <c r="E217" s="1" t="inlineStr">
@@ -7363,7 +7379,7 @@
       </c>
       <c r="B218" s="1" t="inlineStr">
         <is>
-          <t>[duˈzẽ.tus] 两百&lt;名&gt;</t>
+          <t>[/duˈzẽ.tus/] 两百&lt;数&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C218" s="1" t="inlineStr">
@@ -7373,7 +7389,7 @@
       </c>
       <c r="D218" s="1" t="inlineStr">
         <is>
-          <t>两百</t>
+          <t>两百&lt;数&gt;</t>
         </is>
       </c>
       <c r="E218" s="1" t="inlineStr">
@@ -8232,7 +8248,7 @@
       </c>
       <c r="C245" s="1" t="inlineStr">
         <is>
-          <t>fa.ˈtox</t>
+          <t>/fa.ˈtox/</t>
         </is>
       </c>
       <c r="D245" s="1" t="inlineStr">
@@ -8291,7 +8307,7 @@
       </c>
       <c r="B247" s="1" t="inlineStr">
         <is>
-          <t>[a.pɾo.si.maˈsɐ̃w̃] 方法&lt;名&gt;</t>
+          <t>[/a.pɾo.si.maˈsɐ̃w̃/] 接近&lt;名&gt;；靠近&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C247" s="1" t="inlineStr">
@@ -8301,7 +8317,7 @@
       </c>
       <c r="D247" s="1" t="inlineStr">
         <is>
-          <t>方法</t>
+          <t>接近&lt;名&gt;；靠近&lt;名&gt;</t>
         </is>
       </c>
       <c r="E247" s="1" t="inlineStr">
@@ -8995,7 +9011,7 @@
       </c>
       <c r="B269" s="1" t="inlineStr">
         <is>
-          <t>[mu.ziˈka(ʁ)] 音乐&lt;动&gt;</t>
+          <t>[mu.ziˈka(ʁ)] 谱曲；配乐&lt;动&gt;</t>
         </is>
       </c>
       <c r="C269" s="1" t="inlineStr">
@@ -9005,7 +9021,7 @@
       </c>
       <c r="D269" s="1" t="inlineStr">
         <is>
-          <t>音乐</t>
+          <t>谱曲；配乐</t>
         </is>
       </c>
       <c r="E269" s="1" t="inlineStr">
@@ -9059,7 +9075,7 @@
       </c>
       <c r="B271" s="1" t="inlineStr">
         <is>
-          <t>[ˈlo(w).ɾu] 金发女郎&lt;名&gt;</t>
+          <t>[/ˈlo(w).ɾu/] 月桂树；金发男子&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C271" s="1" t="inlineStr">
@@ -9069,7 +9085,7 @@
       </c>
       <c r="D271" s="1" t="inlineStr">
         <is>
-          <t>金发女郎</t>
+          <t>月桂树；金发男子</t>
         </is>
       </c>
       <c r="E271" s="1" t="inlineStr">
@@ -9091,7 +9107,7 @@
       </c>
       <c r="B272" s="1" t="inlineStr">
         <is>
-          <t>[koʁˈde(j).ɾu] 羊肉&lt;名&gt;</t>
+          <t>[/koʁˈde(j).ɾu/] 羔羊&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C272" s="1" t="inlineStr">
@@ -9101,7 +9117,7 @@
       </c>
       <c r="D272" s="1" t="inlineStr">
         <is>
-          <t>羊肉</t>
+          <t>羔羊</t>
         </is>
       </c>
       <c r="E272" s="1" t="inlineStr">
@@ -9192,7 +9208,7 @@
       </c>
       <c r="C275" s="1" t="inlineStr">
         <is>
-          <t>a.tɾa.ˈi.dʊ</t>
+          <t>/a.tɾa.ˈi.dʊ/</t>
         </is>
       </c>
       <c r="D275" s="1" t="inlineStr">
@@ -9411,7 +9427,7 @@
       </c>
       <c r="B282" s="1" t="inlineStr">
         <is>
-          <t>[doˈza(ʁ)] 剂量&lt;动&gt;</t>
+          <t>[doˈza(ʁ)] 按剂量配给；调剂；节制&lt;动&gt;</t>
         </is>
       </c>
       <c r="C282" s="1" t="inlineStr">
@@ -9421,7 +9437,7 @@
       </c>
       <c r="D282" s="1" t="inlineStr">
         <is>
-          <t>剂量</t>
+          <t>按剂量配给；调剂；节制</t>
         </is>
       </c>
       <c r="E282" s="1" t="inlineStr">
@@ -9448,7 +9464,7 @@
       </c>
       <c r="C283" s="1" t="inlineStr">
         <is>
-          <t>kõs.tɾu.ˈi.ɾãʊ̃</t>
+          <t>/kõs.tɾu.ˈi.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D283" s="1" t="inlineStr">
@@ -9795,7 +9811,7 @@
       </c>
       <c r="B294" s="1" t="inlineStr">
         <is>
-          <t>[ẽˈvi.u] 运输&lt;名&gt;</t>
+          <t>[/ẽˈvi.u/] 发送；寄送&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C294" s="1" t="inlineStr">
@@ -9805,7 +9821,7 @@
       </c>
       <c r="D294" s="1" t="inlineStr">
         <is>
-          <t>运输</t>
+          <t>发送；寄送&lt;名&gt;</t>
         </is>
       </c>
       <c r="E294" s="1" t="inlineStr">
@@ -9859,7 +9875,7 @@
       </c>
       <c r="B296" s="1" t="inlineStr">
         <is>
-          <t>[kapˈta(ʁ)] 捕获&lt;动&gt;</t>
+          <t>[/kapˈta(ʁ)/] 捕捉；领会；接收&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C296" s="1" t="inlineStr">
@@ -9869,7 +9885,7 @@
       </c>
       <c r="D296" s="1" t="inlineStr">
         <is>
-          <t>捕获</t>
+          <t>捕捉；领会；接收&lt;动&gt;</t>
         </is>
       </c>
       <c r="E296" s="1" t="inlineStr">
@@ -10278,7 +10294,11 @@
           <t>嗯&lt;叹&gt;</t>
         </is>
       </c>
-      <c r="C309" s="1" t="inlineStr"/>
+      <c r="C309" s="1" t="inlineStr">
+        <is>
+          <t>/mmm/</t>
+        </is>
+      </c>
       <c r="D309" s="1" t="inlineStr">
         <is>
           <t>嗯</t>
@@ -10399,7 +10419,7 @@
       </c>
       <c r="B313" s="1" t="inlineStr">
         <is>
-          <t>[ˈtɾa.su] 破折号&lt;名&gt;</t>
+          <t>[/ˈtɾa.su/] 笔画；线条；特征&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C313" s="1" t="inlineStr">
@@ -10409,7 +10429,7 @@
       </c>
       <c r="D313" s="1" t="inlineStr">
         <is>
-          <t>破折号</t>
+          <t>笔画；线条；特征&lt;名&gt;</t>
         </is>
       </c>
       <c r="E313" s="1" t="inlineStr">
@@ -10436,7 +10456,7 @@
       </c>
       <c r="C314" s="1" t="inlineStr">
         <is>
-          <t>kwa.li.fi.ˈka.dʊ</t>
+          <t>/kwa.li.fi.ˈka.dʊ/</t>
         </is>
       </c>
       <c r="D314" s="1" t="inlineStr">
@@ -10591,7 +10611,7 @@
       </c>
       <c r="B319" s="1" t="inlineStr">
         <is>
-          <t>[sɐ̃ˈɡwĩ.nju] 乐观的&lt;形&gt;</t>
+          <t>[sɐ̃ˈɡwĩ.nju] 血液的；乐观的；面色红润的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C319" s="1" t="inlineStr">
@@ -10601,7 +10621,7 @@
       </c>
       <c r="D319" s="1" t="inlineStr">
         <is>
-          <t>乐观的</t>
+          <t>血液的；乐观的；面色红润的</t>
         </is>
       </c>
       <c r="E319" s="1" t="inlineStr">
@@ -10916,7 +10936,7 @@
       </c>
       <c r="C329" s="1" t="inlineStr">
         <is>
-          <t>ĩs.pe.ˈsãʊ̃</t>
+          <t>/ĩs.pe.ˈsãʊ̃/</t>
         </is>
       </c>
       <c r="D329" s="1" t="inlineStr">
@@ -11007,7 +11027,7 @@
       </c>
       <c r="B332" s="1" t="inlineStr">
         <is>
-          <t>[kõ.pɾo.meˈte(ʁ)] 提交&lt;动&gt;</t>
+          <t>[kõ.pɾo.meˈte(ʁ)] 承诺；使承担义务；危害；连累&lt;动&gt;</t>
         </is>
       </c>
       <c r="C332" s="1" t="inlineStr">
@@ -11017,7 +11037,7 @@
       </c>
       <c r="D332" s="1" t="inlineStr">
         <is>
-          <t>提交</t>
+          <t>承诺；使承担义务；危害；连累</t>
         </is>
       </c>
       <c r="E332" s="1" t="inlineStr">
@@ -11071,7 +11091,7 @@
       </c>
       <c r="B334" s="1" t="inlineStr">
         <is>
-          <t>[maʁˈʃa(ʁ)] 进行曲&lt;动&gt;</t>
+          <t>[maʁˈʃa(ʁ)] 行军；前进&lt;动&gt;</t>
         </is>
       </c>
       <c r="C334" s="1" t="inlineStr">
@@ -11081,7 +11101,7 @@
       </c>
       <c r="D334" s="1" t="inlineStr">
         <is>
-          <t>进行曲</t>
+          <t>行军；前进</t>
         </is>
       </c>
       <c r="E334" s="1" t="inlineStr">
@@ -11177,7 +11197,7 @@
       </c>
       <c r="D337" s="1" t="inlineStr">
         <is>
-          <t>笔</t>
+          <t>英语词，非葡萄牙语词条</t>
         </is>
       </c>
       <c r="E337" s="1" t="inlineStr">
@@ -11295,7 +11315,7 @@
       </c>
       <c r="B341" s="1" t="inlineStr">
         <is>
-          <t>[deˈsi.dɐ] 血统&lt;名&gt;</t>
+          <t>[deˈsi.dɐ] 下降；下坡；降落&lt;名&gt;</t>
         </is>
       </c>
       <c r="C341" s="1" t="inlineStr">
@@ -11305,7 +11325,7 @@
       </c>
       <c r="D341" s="1" t="inlineStr">
         <is>
-          <t>血统</t>
+          <t>下降；下坡；降落</t>
         </is>
       </c>
       <c r="E341" s="1" t="inlineStr">
@@ -11327,7 +11347,7 @@
       </c>
       <c r="B342" s="1" t="inlineStr">
         <is>
-          <t>[e.miˈt͡ʃi(ʁ)] 问题&lt;动&gt;</t>
+          <t>[e.miˈt͡ʃi(ʁ)] 发出；发射；发行；签发；播送&lt;动&gt;</t>
         </is>
       </c>
       <c r="C342" s="1" t="inlineStr">
@@ -11337,7 +11357,7 @@
       </c>
       <c r="D342" s="1" t="inlineStr">
         <is>
-          <t>问题</t>
+          <t>发出；发射；发行；签发；播送</t>
         </is>
       </c>
       <c r="E342" s="1" t="inlineStr">
@@ -11359,7 +11379,7 @@
       </c>
       <c r="B343" s="1" t="inlineStr">
         <is>
-          <t>[ˈnaj.t͡ʃi] 晚上&lt;名&gt;</t>
+          <t>[ˈnaj.t͡ʃi] 夜总会；夜生活&lt;名&gt;</t>
         </is>
       </c>
       <c r="C343" s="1" t="inlineStr">
@@ -11369,7 +11389,7 @@
       </c>
       <c r="D343" s="1" t="inlineStr">
         <is>
-          <t>晚上</t>
+          <t>夜总会；夜生活</t>
         </is>
       </c>
       <c r="E343" s="1" t="inlineStr">
@@ -11906,7 +11926,11 @@
           <t>v.&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C360" s="1" t="inlineStr"/>
+      <c r="C360" s="1" t="inlineStr">
+        <is>
+          <t>/ˈve/</t>
+        </is>
+      </c>
       <c r="D360" s="1" t="inlineStr">
         <is>
           <t>v.</t>
@@ -11968,7 +11992,7 @@
       </c>
       <c r="C362" s="1" t="inlineStr">
         <is>
-          <t>ã.ˈda.ɾãʊ̃</t>
+          <t>/ã.ˈda.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D362" s="1" t="inlineStr">
@@ -12155,7 +12179,7 @@
       </c>
       <c r="B368" s="1" t="inlineStr">
         <is>
-          <t>[baˈlɐ̃.sɐ] 规模&lt;名&gt;</t>
+          <t>[baˈlɐ̃.sɐ] 秤；天平；（贸易）差额&lt;名&gt;</t>
         </is>
       </c>
       <c r="C368" s="1" t="inlineStr">
@@ -12165,7 +12189,7 @@
       </c>
       <c r="D368" s="1" t="inlineStr">
         <is>
-          <t>规模</t>
+          <t>秤；天平；（贸易）差额</t>
         </is>
       </c>
       <c r="E368" s="1" t="inlineStr">
@@ -12224,7 +12248,7 @@
       </c>
       <c r="C370" s="1" t="inlineStr">
         <is>
-          <t>ˈfɔ.fə</t>
+          <t>/ˈfɔ.fə/</t>
         </is>
       </c>
       <c r="D370" s="1" t="inlineStr">
@@ -12256,7 +12280,7 @@
       </c>
       <c r="C371" s="1" t="inlineStr">
         <is>
-          <t>vi.ˈve.ɾãʊ̃</t>
+          <t>/vi.ˈve.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D371" s="1" t="inlineStr">
@@ -12416,7 +12440,7 @@
       </c>
       <c r="C376" s="1" t="inlineStr">
         <is>
-          <t>a.ʒu.ˈda.ɾãʊ̃</t>
+          <t>/a.ʒu.ˈda.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D376" s="1" t="inlineStr">
@@ -12827,7 +12851,7 @@
       </c>
       <c r="B389" s="1" t="inlineStr">
         <is>
-          <t>[u.ni.veʁ.siˈta.ɾju] 大学&lt;名&gt;</t>
+          <t>[u.ni.veʁ.siˈta.ɾju] 大学的；大学生&lt;名&gt;</t>
         </is>
       </c>
       <c r="C389" s="1" t="inlineStr">
@@ -12837,7 +12861,7 @@
       </c>
       <c r="D389" s="1" t="inlineStr">
         <is>
-          <t>大学</t>
+          <t>大学的；大学生</t>
         </is>
       </c>
       <c r="E389" s="1" t="inlineStr">
@@ -13019,7 +13043,7 @@
       </c>
       <c r="B395" s="1" t="inlineStr">
         <is>
-          <t>[ˈɔ.lɐ] 你好&lt;名&gt;</t>
+          <t>[/ˈɔ.lɐ/] olá（你好）&lt;叹&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C395" s="1" t="inlineStr">
@@ -13029,7 +13053,7 @@
       </c>
       <c r="D395" s="1" t="inlineStr">
         <is>
-          <t>你好</t>
+          <t>olá（你好）&lt;叹&gt;</t>
         </is>
       </c>
       <c r="E395" s="1" t="inlineStr">
@@ -13051,17 +13075,17 @@
       </c>
       <c r="B396" s="1" t="inlineStr">
         <is>
-          <t>[dʒis.pa.ˈɾa.ɾãʊ̃] 被解雇&lt;动&gt;</t>
+          <t>[dʒis.pa.ˈɾa.ɾãʊ̃] 射击；发射；猛涨&lt;动&gt;</t>
         </is>
       </c>
       <c r="C396" s="1" t="inlineStr">
         <is>
-          <t>dʒis.pa.ˈɾa.ɾãʊ̃</t>
+          <t>/dʒis.pa.ˈɾa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D396" s="1" t="inlineStr">
         <is>
-          <t>被解雇</t>
+          <t>射击；发射；猛涨</t>
         </is>
       </c>
       <c r="E396" s="1" t="inlineStr">
@@ -13120,7 +13144,7 @@
       </c>
       <c r="C398" s="1" t="inlineStr">
         <is>
-          <t>xe.a.ˈtox</t>
+          <t>/xe.a.ˈtox/</t>
         </is>
       </c>
       <c r="D398" s="1" t="inlineStr">
@@ -13280,7 +13304,7 @@
       </c>
       <c r="C403" s="1" t="inlineStr">
         <is>
-          <t>ˈpa.ɾa.ke.dəs</t>
+          <t>/ˈpa.ɾa.ke.dəs/</t>
         </is>
       </c>
       <c r="D403" s="1" t="inlineStr">
@@ -14011,7 +14035,7 @@
       </c>
       <c r="B426" s="1" t="inlineStr">
         <is>
-          <t>[ˈbũ] 繁荣&lt;名&gt;</t>
+          <t>[/ˈbũ/] 砰&lt;拟声&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C426" s="1" t="inlineStr">
@@ -14021,7 +14045,7 @@
       </c>
       <c r="D426" s="1" t="inlineStr">
         <is>
-          <t>繁荣</t>
+          <t>砰&lt;拟声&gt;</t>
         </is>
       </c>
       <c r="E426" s="1" t="inlineStr">
@@ -14235,7 +14259,7 @@
       </c>
       <c r="B433" s="1" t="inlineStr">
         <is>
-          <t>[siˈta(ʁ)] 报价&lt;动&gt;</t>
+          <t>[siˈta(ʁ)] 引用；引述；提及&lt;动&gt;</t>
         </is>
       </c>
       <c r="C433" s="1" t="inlineStr">
@@ -14245,7 +14269,7 @@
       </c>
       <c r="D433" s="1" t="inlineStr">
         <is>
-          <t>报价</t>
+          <t>引用；引述；提及</t>
         </is>
       </c>
       <c r="E433" s="1" t="inlineStr">
@@ -14560,7 +14584,7 @@
       </c>
       <c r="C443" s="1" t="inlineStr">
         <is>
-          <t>a.tʃi.ˈva.dʊ</t>
+          <t>/a.tʃi.ˈva.dʊ/</t>
         </is>
       </c>
       <c r="D443" s="1" t="inlineStr">
@@ -14651,7 +14675,7 @@
       </c>
       <c r="B446" s="1" t="inlineStr">
         <is>
-          <t>[vẽˈsi.du] 赢了&lt;形&gt;</t>
+          <t>[vẽˈsi.du] 过期的；到期的；被击败的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C446" s="1" t="inlineStr">
@@ -14661,7 +14685,7 @@
       </c>
       <c r="D446" s="1" t="inlineStr">
         <is>
-          <t>赢了</t>
+          <t>过期的；到期的；被击败的</t>
         </is>
       </c>
       <c r="E446" s="1" t="inlineStr">
@@ -14747,7 +14771,7 @@
       </c>
       <c r="B449" s="1" t="inlineStr">
         <is>
-          <t>[pɾo.ɡɾaˈma(ʁ)] 节目&lt;动&gt;</t>
+          <t>[pɾo.ɡɾaˈma(ʁ)] 计划；安排；编程&lt;动&gt;</t>
         </is>
       </c>
       <c r="C449" s="1" t="inlineStr">
@@ -14757,7 +14781,7 @@
       </c>
       <c r="D449" s="1" t="inlineStr">
         <is>
-          <t>节目</t>
+          <t>计划；安排；编程</t>
         </is>
       </c>
       <c r="E449" s="1" t="inlineStr">
@@ -14912,7 +14936,7 @@
       </c>
       <c r="C454" s="1" t="inlineStr">
         <is>
-          <t>des.tɾu.ˈi.ɾãʊ̃</t>
+          <t>/des.tɾu.ˈi.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D454" s="1" t="inlineStr">
@@ -14939,7 +14963,7 @@
       </c>
       <c r="B455" s="1" t="inlineStr">
         <is>
-          <t>[is.koˈt͡ʃi.ʎɐ] 孵化&lt;名&gt;</t>
+          <t>[is.koˈt͡ʃi.ʎɐ] 舱口；舱盖&lt;名&gt;</t>
         </is>
       </c>
       <c r="C455" s="1" t="inlineStr">
@@ -14949,7 +14973,7 @@
       </c>
       <c r="D455" s="1" t="inlineStr">
         <is>
-          <t>孵化</t>
+          <t>舱口；舱盖</t>
         </is>
       </c>
       <c r="E455" s="1" t="inlineStr">
@@ -14976,7 +15000,7 @@
       </c>
       <c r="C456" s="1" t="inlineStr">
         <is>
-          <t>ĩ.vẽ.ˈta.dʊ</t>
+          <t>/ĩ.vẽ.ˈta.dʊ/</t>
         </is>
       </c>
       <c r="D456" s="1" t="inlineStr">
@@ -15035,7 +15059,7 @@
       </c>
       <c r="B458" s="1" t="inlineStr">
         <is>
-          <t>[toˈtɔ] 极客&lt;名&gt;</t>
+          <t>[toˈtɔ] 足球彩票；狗狗（犬的昵称）&lt;名&gt;</t>
         </is>
       </c>
       <c r="C458" s="1" t="inlineStr">
@@ -15045,7 +15069,7 @@
       </c>
       <c r="D458" s="1" t="inlineStr">
         <is>
-          <t>极客</t>
+          <t>足球彩票；狗狗（犬的昵称）</t>
         </is>
       </c>
       <c r="E458" s="1" t="inlineStr">
@@ -15099,7 +15123,7 @@
       </c>
       <c r="B460" s="1" t="inlineStr">
         <is>
-          <t>[ˈmu.lu] 骡子&lt;名&gt;</t>
+          <t>[/ˈmu.lu/] 骡子（标准词形为 mula）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C460" s="1" t="inlineStr">
@@ -15109,7 +15133,7 @@
       </c>
       <c r="D460" s="1" t="inlineStr">
         <is>
-          <t>骡子</t>
+          <t>骡子（标准词形为 mula）</t>
         </is>
       </c>
       <c r="E460" s="1" t="inlineStr">
@@ -15134,7 +15158,11 @@
           <t>教授&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C461" s="1" t="inlineStr"/>
+      <c r="C461" s="1" t="inlineStr">
+        <is>
+          <t>/pɾo.feˈsoʁ/</t>
+        </is>
+      </c>
       <c r="D461" s="1" t="inlineStr">
         <is>
           <t>教授</t>
@@ -15260,7 +15288,7 @@
       </c>
       <c r="C465" s="1" t="inlineStr">
         <is>
-          <t>ob.ʒe.ˈsãʊ̃</t>
+          <t>/ob.ʒe.ˈsãʊ̃/</t>
         </is>
       </c>
       <c r="D465" s="1" t="inlineStr">
@@ -15287,7 +15315,7 @@
       </c>
       <c r="B466" s="1" t="inlineStr">
         <is>
-          <t>[ẽ.ko.mẽˈda(ʁ)] 订单&lt;动&gt;</t>
+          <t>[ẽ.ko.mẽˈda(ʁ)] 订购；定制；委托&lt;动&gt;</t>
         </is>
       </c>
       <c r="C466" s="1" t="inlineStr">
@@ -15297,7 +15325,7 @@
       </c>
       <c r="D466" s="1" t="inlineStr">
         <is>
-          <t>订单</t>
+          <t>订购；定制；委托</t>
         </is>
       </c>
       <c r="E466" s="1" t="inlineStr">
@@ -15612,7 +15640,7 @@
       </c>
       <c r="C476" s="1" t="inlineStr">
         <is>
-          <t>op.tʃi.ˈmis.tə</t>
+          <t>/op.tʃi.ˈmis.tə/</t>
         </is>
       </c>
       <c r="D476" s="1" t="inlineStr">
@@ -15639,7 +15667,7 @@
       </c>
       <c r="B477" s="1" t="inlineStr">
         <is>
-          <t>[ˈpɾɐ̃.ʃɐ] 董事会&lt;名&gt;</t>
+          <t>[ˈpɾɐ̃.ʃɐ] 木板；板；冲浪板；跳板&lt;名&gt;</t>
         </is>
       </c>
       <c r="C477" s="1" t="inlineStr">
@@ -15649,7 +15677,7 @@
       </c>
       <c r="D477" s="1" t="inlineStr">
         <is>
-          <t>董事会</t>
+          <t>木板；板；冲浪板；跳板</t>
         </is>
       </c>
       <c r="E477" s="1" t="inlineStr">
@@ -15799,7 +15827,7 @@
       </c>
       <c r="B482" s="1" t="inlineStr">
         <is>
-          <t>[a.sẽˈblɛj.ɐ] 组装&lt;名&gt;</t>
+          <t>[/a.sẽˈblɛj.ɐ/] 大会；议会&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C482" s="1" t="inlineStr">
@@ -15809,7 +15837,7 @@
       </c>
       <c r="D482" s="1" t="inlineStr">
         <is>
-          <t>组装</t>
+          <t>大会；议会&lt;名&gt;</t>
         </is>
       </c>
       <c r="E482" s="1" t="inlineStr">
@@ -15831,7 +15859,7 @@
       </c>
       <c r="B483" s="1" t="inlineStr">
         <is>
-          <t>[ɐ̃.sesˈtɾaw] 祖先&lt;名&gt;</t>
+          <t>[/ɐ̃.sesˈtɾaw/] 祖先的；古老的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C483" s="1" t="inlineStr">
@@ -15841,7 +15869,7 @@
       </c>
       <c r="D483" s="1" t="inlineStr">
         <is>
-          <t>祖先</t>
+          <t>祖先的；古老的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E483" s="1" t="inlineStr">
@@ -15868,7 +15896,7 @@
       </c>
       <c r="C484" s="1" t="inlineStr">
         <is>
-          <t>ˈpa.tʊs</t>
+          <t>/ˈpa.tʊs/</t>
         </is>
       </c>
       <c r="D484" s="1" t="inlineStr">
@@ -15959,7 +15987,7 @@
       </c>
       <c r="B487" s="1" t="inlineStr">
         <is>
-          <t>[klaˈɾe.zɐ] 克莱雷萨&lt;名&gt;</t>
+          <t>[/klaˈɾe.zɐ/] 清晰；明亮&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C487" s="1" t="inlineStr">
@@ -15969,7 +15997,7 @@
       </c>
       <c r="D487" s="1" t="inlineStr">
         <is>
-          <t>克莱雷萨</t>
+          <t>清晰；明亮&lt;名&gt;</t>
         </is>
       </c>
       <c r="E487" s="1" t="inlineStr">
@@ -15991,7 +16019,7 @@
       </c>
       <c r="B488" s="1" t="inlineStr">
         <is>
-          <t>[foˈɡɐ̃w̃] 福冈&lt;名&gt;</t>
+          <t>[/foˈɡɐ̃w̃/] 炉子；灶&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C488" s="1" t="inlineStr">
@@ -16001,7 +16029,7 @@
       </c>
       <c r="D488" s="1" t="inlineStr">
         <is>
-          <t>福冈</t>
+          <t>炉子；灶&lt;名&gt;</t>
         </is>
       </c>
       <c r="E488" s="1" t="inlineStr">
@@ -16087,7 +16115,7 @@
       </c>
       <c r="B491" s="1" t="inlineStr">
         <is>
-          <t>[vi.t͡ʃiˈma(ʁ)] 维蒂马尔&lt;动&gt;</t>
+          <t>[/vi.t͡ʃiˈma(ʁ)/] 使受害；杀害&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C491" s="1" t="inlineStr">
@@ -16097,7 +16125,7 @@
       </c>
       <c r="D491" s="1" t="inlineStr">
         <is>
-          <t>维蒂马尔</t>
+          <t>使受害；杀害&lt;动&gt;</t>
         </is>
       </c>
       <c r="E491" s="1" t="inlineStr">
@@ -16183,7 +16211,7 @@
       </c>
       <c r="B494" s="1" t="inlineStr">
         <is>
-          <t>[ˈʃɐ̃] 陈&lt;名&gt;</t>
+          <t>[ˈʃɐ̃] 平坦的；平地，低地&lt;名&gt;</t>
         </is>
       </c>
       <c r="C494" s="1" t="inlineStr">
@@ -16193,7 +16221,7 @@
       </c>
       <c r="D494" s="1" t="inlineStr">
         <is>
-          <t>陈</t>
+          <t>平坦的；平地，低地</t>
         </is>
       </c>
       <c r="E494" s="1" t="inlineStr">
@@ -16215,17 +16243,17 @@
       </c>
       <c r="B495" s="1" t="inlineStr">
         <is>
-          <t>[a.ˈbɾi.ɾãʊ̃] 阿布里拉姆&lt;动&gt;</t>
+          <t>[a.ˈbɾi.ɾãʊ̃] 打开（他们）&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C495" s="1" t="inlineStr">
         <is>
-          <t>a.ˈbɾi.ɾãʊ̃</t>
+          <t>/a.ˈbɾi.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D495" s="1" t="inlineStr">
         <is>
-          <t>阿布里拉姆</t>
+          <t>打开（他们）&lt;动&gt;</t>
         </is>
       </c>
       <c r="E495" s="1" t="inlineStr">
@@ -16311,17 +16339,17 @@
       </c>
       <c r="B498" s="1" t="inlineStr">
         <is>
-          <t>[na.ˈse.ɾãʊ̃] 纳斯塞拉姆&lt;动&gt;</t>
+          <t>[na.ˈse.ɾãʊ̃] 出生（他们）&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C498" s="1" t="inlineStr">
         <is>
-          <t>na.ˈse.ɾãʊ̃</t>
+          <t>/na.ˈse.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D498" s="1" t="inlineStr">
         <is>
-          <t>纳斯塞拉姆</t>
+          <t>出生（他们）&lt;动&gt;</t>
         </is>
       </c>
       <c r="E498" s="1" t="inlineStr">
@@ -16343,7 +16371,7 @@
       </c>
       <c r="B499" s="1" t="inlineStr">
         <is>
-          <t>[ˈtɾɐ̃.kɐ] 特兰卡&lt;名&gt;</t>
+          <t>[ˈtɾɐ̃.kɐ] 锁；门闩&lt;名&gt;</t>
         </is>
       </c>
       <c r="C499" s="1" t="inlineStr">
@@ -16353,7 +16381,7 @@
       </c>
       <c r="D499" s="1" t="inlineStr">
         <is>
-          <t>特兰卡</t>
+          <t>锁；门闩</t>
         </is>
       </c>
       <c r="E499" s="1" t="inlineStr">
@@ -16503,7 +16531,7 @@
       </c>
       <c r="B504" s="1" t="inlineStr">
         <is>
-          <t>[ʁeˈvɔw.veʁ] 旋转器&lt;名&gt;</t>
+          <t>[ʁeˈvɔw.veʁ] 左轮手枪&lt;名&gt;</t>
         </is>
       </c>
       <c r="C504" s="1" t="inlineStr">
@@ -16513,7 +16541,7 @@
       </c>
       <c r="D504" s="1" t="inlineStr">
         <is>
-          <t>旋转器</t>
+          <t>左轮手枪</t>
         </is>
       </c>
       <c r="E504" s="1" t="inlineStr">
@@ -16567,7 +16595,7 @@
       </c>
       <c r="B506" s="1" t="inlineStr">
         <is>
-          <t>[suˈka.tɐ] 苏卡塔&lt;名&gt;</t>
+          <t>[/suˈka.tɐ/] 废料；废旧金属&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C506" s="1" t="inlineStr">
@@ -16577,7 +16605,7 @@
       </c>
       <c r="D506" s="1" t="inlineStr">
         <is>
-          <t>苏卡塔</t>
+          <t>废料；废旧金属&lt;名&gt;</t>
         </is>
       </c>
       <c r="E506" s="1" t="inlineStr">
@@ -16631,17 +16659,17 @@
       </c>
       <c r="B508" s="1" t="inlineStr">
         <is>
-          <t>[lu.ˈta.ɾãʊ̃] 卢塔拉姆&lt;动&gt;</t>
+          <t>[lu.ˈta.ɾãʊ̃] 战斗；搏斗（他们）&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C508" s="1" t="inlineStr">
         <is>
-          <t>lu.ˈta.ɾãʊ̃</t>
+          <t>/lu.ˈta.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D508" s="1" t="inlineStr">
         <is>
-          <t>卢塔拉姆</t>
+          <t>战斗；搏斗（他们）&lt;动&gt;</t>
         </is>
       </c>
       <c r="E508" s="1" t="inlineStr">
@@ -16727,17 +16755,17 @@
       </c>
       <c r="B511" s="1" t="inlineStr">
         <is>
-          <t>[teɣ.mi.ˈna.ɾãʊ̃] 终点站&lt;动&gt;</t>
+          <t>[teɣ.mi.ˈna.ɾãʊ̃] 结束；完成&lt;动&gt;</t>
         </is>
       </c>
       <c r="C511" s="1" t="inlineStr">
         <is>
-          <t>teɣ.mi.ˈna.ɾãʊ̃</t>
+          <t>/teɣ.mi.ˈna.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D511" s="1" t="inlineStr">
         <is>
-          <t>终点站</t>
+          <t>结束；完成</t>
         </is>
       </c>
       <c r="E511" s="1" t="inlineStr">
@@ -16791,7 +16819,7 @@
       </c>
       <c r="B513" s="1" t="inlineStr">
         <is>
-          <t>[paʁ.siˈaw] 帕西亚尔&lt;形&gt;</t>
+          <t>[paʁ.siˈaw] 部分的；偏袒的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C513" s="1" t="inlineStr">
@@ -16801,7 +16829,7 @@
       </c>
       <c r="D513" s="1" t="inlineStr">
         <is>
-          <t>帕西亚尔</t>
+          <t>部分的；偏袒的</t>
         </is>
       </c>
       <c r="E513" s="1" t="inlineStr">
@@ -16956,7 +16984,7 @@
       </c>
       <c r="C518" s="1" t="inlineStr">
         <is>
-          <t>fa.ˈʎa.ɾãʊ̃</t>
+          <t>/fa.ˈʎa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D518" s="1" t="inlineStr">
@@ -17239,7 +17267,7 @@
       </c>
       <c r="B527" s="1" t="inlineStr">
         <is>
-          <t>[maˈɛs.tɾu] 导体&lt;名&gt;</t>
+          <t>[maˈɛs.tɾu] 指挥家；音乐大师&lt;名&gt;</t>
         </is>
       </c>
       <c r="C527" s="1" t="inlineStr">
@@ -17249,7 +17277,7 @@
       </c>
       <c r="D527" s="1" t="inlineStr">
         <is>
-          <t>导体</t>
+          <t>指挥家；音乐大师</t>
         </is>
       </c>
       <c r="E527" s="1" t="inlineStr">
@@ -17783,7 +17811,7 @@
       </c>
       <c r="B544" s="1" t="inlineStr">
         <is>
-          <t>[ma.ni.fes.taˈsɐ̃w̃] 示范&lt;名&gt;</t>
+          <t>[ma.ni.fes.taˈsɐ̃w̃] 示威游行；表现；表明&lt;名&gt;</t>
         </is>
       </c>
       <c r="C544" s="1" t="inlineStr">
@@ -17793,7 +17821,7 @@
       </c>
       <c r="D544" s="1" t="inlineStr">
         <is>
-          <t>示范</t>
+          <t>示威游行；表现；表明</t>
         </is>
       </c>
       <c r="E544" s="1" t="inlineStr">
@@ -18106,7 +18134,11 @@
           <t>你会的&lt;动&gt;</t>
         </is>
       </c>
-      <c r="C554" s="1" t="inlineStr"/>
+      <c r="C554" s="1" t="inlineStr">
+        <is>
+          <t>/ˈazdɨ/</t>
+        </is>
+      </c>
       <c r="D554" s="1" t="inlineStr">
         <is>
           <t>你会的</t>
@@ -18198,7 +18230,11 @@
           <t>莫妮卡&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C557" s="1" t="inlineStr"/>
+      <c r="C557" s="1" t="inlineStr">
+        <is>
+          <t>/mɔnˈika/</t>
+        </is>
+      </c>
       <c r="D557" s="1" t="inlineStr">
         <is>
           <t>莫妮卡</t>
@@ -18772,7 +18808,7 @@
       </c>
       <c r="C575" s="1" t="inlineStr">
         <is>
-          <t>su.peɣ.vi.ˈzãʊ̃</t>
+          <t>/su.peɣ.vi.ˈzãʊ̃/</t>
         </is>
       </c>
       <c r="D575" s="1" t="inlineStr">
@@ -19375,7 +19411,7 @@
       </c>
       <c r="B594" s="1" t="inlineStr">
         <is>
-          <t>[ˌɡɾa.viˈmẽ.t͡ʃi] 认真地&lt;副&gt;</t>
+          <t>[ˌɡɾa.viˈmẽ.t͡ʃi] 严重地；沉重地&lt;副&gt;</t>
         </is>
       </c>
       <c r="C594" s="1" t="inlineStr">
@@ -19385,7 +19421,7 @@
       </c>
       <c r="D594" s="1" t="inlineStr">
         <is>
-          <t>认真地</t>
+          <t>严重地；沉重地</t>
         </is>
       </c>
       <c r="E594" s="1" t="inlineStr">
@@ -19695,7 +19731,7 @@
       </c>
       <c r="B604" s="1" t="inlineStr">
         <is>
-          <t>[ˈkɐ̃.pɐ] 坟墓&lt;名&gt;</t>
+          <t>[/ˈkɐ̃.pɐ/] 墓碑&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C604" s="1" t="inlineStr">
@@ -19705,7 +19741,7 @@
       </c>
       <c r="D604" s="1" t="inlineStr">
         <is>
-          <t>坟墓</t>
+          <t>墓碑&lt;名&gt;</t>
         </is>
       </c>
       <c r="E604" s="1" t="inlineStr">
@@ -19983,7 +20019,7 @@
       </c>
       <c r="B613" s="1" t="inlineStr">
         <is>
-          <t>[e.ɾupˈsɐ̃w̃] 皮疹&lt;名&gt;</t>
+          <t>[/e.ɾupˈsɐ̃w̃/] 爆发；喷发&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C613" s="1" t="inlineStr">
@@ -19993,7 +20029,7 @@
       </c>
       <c r="D613" s="1" t="inlineStr">
         <is>
-          <t>皮疹</t>
+          <t>爆发；喷发</t>
         </is>
       </c>
       <c r="E613" s="1" t="inlineStr">
@@ -20340,7 +20376,7 @@
       </c>
       <c r="C624" s="1" t="inlineStr">
         <is>
-          <t>peɣ.gũ.ˈta.ɾãʊ̃</t>
+          <t>/peɣ.gũ.ˈta.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D624" s="1" t="inlineStr">
@@ -20399,7 +20435,7 @@
       </c>
       <c r="B626" s="1" t="inlineStr">
         <is>
-          <t>[a.põˈta.du] 尖的&lt;形&gt;</t>
+          <t>[a.põˈta.du] 指出的；削尖的；记录的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C626" s="1" t="inlineStr">
@@ -20409,7 +20445,7 @@
       </c>
       <c r="D626" s="1" t="inlineStr">
         <is>
-          <t>尖的</t>
+          <t>指出的；削尖的；记录的</t>
         </is>
       </c>
       <c r="E626" s="1" t="inlineStr">
@@ -20943,7 +20979,7 @@
       </c>
       <c r="B643" s="1" t="inlineStr">
         <is>
-          <t>[pa] 帕&lt;介&gt;</t>
+          <t>[pa] 向；为了；到&lt;介&gt;</t>
         </is>
       </c>
       <c r="C643" s="1" t="inlineStr">
@@ -20953,7 +20989,7 @@
       </c>
       <c r="D643" s="1" t="inlineStr">
         <is>
-          <t>帕</t>
+          <t>向；为了；到</t>
         </is>
       </c>
       <c r="E643" s="1" t="inlineStr">
@@ -21039,7 +21075,7 @@
       </c>
       <c r="B646" s="1" t="inlineStr">
         <is>
-          <t>[fisˈkaw] 税&lt;名&gt;</t>
+          <t>[fisˈkaw] 税务的；财政的；税务员；稽查员&lt;名&gt;</t>
         </is>
       </c>
       <c r="C646" s="1" t="inlineStr">
@@ -21049,7 +21085,7 @@
       </c>
       <c r="D646" s="1" t="inlineStr">
         <is>
-          <t>税</t>
+          <t>税务的；财政的；税务员；稽查员</t>
         </is>
       </c>
       <c r="E646" s="1" t="inlineStr">
@@ -21140,7 +21176,7 @@
       </c>
       <c r="C649" s="1" t="inlineStr">
         <is>
-          <t>a.gɾi.kuw.ˈtu.ɾə</t>
+          <t>/a.gɾi.kuw.ˈtu.ɾə/</t>
         </is>
       </c>
       <c r="D649" s="1" t="inlineStr">
@@ -21327,7 +21363,7 @@
       </c>
       <c r="B655" s="1" t="inlineStr">
         <is>
-          <t>[taˈpa(ʁ)] 封面&lt;动&gt;</t>
+          <t>[taˈpa(ʁ)] 盖住；堵住；遮盖&lt;动&gt;</t>
         </is>
       </c>
       <c r="C655" s="1" t="inlineStr">
@@ -21337,7 +21373,7 @@
       </c>
       <c r="D655" s="1" t="inlineStr">
         <is>
-          <t>封面</t>
+          <t>盖住；堵住；遮盖</t>
         </is>
       </c>
       <c r="E655" s="1" t="inlineStr">
@@ -21716,7 +21752,7 @@
       </c>
       <c r="C667" s="1" t="inlineStr">
         <is>
-          <t>aw.te.ˈɾa.dʊ</t>
+          <t>/aw.te.ˈɾa.dʊ/</t>
         </is>
       </c>
       <c r="D667" s="1" t="inlineStr">
@@ -21775,7 +21811,7 @@
       </c>
       <c r="B669" s="1" t="inlineStr">
         <is>
-          <t>[fo.to.ɡɾaˈfa(ʁ)] 照片&lt;动&gt;</t>
+          <t>[fo.to.ɡɾaˈfa(ʁ)] 拍照；摄影&lt;动&gt;</t>
         </is>
       </c>
       <c r="C669" s="1" t="inlineStr">
@@ -21785,7 +21821,7 @@
       </c>
       <c r="D669" s="1" t="inlineStr">
         <is>
-          <t>照片</t>
+          <t>拍照；摄影</t>
         </is>
       </c>
       <c r="E669" s="1" t="inlineStr">
@@ -21871,7 +21907,7 @@
       </c>
       <c r="B672" s="1" t="inlineStr">
         <is>
-          <t>[fi.nɐ̃.siˈa(ʁ)] 金融&lt;动&gt;</t>
+          <t>[fi.nɐ̃.siˈa(ʁ)] 资助；融资；提供资金&lt;动&gt;</t>
         </is>
       </c>
       <c r="C672" s="1" t="inlineStr">
@@ -21881,7 +21917,7 @@
       </c>
       <c r="D672" s="1" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>资助；融资；提供资金</t>
         </is>
       </c>
       <c r="E672" s="1" t="inlineStr">
@@ -22095,7 +22131,7 @@
       </c>
       <c r="B679" s="1" t="inlineStr">
         <is>
-          <t>[kaˈpu(j)s] 引擎盖&lt;名&gt;</t>
+          <t>[kaˈpu(j)s] 兜帽；风帽&lt;名&gt;</t>
         </is>
       </c>
       <c r="C679" s="1" t="inlineStr">
@@ -22105,7 +22141,7 @@
       </c>
       <c r="D679" s="1" t="inlineStr">
         <is>
-          <t>引擎盖</t>
+          <t>兜帽；风帽</t>
         </is>
       </c>
       <c r="E679" s="1" t="inlineStr">
@@ -22543,7 +22579,7 @@
       </c>
       <c r="B693" s="1" t="inlineStr">
         <is>
-          <t>[ʁe.aˈle.zɐ] 版税&lt;名&gt;</t>
+          <t>[/ʁe.aˈle.zɐ/] 王室；王族&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C693" s="1" t="inlineStr">
@@ -22553,7 +22589,7 @@
       </c>
       <c r="D693" s="1" t="inlineStr">
         <is>
-          <t>版税</t>
+          <t>王室；王族&lt;名&gt;</t>
         </is>
       </c>
       <c r="E693" s="1" t="inlineStr">
@@ -22639,7 +22675,7 @@
       </c>
       <c r="B696" s="1" t="inlineStr">
         <is>
-          <t>[liˈʃe(j).ɾu] 垃圾人&lt;名&gt;</t>
+          <t>[/liˈʃe(j).ɾu/] 清洁工；垃圾收集工&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C696" s="1" t="inlineStr">
@@ -22649,7 +22685,7 @@
       </c>
       <c r="D696" s="1" t="inlineStr">
         <is>
-          <t>垃圾人</t>
+          <t>清洁工；垃圾收集工&lt;名&gt;</t>
         </is>
       </c>
       <c r="E696" s="1" t="inlineStr">
@@ -23023,7 +23059,7 @@
       </c>
       <c r="B708" s="1" t="inlineStr">
         <is>
-          <t>[a.sẽˈta(ʁ)] 解决&lt;动&gt;</t>
+          <t>[/a.sẽˈta(ʁ)/] 安放；使固定；定居&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C708" s="1" t="inlineStr">
@@ -23033,7 +23069,7 @@
       </c>
       <c r="D708" s="1" t="inlineStr">
         <is>
-          <t>解决</t>
+          <t>安放；使固定；定居&lt;动&gt;</t>
         </is>
       </c>
       <c r="E708" s="1" t="inlineStr">
@@ -23215,7 +23251,7 @@
       </c>
       <c r="B714" s="1" t="inlineStr">
         <is>
-          <t>[ˈi.d͡ʒi] 去&lt;名&gt;</t>
+          <t>[/ˈi.d͡ʒi/] 去&lt;动&gt;（动词 ir 的变位形式）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C714" s="1" t="inlineStr">
@@ -23225,7 +23261,7 @@
       </c>
       <c r="D714" s="1" t="inlineStr">
         <is>
-          <t>去</t>
+          <t>去&lt;动&gt;（动词 ir 的变位形式）</t>
         </is>
       </c>
       <c r="E714" s="1" t="inlineStr">
@@ -23284,7 +23320,7 @@
       </c>
       <c r="C716" s="1" t="inlineStr">
         <is>
-          <t>se.le.ˈsãʊ̃</t>
+          <t>/se.le.ˈsãʊ̃/</t>
         </is>
       </c>
       <c r="D716" s="1" t="inlineStr">
@@ -23631,7 +23667,7 @@
       </c>
       <c r="B727" s="1" t="inlineStr">
         <is>
-          <t>[dezˈɡos.tu] 心碎&lt;名&gt;</t>
+          <t>[dezˈɡos.tu] 悲伤；痛苦；厌恶&lt;名&gt;</t>
         </is>
       </c>
       <c r="C727" s="1" t="inlineStr">
@@ -23641,7 +23677,7 @@
       </c>
       <c r="D727" s="1" t="inlineStr">
         <is>
-          <t>心碎</t>
+          <t>悲伤；痛苦；厌恶</t>
         </is>
       </c>
       <c r="E727" s="1" t="inlineStr">
@@ -23887,7 +23923,7 @@
       </c>
       <c r="B735" s="1" t="inlineStr">
         <is>
-          <t>[vo.aˈdoʁ] 飞行&lt;形&gt;</t>
+          <t>[vo.aˈdoʁ] 飞行的；会飞的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C735" s="1" t="inlineStr">
@@ -23897,7 +23933,7 @@
       </c>
       <c r="D735" s="1" t="inlineStr">
         <is>
-          <t>飞行</t>
+          <t>飞行的；会飞的</t>
         </is>
       </c>
       <c r="E735" s="1" t="inlineStr">
@@ -23983,7 +24019,7 @@
       </c>
       <c r="B738" s="1" t="inlineStr">
         <is>
-          <t>[ko.moˈvẽ.t͡ʃi] 移动&lt;形&gt;</t>
+          <t>[ko.moˈvẽ.t͡ʃi] 感人的；动人的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C738" s="1" t="inlineStr">
@@ -23993,7 +24029,7 @@
       </c>
       <c r="D738" s="1" t="inlineStr">
         <is>
-          <t>移动</t>
+          <t>感人的；动人的</t>
         </is>
       </c>
       <c r="E738" s="1" t="inlineStr">
@@ -24207,7 +24243,7 @@
       </c>
       <c r="B745" s="1" t="inlineStr">
         <is>
-          <t>[ʁe.toˈma(ʁ)] 简历&lt;动&gt;</t>
+          <t>[ʁe.toˈma(ʁ)] 恢复；重新开始；取回&lt;动&gt;</t>
         </is>
       </c>
       <c r="C745" s="1" t="inlineStr">
@@ -24217,7 +24253,7 @@
       </c>
       <c r="D745" s="1" t="inlineStr">
         <is>
-          <t>简历</t>
+          <t>恢复；重新开始；取回</t>
         </is>
       </c>
       <c r="E745" s="1" t="inlineStr">
@@ -24308,7 +24344,7 @@
       </c>
       <c r="C748" s="1" t="inlineStr">
         <is>
-          <t>a.xã.ˈʒa.ɾãʊ̃</t>
+          <t>/a.xã.ˈʒa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D748" s="1" t="inlineStr">
@@ -24655,7 +24691,7 @@
       </c>
       <c r="B759" s="1" t="inlineStr">
         <is>
-          <t>[ˈbɛ.ki] 贝克&lt;名&gt;</t>
+          <t>[/ˈbɛ.ki/] 大麻烟卷&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C759" s="1" t="inlineStr">
@@ -24665,7 +24701,7 @@
       </c>
       <c r="D759" s="1" t="inlineStr">
         <is>
-          <t>贝克</t>
+          <t>大麻烟卷&lt;名&gt;</t>
         </is>
       </c>
       <c r="E759" s="1" t="inlineStr">
@@ -24719,7 +24755,7 @@
       </c>
       <c r="B761" s="1" t="inlineStr">
         <is>
-          <t>[aˈta(ʁ)] 领带&lt;动&gt;</t>
+          <t>[aˈta(ʁ)] 系；绑；捆&lt;动&gt;</t>
         </is>
       </c>
       <c r="C761" s="1" t="inlineStr">
@@ -24729,7 +24765,7 @@
       </c>
       <c r="D761" s="1" t="inlineStr">
         <is>
-          <t>领带</t>
+          <t>系；绑；捆</t>
         </is>
       </c>
       <c r="E761" s="1" t="inlineStr">
@@ -24847,7 +24883,7 @@
       </c>
       <c r="B765" s="1" t="inlineStr">
         <is>
-          <t>[kaʁˈva.ʎu] 橡木&lt;名&gt;</t>
+          <t>[/kaʁˈva.ʎu/] 橡树&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C765" s="1" t="inlineStr">
@@ -24857,7 +24893,7 @@
       </c>
       <c r="D765" s="1" t="inlineStr">
         <is>
-          <t>橡木</t>
+          <t>橡树&lt;名&gt;</t>
         </is>
       </c>
       <c r="E765" s="1" t="inlineStr">
@@ -24916,7 +24952,7 @@
       </c>
       <c r="C767" s="1" t="inlineStr">
         <is>
-          <t>es.tɾa.ˈsãʊ̃</t>
+          <t>/es.tɾa.ˈsãʊ̃/</t>
         </is>
       </c>
       <c r="D767" s="1" t="inlineStr">
@@ -24948,7 +24984,7 @@
       </c>
       <c r="C768" s="1" t="inlineStr">
         <is>
-          <t>a.sex.ˈta.dʊ</t>
+          <t>/a.sex.ˈta.dʊ/</t>
         </is>
       </c>
       <c r="D768" s="1" t="inlineStr">
@@ -25103,7 +25139,7 @@
       </c>
       <c r="B773" s="1" t="inlineStr">
         <is>
-          <t>[isˈta.bu.lu] 稳定&lt;名&gt;</t>
+          <t>[isˈta.bu.lu] 马厩；畜栏&lt;名&gt;</t>
         </is>
       </c>
       <c r="C773" s="1" t="inlineStr">
@@ -25113,7 +25149,7 @@
       </c>
       <c r="D773" s="1" t="inlineStr">
         <is>
-          <t>稳定</t>
+          <t>马厩；畜栏</t>
         </is>
       </c>
       <c r="E773" s="1" t="inlineStr">
@@ -25138,7 +25174,11 @@
           <t>向下&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C774" s="1" t="inlineStr"/>
+      <c r="C774" s="1" t="inlineStr">
+        <is>
+          <t>/daʊn/</t>
+        </is>
+      </c>
       <c r="D774" s="1" t="inlineStr">
         <is>
           <t>向下</t>
@@ -25232,7 +25272,7 @@
       </c>
       <c r="C777" s="1" t="inlineStr">
         <is>
-          <t>ˈfi.ɾeʁ</t>
+          <t>/ˈfi.ɾeʁ/</t>
         </is>
       </c>
       <c r="D777" s="1" t="inlineStr">
@@ -25296,7 +25336,7 @@
       </c>
       <c r="C779" s="1" t="inlineStr">
         <is>
-          <t>ax.ki.ˈtɛ.tʊ</t>
+          <t>/ax.ki.ˈtɛ.tʊ/</t>
         </is>
       </c>
       <c r="D779" s="1" t="inlineStr">
@@ -25963,7 +26003,7 @@
       </c>
       <c r="B800" s="1" t="inlineStr">
         <is>
-          <t>[si.taˈsɐ̃w̃] 报价&lt;名&gt;</t>
+          <t>[si.taˈsɐ̃w̃] 引用；引文；传票&lt;名&gt;</t>
         </is>
       </c>
       <c r="C800" s="1" t="inlineStr">
@@ -25973,7 +26013,7 @@
       </c>
       <c r="D800" s="1" t="inlineStr">
         <is>
-          <t>报价</t>
+          <t>引用；引文；传票</t>
         </is>
       </c>
       <c r="E800" s="1" t="inlineStr">
@@ -26000,7 +26040,7 @@
       </c>
       <c r="C801" s="1" t="inlineStr">
         <is>
-          <t>a.ˈfe.tʊ</t>
+          <t>/a.ˈfe.tʊ/</t>
         </is>
       </c>
       <c r="D801" s="1" t="inlineStr">
@@ -26123,7 +26163,7 @@
       </c>
       <c r="B805" s="1" t="inlineStr">
         <is>
-          <t>[maˈɾa.du] 疯狂的&lt;形&gt;</t>
+          <t>[maˈɾa.du] 疯狂的；发疯的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C805" s="1" t="inlineStr">
@@ -26133,7 +26173,7 @@
       </c>
       <c r="D805" s="1" t="inlineStr">
         <is>
-          <t>疯狂的</t>
+          <t>疯狂的；发疯的</t>
         </is>
       </c>
       <c r="E805" s="1" t="inlineStr">
@@ -26446,7 +26486,11 @@
           <t>厕所&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C815" s="1" t="inlineStr"/>
+      <c r="C815" s="1" t="inlineStr">
+        <is>
+          <t>/dab.li.uˈse/</t>
+        </is>
+      </c>
       <c r="D815" s="1" t="inlineStr">
         <is>
           <t>厕所</t>
@@ -26604,7 +26648,7 @@
       </c>
       <c r="C820" s="1" t="inlineStr">
         <is>
-          <t>ˈpɔ.dɾɪs</t>
+          <t>/ˈpɔ.dɾɪs/</t>
         </is>
       </c>
       <c r="D820" s="1" t="inlineStr">
@@ -26855,17 +26899,17 @@
       </c>
       <c r="B828" s="1" t="inlineStr">
         <is>
-          <t>[se.ˈgi.ɾãʊ̃] 已关注&lt;动&gt;</t>
+          <t>[se.ˈgi.ɾãʊ̃] 跟随；追随&lt;动&gt;</t>
         </is>
       </c>
       <c r="C828" s="1" t="inlineStr">
         <is>
-          <t>se.ˈgi.ɾãʊ̃</t>
+          <t>/se.ˈgi.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D828" s="1" t="inlineStr">
         <is>
-          <t>已关注</t>
+          <t>跟随；追随</t>
         </is>
       </c>
       <c r="E828" s="1" t="inlineStr">
@@ -26956,7 +27000,7 @@
       </c>
       <c r="C831" s="1" t="inlineStr">
         <is>
-          <t>es.ka.ˈpa.ɾãʊ̃</t>
+          <t>/es.ka.ˈpa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D831" s="1" t="inlineStr">
@@ -27148,7 +27192,7 @@
       </c>
       <c r="C837" s="1" t="inlineStr">
         <is>
-          <t>pe.ˈga.ɾãʊ̃</t>
+          <t>/pe.ˈga.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D837" s="1" t="inlineStr">
@@ -27175,7 +27219,7 @@
       </c>
       <c r="B838" s="1" t="inlineStr">
         <is>
-          <t>[is.peˈlũ.kɐ] 联合&lt;名&gt;</t>
+          <t>[is.peˈlũ.kɐ] 下等酒吧；低级酒馆；贼窝&lt;名&gt;</t>
         </is>
       </c>
       <c r="C838" s="1" t="inlineStr">
@@ -27185,7 +27229,7 @@
       </c>
       <c r="D838" s="1" t="inlineStr">
         <is>
-          <t>联合</t>
+          <t>下等酒吧；低级酒馆；贼窝</t>
         </is>
       </c>
       <c r="E838" s="1" t="inlineStr">
@@ -27687,7 +27731,7 @@
       </c>
       <c r="B854" s="1" t="inlineStr">
         <is>
-          <t>[tɾeˈmẽ.du] 摇晃&lt;形&gt;</t>
+          <t>[tɾeˈmẽ.du] 惊人的；巨大的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C854" s="1" t="inlineStr">
@@ -27697,7 +27741,7 @@
       </c>
       <c r="D854" s="1" t="inlineStr">
         <is>
-          <t>摇晃</t>
+          <t>惊人的；巨大的</t>
         </is>
       </c>
       <c r="E854" s="1" t="inlineStr">
@@ -27786,7 +27830,11 @@
           <t>在线&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C857" s="1" t="inlineStr"/>
+      <c r="C857" s="1" t="inlineStr">
+        <is>
+          <t>/õˈlaj.ni/</t>
+        </is>
+      </c>
       <c r="D857" s="1" t="inlineStr">
         <is>
           <t>在线</t>
@@ -27811,7 +27859,7 @@
       </c>
       <c r="B858" s="1" t="inlineStr">
         <is>
-          <t>[ˈta.bwɐ] 董事会&lt;名&gt;</t>
+          <t>[ˈta.bwɐ] 木板；板&lt;名&gt;</t>
         </is>
       </c>
       <c r="C858" s="1" t="inlineStr">
@@ -27821,7 +27869,7 @@
       </c>
       <c r="D858" s="1" t="inlineStr">
         <is>
-          <t>董事会</t>
+          <t>木板；板</t>
         </is>
       </c>
       <c r="E858" s="1" t="inlineStr">
@@ -28035,7 +28083,7 @@
       </c>
       <c r="B865" s="1" t="inlineStr">
         <is>
-          <t>[mo.ni.to.ɾiˈza(ʁ)] 监视器&lt;动&gt;</t>
+          <t>[mo.ni.to.ɾiˈza(ʁ)] 监控；监测&lt;动&gt;</t>
         </is>
       </c>
       <c r="C865" s="1" t="inlineStr">
@@ -28045,7 +28093,7 @@
       </c>
       <c r="D865" s="1" t="inlineStr">
         <is>
-          <t>监视器</t>
+          <t>监控；监测</t>
         </is>
       </c>
       <c r="E865" s="1" t="inlineStr">
@@ -28067,17 +28115,17 @@
       </c>
       <c r="B866" s="1" t="inlineStr">
         <is>
-          <t>[ˈfɾã.sɪs] 法语&lt;名&gt;</t>
+          <t>[ˈfɾã.sɪs] francês 法语&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C866" s="1" t="inlineStr">
         <is>
-          <t>ˈfɾã.sɪs</t>
+          <t>/ˈfɾã.sɪs/</t>
         </is>
       </c>
       <c r="D866" s="1" t="inlineStr">
         <is>
-          <t>法语</t>
+          <t>francês 法语&lt;名&gt;</t>
         </is>
       </c>
       <c r="E866" s="1" t="inlineStr">
@@ -28131,7 +28179,7 @@
       </c>
       <c r="B868" s="1" t="inlineStr">
         <is>
-          <t>[ˈma.ɡu] 向导&lt;名&gt;</t>
+          <t>[ˈma.ɡu] 魔法师；巫师&lt;名&gt;</t>
         </is>
       </c>
       <c r="C868" s="1" t="inlineStr">
@@ -28141,7 +28189,7 @@
       </c>
       <c r="D868" s="1" t="inlineStr">
         <is>
-          <t>向导</t>
+          <t>魔法师；巫师</t>
         </is>
       </c>
       <c r="E868" s="1" t="inlineStr">
@@ -28163,7 +28211,7 @@
       </c>
       <c r="B869" s="1" t="inlineStr">
         <is>
-          <t>[ẽ.paˈta(ʁ)] 画&lt;动&gt;</t>
+          <t>[ẽ.paˈta(ʁ)] 打成平局；战平&lt;动&gt;</t>
         </is>
       </c>
       <c r="C869" s="1" t="inlineStr">
@@ -28173,7 +28221,7 @@
       </c>
       <c r="D869" s="1" t="inlineStr">
         <is>
-          <t>画</t>
+          <t>打成平局；战平</t>
         </is>
       </c>
       <c r="E869" s="1" t="inlineStr">
@@ -28296,7 +28344,7 @@
       </c>
       <c r="C873" s="1" t="inlineStr">
         <is>
-          <t>ˈdo.i</t>
+          <t>/ˈdo.i/</t>
         </is>
       </c>
       <c r="D873" s="1" t="inlineStr">
@@ -28968,7 +29016,7 @@
       </c>
       <c r="C894" s="1" t="inlineStr">
         <is>
-          <t>a.tʃi.ˈɾa.ɾãʊ̃</t>
+          <t>/a.tʃi.ˈɾa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D894" s="1" t="inlineStr">
@@ -29128,7 +29176,7 @@
       </c>
       <c r="C899" s="1" t="inlineStr">
         <is>
-          <t>pa.ɾa.ˈnɔy.ə</t>
+          <t>/pa.ɾa.ˈnɔy.ə/</t>
         </is>
       </c>
       <c r="D899" s="1" t="inlineStr">
@@ -29251,13 +29299,17 @@
       </c>
       <c r="B903" s="1" t="inlineStr">
         <is>
-          <t>不。&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C903" s="1" t="inlineStr"/>
+          <t>号码；编号&lt;名&gt;</t>
+        </is>
+      </c>
+      <c r="C903" s="1" t="inlineStr">
+        <is>
+          <t>/ˈnũ.me.ɾu/</t>
+        </is>
+      </c>
       <c r="D903" s="1" t="inlineStr">
         <is>
-          <t>不。</t>
+          <t>号码；编号</t>
         </is>
       </c>
       <c r="E903" s="1" t="inlineStr">
@@ -29311,7 +29363,7 @@
       </c>
       <c r="B905" s="1" t="inlineStr">
         <is>
-          <t>[ĩ.d͡ʒi.kaˈsɐ̃w̃] 指示&lt;名&gt;</t>
+          <t>[/ĩ.d͡ʒi.kaˈsɐ̃w̃/] 表明；指示；推荐&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C905" s="1" t="inlineStr">
@@ -29321,7 +29373,7 @@
       </c>
       <c r="D905" s="1" t="inlineStr">
         <is>
-          <t>指示</t>
+          <t>表明；指示；推荐&lt;名&gt;</t>
         </is>
       </c>
       <c r="E905" s="1" t="inlineStr">
@@ -29407,7 +29459,7 @@
       </c>
       <c r="B908" s="1" t="inlineStr">
         <is>
-          <t>[ko.ĩ.siˈd͡ʒi(ʁ)] 比赛&lt;动&gt;</t>
+          <t>[ko.ĩ.siˈd͡ʒi(ʁ)] 巧合；一致；同时发生&lt;动&gt;</t>
         </is>
       </c>
       <c r="C908" s="1" t="inlineStr">
@@ -29417,7 +29469,7 @@
       </c>
       <c r="D908" s="1" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>巧合；一致；同时发生</t>
         </is>
       </c>
       <c r="E908" s="1" t="inlineStr">
@@ -29666,7 +29718,11 @@
           <t>恶习&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C916" s="1" t="inlineStr"/>
+      <c r="C916" s="1" t="inlineStr">
+        <is>
+          <t>/vˈike/</t>
+        </is>
+      </c>
       <c r="D916" s="1" t="inlineStr">
         <is>
           <t>恶习</t>
@@ -29755,7 +29811,7 @@
       </c>
       <c r="B919" s="1" t="inlineStr">
         <is>
-          <t>[ɐɾ.tɨˈfak.tu] 神器&lt;名&gt;</t>
+          <t>[ɐɾ.tɨˈfak.tu] 器物；装置&lt;名&gt;</t>
         </is>
       </c>
       <c r="C919" s="1" t="inlineStr">
@@ -29765,7 +29821,7 @@
       </c>
       <c r="D919" s="1" t="inlineStr">
         <is>
-          <t>神器</t>
+          <t>器物；装置</t>
         </is>
       </c>
       <c r="E919" s="1" t="inlineStr">
@@ -29856,7 +29912,7 @@
       </c>
       <c r="C922" s="1" t="inlineStr">
         <is>
-          <t>kõ.ˈpɾa.ɾãʊ̃</t>
+          <t>/kõ.ˈpɾa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D922" s="1" t="inlineStr">
@@ -29952,7 +30008,7 @@
       </c>
       <c r="C925" s="1" t="inlineStr">
         <is>
-          <t>a.dop.ˈtax</t>
+          <t>/a.dop.ˈtax/</t>
         </is>
       </c>
       <c r="D925" s="1" t="inlineStr">
@@ -30203,7 +30259,7 @@
       </c>
       <c r="B933" s="1" t="inlineStr">
         <is>
-          <t>[ʁas.tɾeˈa(ʁ)] 轨道&lt;动&gt;</t>
+          <t>[ʁas.tɾeˈa(ʁ)] 追踪；跟踪&lt;动&gt;</t>
         </is>
       </c>
       <c r="C933" s="1" t="inlineStr">
@@ -30213,7 +30269,7 @@
       </c>
       <c r="D933" s="1" t="inlineStr">
         <is>
-          <t>轨道</t>
+          <t>追踪；跟踪</t>
         </is>
       </c>
       <c r="E933" s="1" t="inlineStr">
@@ -30592,7 +30648,7 @@
       </c>
       <c r="C945" s="1" t="inlineStr">
         <is>
-          <t>es.te.ˈɾɔy.dʒɪ</t>
+          <t>/es.te.ˈɾɔy.dʒɪ/</t>
         </is>
       </c>
       <c r="D945" s="1" t="inlineStr">
@@ -30747,7 +30803,7 @@
       </c>
       <c r="B950" s="1" t="inlineStr">
         <is>
-          <t>[ˈɡɾe.ʎɐ] 烧烤&lt;名&gt;</t>
+          <t>[/ˈɡɾe.ʎɐ/] 烤架&lt;名&gt;；烤网&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C950" s="1" t="inlineStr">
@@ -30757,7 +30813,7 @@
       </c>
       <c r="D950" s="1" t="inlineStr">
         <is>
-          <t>烧烤</t>
+          <t>烤架&lt;名&gt;；烤网&lt;名&gt;</t>
         </is>
       </c>
       <c r="E950" s="1" t="inlineStr">
@@ -30878,7 +30934,11 @@
           <t>例如&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C954" s="1" t="inlineStr"/>
+      <c r="C954" s="1" t="inlineStr">
+        <is>
+          <t>/eˈzẽ.plu/</t>
+        </is>
+      </c>
       <c r="D954" s="1" t="inlineStr">
         <is>
           <t>例如</t>
@@ -30938,7 +30998,11 @@
           <t>河&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C956" s="1" t="inlineStr"/>
+      <c r="C956" s="1" t="inlineStr">
+        <is>
+          <t>/ˈʁi.u/</t>
+        </is>
+      </c>
       <c r="D956" s="1" t="inlineStr">
         <is>
           <t>河</t>
@@ -30968,7 +31032,7 @@
       </c>
       <c r="C957" s="1" t="inlineStr">
         <is>
-          <t>a.moɣ.ˈzĩ.ɲʊ</t>
+          <t>/a.moɣ.ˈzĩ.ɲʊ/</t>
         </is>
       </c>
       <c r="D957" s="1" t="inlineStr">
@@ -31091,7 +31155,7 @@
       </c>
       <c r="B961" s="1" t="inlineStr">
         <is>
-          <t>[bɾĩˈda(ʁ)] 吐司&lt;动&gt;</t>
+          <t>[bɾĩˈda(ʁ)] 敬酒；祝酒&lt;动&gt;</t>
         </is>
       </c>
       <c r="C961" s="1" t="inlineStr">
@@ -31101,7 +31165,7 @@
       </c>
       <c r="D961" s="1" t="inlineStr">
         <is>
-          <t>吐司</t>
+          <t>敬酒；祝酒</t>
         </is>
       </c>
       <c r="E961" s="1" t="inlineStr">
@@ -31126,7 +31190,11 @@
           <t>电子产品&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C962" s="1" t="inlineStr"/>
+      <c r="C962" s="1" t="inlineStr">
+        <is>
+          <t>/elektʁɔnˈika/</t>
+        </is>
+      </c>
       <c r="D962" s="1" t="inlineStr">
         <is>
           <t>电子产品</t>
@@ -31439,7 +31507,7 @@
       </c>
       <c r="B972" s="1" t="inlineStr">
         <is>
-          <t>[dez.liˈza(ʁ)] 幻灯片&lt;动&gt;</t>
+          <t>[dez.liˈza(ʁ)] 滑动；滑行&lt;动&gt;</t>
         </is>
       </c>
       <c r="C972" s="1" t="inlineStr">
@@ -31449,7 +31517,7 @@
       </c>
       <c r="D972" s="1" t="inlineStr">
         <is>
-          <t>幻灯片</t>
+          <t>滑动；滑行</t>
         </is>
       </c>
       <c r="E972" s="1" t="inlineStr">
@@ -31695,7 +31763,7 @@
       </c>
       <c r="B980" s="1" t="inlineStr">
         <is>
-          <t>[iˈsa(ʁ)] 提升机&lt;动&gt;</t>
+          <t>[iˈsa(ʁ)] 升起；吊起&lt;动&gt;</t>
         </is>
       </c>
       <c r="C980" s="1" t="inlineStr">
@@ -31705,7 +31773,7 @@
       </c>
       <c r="D980" s="1" t="inlineStr">
         <is>
-          <t>提升机</t>
+          <t>升起；吊起</t>
         </is>
       </c>
       <c r="E980" s="1" t="inlineStr">
@@ -31794,7 +31862,11 @@
           <t>会&lt;动&gt;</t>
         </is>
       </c>
-      <c r="C983" s="1" t="inlineStr"/>
+      <c r="C983" s="1" t="inlineStr">
+        <is>
+          <t>/ˈɐ̃w̃dɨ/</t>
+        </is>
+      </c>
       <c r="D983" s="1" t="inlineStr">
         <is>
           <t>会</t>
@@ -31822,7 +31894,11 @@
           <t>热&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C984" s="1" t="inlineStr"/>
+      <c r="C984" s="1" t="inlineStr">
+        <is>
+          <t>/ˈot/</t>
+        </is>
+      </c>
       <c r="D984" s="1" t="inlineStr">
         <is>
           <t>热</t>
@@ -31911,7 +31987,7 @@
       </c>
       <c r="B987" s="1" t="inlineStr">
         <is>
-          <t>[maʁ.kaˈdoʁ] 标记&lt;名&gt;</t>
+          <t>[/maʁ.kaˈdoʁ/] 记号笔；标记物&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C987" s="1" t="inlineStr">
@@ -31921,7 +31997,7 @@
       </c>
       <c r="D987" s="1" t="inlineStr">
         <is>
-          <t>标记</t>
+          <t>记号笔；标记物&lt;名&gt;</t>
         </is>
       </c>
       <c r="E987" s="1" t="inlineStr">
@@ -32007,7 +32083,7 @@
       </c>
       <c r="B990" s="1" t="inlineStr">
         <is>
-          <t>[sẽ.sa.si.oˈnaw] 耸人听闻的&lt;形&gt;</t>
+          <t>[/sẽ.sa.si.oˈnaw/] 精彩的；轰动的&lt;形&gt;&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C990" s="1" t="inlineStr">
@@ -32017,7 +32093,7 @@
       </c>
       <c r="D990" s="1" t="inlineStr">
         <is>
-          <t>耸人听闻的</t>
+          <t>精彩的；轰动的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E990" s="1" t="inlineStr">
@@ -32071,7 +32147,7 @@
       </c>
       <c r="B992" s="1" t="inlineStr">
         <is>
-          <t>[ˈʃi.sɐ] 奇卡&lt;叹&gt;</t>
+          <t>[ˈʃi.sɐ] 哎呀；天哪&lt;叹&gt;</t>
         </is>
       </c>
       <c r="C992" s="1" t="inlineStr">
@@ -32081,7 +32157,7 @@
       </c>
       <c r="D992" s="1" t="inlineStr">
         <is>
-          <t>奇卡</t>
+          <t>哎呀；天哪</t>
         </is>
       </c>
       <c r="E992" s="1" t="inlineStr">
@@ -32874,7 +32950,11 @@
           <t>黑帮&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1017" s="1" t="inlineStr"/>
+      <c r="C1017" s="1" t="inlineStr">
+        <is>
+          <t>/ˈɡɐ̃ʃ.tɛʁ/</t>
+        </is>
+      </c>
       <c r="D1017" s="1" t="inlineStr">
         <is>
           <t>黑帮</t>
@@ -33288,7 +33368,7 @@
       </c>
       <c r="C1030" s="1" t="inlineStr">
         <is>
-          <t>dʒis.ku.ˈtʃi.ɾãʊ̃</t>
+          <t>/dʒis.ku.ˈtʃi.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1030" s="1" t="inlineStr">
@@ -33315,7 +33395,7 @@
       </c>
       <c r="B1031" s="1" t="inlineStr">
         <is>
-          <t>[aˈdɛ.ɡɐ] 地窖&lt;名&gt;</t>
+          <t>[/aˈdɛ.ɡɐ/] 酒窖&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1031" s="1" t="inlineStr">
@@ -33325,7 +33405,7 @@
       </c>
       <c r="D1031" s="1" t="inlineStr">
         <is>
-          <t>地窖</t>
+          <t>酒窖&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1031" s="1" t="inlineStr">
@@ -33411,7 +33491,7 @@
       </c>
       <c r="B1034" s="1" t="inlineStr">
         <is>
-          <t>[de.koˈɾa(ʁ)] 装饰&lt;动&gt;</t>
+          <t>[/de.koˈɾa(ʁ)/] 背诵&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1034" s="1" t="inlineStr">
@@ -33421,7 +33501,7 @@
       </c>
       <c r="D1034" s="1" t="inlineStr">
         <is>
-          <t>装饰</t>
+          <t>背诵&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1034" s="1" t="inlineStr">
@@ -33603,7 +33683,7 @@
       </c>
       <c r="B1040" s="1" t="inlineStr">
         <is>
-          <t>[ẽ.ka.ʁeˈɡa(ʁ)] 收费&lt;动&gt;</t>
+          <t>[ẽ.ka.ʁeˈɡa(ʁ)] 委托；负责&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1040" s="1" t="inlineStr">
@@ -33613,7 +33693,7 @@
       </c>
       <c r="D1040" s="1" t="inlineStr">
         <is>
-          <t>收费</t>
+          <t>委托；负责</t>
         </is>
       </c>
       <c r="E1040" s="1" t="inlineStr">
@@ -33699,7 +33779,7 @@
       </c>
       <c r="B1043" s="1" t="inlineStr">
         <is>
-          <t>[ˈa.li.ẽj̃] 外星人&lt;名&gt;</t>
+          <t>[ˈa.li.ẽj̃] 外星人；外国人&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1043" s="1" t="inlineStr">
@@ -33709,7 +33789,7 @@
       </c>
       <c r="D1043" s="1" t="inlineStr">
         <is>
-          <t>外星人</t>
+          <t>外星人；外国人</t>
         </is>
       </c>
       <c r="E1043" s="1" t="inlineStr">
@@ -33896,7 +33976,7 @@
       </c>
       <c r="C1049" s="1" t="inlineStr">
         <is>
-          <t>kox.ˈta.ɾãʊ̃</t>
+          <t>/kox.ˈta.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1049" s="1" t="inlineStr">
@@ -34019,7 +34099,7 @@
       </c>
       <c r="B1053" s="1" t="inlineStr">
         <is>
-          <t>[ˈsɔ.ɡɾɐ] 婆婆&lt;名&gt;</t>
+          <t>[/ˈsɔ.ɡɾɐ/] 岳母；婆婆&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1053" s="1" t="inlineStr">
@@ -34029,7 +34109,7 @@
       </c>
       <c r="D1053" s="1" t="inlineStr">
         <is>
-          <t>婆婆</t>
+          <t>岳母；婆婆&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1053" s="1" t="inlineStr">
@@ -34595,7 +34675,7 @@
       </c>
       <c r="B1071" s="1" t="inlineStr">
         <is>
-          <t>[kos.teˈle.tɐ] 砍&lt;名&gt;</t>
+          <t>[kos.teˈle.tɐ] 排骨；肉排&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1071" s="1" t="inlineStr">
@@ -34605,7 +34685,7 @@
       </c>
       <c r="D1071" s="1" t="inlineStr">
         <is>
-          <t>砍</t>
+          <t>排骨；肉排</t>
         </is>
       </c>
       <c r="E1071" s="1" t="inlineStr">
@@ -34755,7 +34835,7 @@
       </c>
       <c r="B1076" s="1" t="inlineStr">
         <is>
-          <t>[biˈʎɐ̃w̃] 十亿&lt;名&gt;</t>
+          <t>[/biˈʎɐ̃w̃/] 万亿（10¹²）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1076" s="1" t="inlineStr">
@@ -34765,7 +34845,7 @@
       </c>
       <c r="D1076" s="1" t="inlineStr">
         <is>
-          <t>十亿</t>
+          <t>万亿（10¹²）</t>
         </is>
       </c>
       <c r="E1076" s="1" t="inlineStr">
@@ -34888,7 +34968,7 @@
       </c>
       <c r="C1080" s="1" t="inlineStr">
         <is>
-          <t>no.tʃi.ˈsi.ə</t>
+          <t>/no.tʃi.ˈsi.ə/</t>
         </is>
       </c>
       <c r="D1080" s="1" t="inlineStr">
@@ -34952,7 +35032,7 @@
       </c>
       <c r="C1082" s="1" t="inlineStr">
         <is>
-          <t>fe.ˈʃa.ɾãʊ̃</t>
+          <t>/fe.ˈʃa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1082" s="1" t="inlineStr">
@@ -35331,7 +35411,7 @@
       </c>
       <c r="B1094" s="1" t="inlineStr">
         <is>
-          <t>[peˈdɾa.dɐ] 高&lt;名&gt;</t>
+          <t>[peˈdɾa.dɐ] 投石；石击&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1094" s="1" t="inlineStr">
@@ -35341,7 +35421,7 @@
       </c>
       <c r="D1094" s="1" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>投石；石击</t>
         </is>
       </c>
       <c r="E1094" s="1" t="inlineStr">
@@ -35427,13 +35507,17 @@
       </c>
       <c r="B1097" s="1" t="inlineStr">
         <is>
-          <t>为&lt;动&gt;</t>
-        </is>
-      </c>
-      <c r="C1097" s="1" t="inlineStr"/>
+          <t>将是；将去&lt;动&gt;</t>
+        </is>
+      </c>
+      <c r="C1097" s="1" t="inlineStr">
+        <is>
+          <t>/foʁ/</t>
+        </is>
+      </c>
       <c r="D1097" s="1" t="inlineStr">
         <is>
-          <t>为</t>
+          <t>将是；将去</t>
         </is>
       </c>
       <c r="E1097" s="1" t="inlineStr">
@@ -35743,7 +35827,7 @@
       </c>
       <c r="B1107" s="1" t="inlineStr">
         <is>
-          <t>[piˈɐ̃w̃] 典当&lt;名&gt;</t>
+          <t>[piˈɐ̃w̃] 兵；卒；小工&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1107" s="1" t="inlineStr">
@@ -35753,7 +35837,7 @@
       </c>
       <c r="D1107" s="1" t="inlineStr">
         <is>
-          <t>典当</t>
+          <t>兵；卒；小工</t>
         </is>
       </c>
       <c r="E1107" s="1" t="inlineStr">
@@ -35775,7 +35859,7 @@
       </c>
       <c r="B1108" s="1" t="inlineStr">
         <is>
-          <t>[baˈɾa.ʎu] 甲板&lt;名&gt;</t>
+          <t>[baˈɾa.ʎu] 纸牌；扑克牌&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1108" s="1" t="inlineStr">
@@ -35785,7 +35869,7 @@
       </c>
       <c r="D1108" s="1" t="inlineStr">
         <is>
-          <t>甲板</t>
+          <t>纸牌；扑克牌</t>
         </is>
       </c>
       <c r="E1108" s="1" t="inlineStr">
@@ -35967,7 +36051,7 @@
       </c>
       <c r="B1114" s="1" t="inlineStr">
         <is>
-          <t>[ˈdɔ] 抱歉&lt;名&gt;</t>
+          <t>[ˈdɔ] 哆；怜悯&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1114" s="1" t="inlineStr">
@@ -35977,7 +36061,7 @@
       </c>
       <c r="D1114" s="1" t="inlineStr">
         <is>
-          <t>抱歉</t>
+          <t>哆；怜悯</t>
         </is>
       </c>
       <c r="E1114" s="1" t="inlineStr">
@@ -35999,7 +36083,7 @@
       </c>
       <c r="B1115" s="1" t="inlineStr">
         <is>
-          <t>[ʁazˈɡa(ʁ)] 眼泪&lt;动&gt;</t>
+          <t>[ʁazˈɡa(ʁ)] 撕；撕裂&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1115" s="1" t="inlineStr">
@@ -36009,7 +36093,7 @@
       </c>
       <c r="D1115" s="1" t="inlineStr">
         <is>
-          <t>眼泪</t>
+          <t>撕；撕裂</t>
         </is>
       </c>
       <c r="E1115" s="1" t="inlineStr">
@@ -36164,7 +36248,7 @@
       </c>
       <c r="C1120" s="1" t="inlineStr">
         <is>
-          <t>kɾe.ˈse.ɾãʊ̃</t>
+          <t>/kɾe.ˈse.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1120" s="1" t="inlineStr">
@@ -36191,7 +36275,7 @@
       </c>
       <c r="B1121" s="1" t="inlineStr">
         <is>
-          <t>[ẽ.ɡaˈta(ʁ)] 参与&lt;动&gt;</t>
+          <t>[/ẽ.ɡaˈta(ʁ)/] 挂挡；连接；挂钩&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1121" s="1" t="inlineStr">
@@ -36201,7 +36285,7 @@
       </c>
       <c r="D1121" s="1" t="inlineStr">
         <is>
-          <t>参与</t>
+          <t>挂挡；连接；挂钩&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1121" s="1" t="inlineStr">
@@ -36575,7 +36659,7 @@
       </c>
       <c r="B1133" s="1" t="inlineStr">
         <is>
-          <t>[ˈmej] 梅&lt;名&gt;</t>
+          <t>[/ˈmej/] 个体微企业主（Microempreendedor Individual 的缩写）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1133" s="1" t="inlineStr">
@@ -36585,7 +36669,7 @@
       </c>
       <c r="D1133" s="1" t="inlineStr">
         <is>
-          <t>梅</t>
+          <t>个体微企业主（Microempreendedor Individual 的缩写）</t>
         </is>
       </c>
       <c r="E1133" s="1" t="inlineStr">
@@ -37567,7 +37651,7 @@
       </c>
       <c r="B1164" s="1" t="inlineStr">
         <is>
-          <t>[a.leʁˈta(ʁ)] 警报&lt;动&gt;</t>
+          <t>[a.leʁˈta(ʁ)] 警告；使警觉&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1164" s="1" t="inlineStr">
@@ -37577,7 +37661,7 @@
       </c>
       <c r="D1164" s="1" t="inlineStr">
         <is>
-          <t>警报</t>
+          <t>警告；使警觉</t>
         </is>
       </c>
       <c r="E1164" s="1" t="inlineStr">
@@ -37668,7 +37752,7 @@
       </c>
       <c r="C1167" s="1" t="inlineStr">
         <is>
-          <t>so.ˈfɾe.ɾãʊ̃</t>
+          <t>/so.ˈfɾe.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1167" s="1" t="inlineStr">
@@ -38020,7 +38104,7 @@
       </c>
       <c r="C1178" s="1" t="inlineStr">
         <is>
-          <t>ẽ.si.ˈna.ɾãʊ̃</t>
+          <t>/ẽ.si.ˈna.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1178" s="1" t="inlineStr">
@@ -38879,7 +38963,7 @@
       </c>
       <c r="B1205" s="1" t="inlineStr">
         <is>
-          <t>[ˈʁaw̃d͡ʒi] 圆形&lt;名&gt;</t>
+          <t>[/ˈʁaw̃d͡ʒi/] redondo&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1205" s="1" t="inlineStr">
@@ -38889,7 +38973,7 @@
       </c>
       <c r="D1205" s="1" t="inlineStr">
         <is>
-          <t>圆形</t>
+          <t>redondo&lt;形&gt;</t>
         </is>
       </c>
       <c r="E1205" s="1" t="inlineStr">
@@ -38911,7 +38995,7 @@
       </c>
       <c r="B1206" s="1" t="inlineStr">
         <is>
-          <t>[ˈpĩ.tu] 迪克&lt;名&gt;</t>
+          <t>[ˈpĩ.tu] 小鸡；雏鸡&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1206" s="1" t="inlineStr">
@@ -38921,7 +39005,7 @@
       </c>
       <c r="D1206" s="1" t="inlineStr">
         <is>
-          <t>迪克</t>
+          <t>小鸡；雏鸡</t>
         </is>
       </c>
       <c r="E1206" s="1" t="inlineStr">
@@ -39394,7 +39478,11 @@
           <t>佛法&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1221" s="1" t="inlineStr"/>
+      <c r="C1221" s="1" t="inlineStr">
+        <is>
+          <t>/ˈdaʁ.mɐ/</t>
+        </is>
+      </c>
       <c r="D1221" s="1" t="inlineStr">
         <is>
           <t>佛法</t>
@@ -40507,7 +40595,7 @@
       </c>
       <c r="B1256" s="1" t="inlineStr">
         <is>
-          <t>[deˈʁɐ̃.mi] 泄漏&lt;名&gt;</t>
+          <t>[/deˈʁɐ̃.mi/] 溢出；中风&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1256" s="1" t="inlineStr">
@@ -40517,7 +40605,7 @@
       </c>
       <c r="D1256" s="1" t="inlineStr">
         <is>
-          <t>泄漏</t>
+          <t>溢出；中风&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1256" s="1" t="inlineStr">
@@ -40768,7 +40856,7 @@
       </c>
       <c r="C1264" s="1" t="inlineStr">
         <is>
-          <t>me.ˈte.ɾãʊ̃</t>
+          <t>/me.ˈte.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1264" s="1" t="inlineStr">
@@ -40923,7 +41011,7 @@
       </c>
       <c r="B1269" s="1" t="inlineStr">
         <is>
-          <t>[ĩ.flu.ẽ.siˈa(ʁ)] 影响力&lt;动&gt;</t>
+          <t>[ĩ.flu.ẽ.siˈa(ʁ)] 影响&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1269" s="1" t="inlineStr">
@@ -40933,7 +41021,7 @@
       </c>
       <c r="D1269" s="1" t="inlineStr">
         <is>
-          <t>影响力</t>
+          <t>影响</t>
         </is>
       </c>
       <c r="E1269" s="1" t="inlineStr">
@@ -41152,7 +41240,7 @@
       </c>
       <c r="C1276" s="1" t="inlineStr">
         <is>
-          <t>a.tu.a.li.za.ˈsãʊ̃</t>
+          <t>/a.tu.a.li.za.ˈsãʊ̃/</t>
         </is>
       </c>
       <c r="D1276" s="1" t="inlineStr">
@@ -41694,7 +41782,11 @@
           <t>气&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1293" s="1" t="inlineStr"/>
+      <c r="C1293" s="1" t="inlineStr">
+        <is>
+          <t>/kˈi/</t>
+        </is>
+      </c>
       <c r="D1293" s="1" t="inlineStr">
         <is>
           <t>气</t>
@@ -41820,7 +41912,7 @@
       </c>
       <c r="C1297" s="1" t="inlineStr">
         <is>
-          <t>[ˌalaˈbɐma]</t>
+          <t>/ˌalaˈbɐma/</t>
         </is>
       </c>
       <c r="D1297" s="1" t="inlineStr">
@@ -42044,7 +42136,7 @@
       </c>
       <c r="C1304" s="1" t="inlineStr">
         <is>
-          <t>a.kõ.se.ʎa.ˈmẽ.tʊ</t>
+          <t>/a.kõ.se.ʎa.ˈmẽ.tʊ/</t>
         </is>
       </c>
       <c r="D1304" s="1" t="inlineStr">
@@ -42300,7 +42392,7 @@
       </c>
       <c r="C1312" s="1" t="inlineStr">
         <is>
-          <t>ˈɛ.ʃʊ</t>
+          <t>/ˈɛ.ʃʊ/</t>
         </is>
       </c>
       <c r="D1312" s="1" t="inlineStr">
@@ -42396,7 +42488,7 @@
       </c>
       <c r="C1315" s="1" t="inlineStr">
         <is>
-          <t>a.pɾẽ.ˈde.ɾãʊ̃</t>
+          <t>/a.pɾẽ.ˈde.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1315" s="1" t="inlineStr">
@@ -42551,17 +42643,17 @@
       </c>
       <c r="B1320" s="1" t="inlineStr">
         <is>
-          <t>[pɾĩ.si.ˈpi.ʊ] 原则&lt;名&gt;</t>
+          <t>[pɾĩ.si.ˈpi.ʊ] （应为princípio）原则&lt;名&gt;；principio本身是principiar的第一人称单数现在时“我开始”&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1320" s="1" t="inlineStr">
         <is>
-          <t>pɾĩ.si.ˈpi.ʊ</t>
+          <t>/pɾĩ.si.ˈpi.ʊ/</t>
         </is>
       </c>
       <c r="D1320" s="1" t="inlineStr">
         <is>
-          <t>原则</t>
+          <t>（应为princípio）原则&lt;名&gt;；principio本身是principiar的第一人称单数现在时“我开始”</t>
         </is>
       </c>
       <c r="E1320" s="1" t="inlineStr">
@@ -42935,7 +43027,7 @@
       </c>
       <c r="B1332" s="1" t="inlineStr">
         <is>
-          <t>[a.boʁˈda(ʁ)] 方法&lt;动&gt;</t>
+          <t>[a.boʁˈda(ʁ)] 接近；着手处理；登船&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1332" s="1" t="inlineStr">
@@ -42945,7 +43037,7 @@
       </c>
       <c r="D1332" s="1" t="inlineStr">
         <is>
-          <t>方法</t>
+          <t>接近；着手处理；登船</t>
         </is>
       </c>
       <c r="E1332" s="1" t="inlineStr">
@@ -43036,7 +43128,7 @@
       </c>
       <c r="C1335" s="1" t="inlineStr">
         <is>
-          <t>es.kɾe.ˈve.ɾãʊ̃</t>
+          <t>/es.kɾe.ˈve.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1335" s="1" t="inlineStr">
@@ -43223,7 +43315,7 @@
       </c>
       <c r="B1341" s="1" t="inlineStr">
         <is>
-          <t>[ba.lɐ̃ˈsa(ʁ)] 秋千&lt;动&gt;</t>
+          <t>[ba.lɐ̃ˈsa(ʁ)] 摇摆；摇晃&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1341" s="1" t="inlineStr">
@@ -43233,7 +43325,7 @@
       </c>
       <c r="D1341" s="1" t="inlineStr">
         <is>
-          <t>秋千</t>
+          <t>摇摆；摇晃</t>
         </is>
       </c>
       <c r="E1341" s="1" t="inlineStr">
@@ -43287,7 +43379,7 @@
       </c>
       <c r="B1343" s="1" t="inlineStr">
         <is>
-          <t>[(i)ʒ.vɐˈzjaɾ] 空的&lt;动&gt;</t>
+          <t>[(i)ʒ.vɐˈzjaɾ] 倒空；排空&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1343" s="1" t="inlineStr">
@@ -43297,7 +43389,7 @@
       </c>
       <c r="D1343" s="1" t="inlineStr">
         <is>
-          <t>空的</t>
+          <t>倒空；排空</t>
         </is>
       </c>
       <c r="E1343" s="1" t="inlineStr">
@@ -43354,7 +43446,11 @@
           <t>扫描仪&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1345" s="1" t="inlineStr"/>
+      <c r="C1345" s="1" t="inlineStr">
+        <is>
+          <t>/isˈkɐ̃.neʁ/</t>
+        </is>
+      </c>
       <c r="D1345" s="1" t="inlineStr">
         <is>
           <t>扫描仪</t>
@@ -43859,7 +43955,7 @@
       </c>
       <c r="B1361" s="1" t="inlineStr">
         <is>
-          <t>[moˈʎa(ʁ)] 湿的&lt;动&gt;</t>
+          <t>[moˈʎa(ʁ)] 弄湿&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1361" s="1" t="inlineStr">
@@ -43869,7 +43965,7 @@
       </c>
       <c r="D1361" s="1" t="inlineStr">
         <is>
-          <t>湿的</t>
+          <t>弄湿</t>
         </is>
       </c>
       <c r="E1361" s="1" t="inlineStr">
@@ -44056,7 +44152,7 @@
       </c>
       <c r="C1367" s="1" t="inlineStr">
         <is>
-          <t>a.kɾe.dʒi.ˈta.ɾãʊ̃</t>
+          <t>/a.kɾe.dʒi.ˈta.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1367" s="1" t="inlineStr">
@@ -44531,7 +44627,7 @@
       </c>
       <c r="B1382" s="1" t="inlineStr">
         <is>
-          <t>[no.meˈa(ʁ)] 姓名&lt;动&gt;</t>
+          <t>[no.meˈa(ʁ)] 命名；任命&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1382" s="1" t="inlineStr">
@@ -44541,7 +44637,7 @@
       </c>
       <c r="D1382" s="1" t="inlineStr">
         <is>
-          <t>姓名</t>
+          <t>命名；任命</t>
         </is>
       </c>
       <c r="E1382" s="1" t="inlineStr">
@@ -44563,7 +44659,7 @@
       </c>
       <c r="B1383" s="1" t="inlineStr">
         <is>
-          <t>[ma.teʁ.niˈda.d͡ʒi] 产妇&lt;名&gt;</t>
+          <t>[ma.teʁ.niˈda.d͡ʒi] 母性；母亲身份；产科医院&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1383" s="1" t="inlineStr">
@@ -44573,7 +44669,7 @@
       </c>
       <c r="D1383" s="1" t="inlineStr">
         <is>
-          <t>产妇</t>
+          <t>母性；母亲身份；产科医院</t>
         </is>
       </c>
       <c r="E1383" s="1" t="inlineStr">
@@ -44595,7 +44691,7 @@
       </c>
       <c r="B1384" s="1" t="inlineStr">
         <is>
-          <t>[ˈtõ.nɐ] 表面&lt;名&gt;</t>
+          <t>[ˈtõ.nɐ] 水面；表层&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1384" s="1" t="inlineStr">
@@ -44605,7 +44701,7 @@
       </c>
       <c r="D1384" s="1" t="inlineStr">
         <is>
-          <t>表面</t>
+          <t>水面；表层</t>
         </is>
       </c>
       <c r="E1384" s="1" t="inlineStr">
@@ -45171,7 +45267,7 @@
       </c>
       <c r="B1402" s="1" t="inlineStr">
         <is>
-          <t>[ẽ.ku.ʁaˈla(ʁ)] 角落&lt;动&gt;</t>
+          <t>[ẽ.ku.ʁaˈla(ʁ)] 围困；逼入绝境&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1402" s="1" t="inlineStr">
@@ -45181,7 +45277,7 @@
       </c>
       <c r="D1402" s="1" t="inlineStr">
         <is>
-          <t>角落</t>
+          <t>围困；逼入绝境</t>
         </is>
       </c>
       <c r="E1402" s="1" t="inlineStr">
@@ -45299,13 +45395,17 @@
       </c>
       <c r="B1406" s="1" t="inlineStr">
         <is>
-          <t>砖&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C1406" s="1" t="inlineStr"/>
+          <t>[ˈbɾik] 砖；砖块&lt;名&gt;</t>
+        </is>
+      </c>
+      <c r="C1406" s="1" t="inlineStr">
+        <is>
+          <t>/bɾik/</t>
+        </is>
+      </c>
       <c r="D1406" s="1" t="inlineStr">
         <is>
-          <t>砖</t>
+          <t>砖；砖块</t>
         </is>
       </c>
       <c r="E1406" s="1" t="inlineStr">
@@ -45396,7 +45496,7 @@
       </c>
       <c r="C1409" s="1" t="inlineStr">
         <is>
-          <t>es.pi.ˈɾi.tʊ</t>
+          <t>/es.pi.ˈɾi.tʊ/</t>
         </is>
       </c>
       <c r="D1409" s="1" t="inlineStr">
@@ -45583,13 +45683,17 @@
       </c>
       <c r="B1415" s="1" t="inlineStr">
         <is>
-          <t>狂喜&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C1415" s="1" t="inlineStr"/>
+          <t>[[ɛksˈtazi]] 摇头丸&lt;名&gt;（MDMA；狂喜应为 êxtase）&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C1415" s="1" t="inlineStr">
+        <is>
+          <t>/ɛk.stɐˈzi/</t>
+        </is>
+      </c>
       <c r="D1415" s="1" t="inlineStr">
         <is>
-          <t>狂喜</t>
+          <t>摇头丸&lt;名&gt;（MDMA；狂喜应为 êxtase）</t>
         </is>
       </c>
       <c r="E1415" s="1" t="inlineStr">
@@ -45835,7 +45939,7 @@
       </c>
       <c r="B1423" s="1" t="inlineStr">
         <is>
-          <t>[vaˈɡɐ̃w̃] 马车&lt;名&gt;</t>
+          <t>[vaˈɡɐ̃w̃] 车厢；货车&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1423" s="1" t="inlineStr">
@@ -45845,7 +45949,7 @@
       </c>
       <c r="D1423" s="1" t="inlineStr">
         <is>
-          <t>马车</t>
+          <t>车厢；货车</t>
         </is>
       </c>
       <c r="E1423" s="1" t="inlineStr">
@@ -46256,7 +46360,7 @@
       </c>
       <c r="C1436" s="1" t="inlineStr">
         <is>
-          <t>a.fe.ˈta.dʊ</t>
+          <t>/a.fe.ˈta.dʊ/</t>
         </is>
       </c>
       <c r="D1436" s="1" t="inlineStr">
@@ -46315,7 +46419,7 @@
       </c>
       <c r="B1438" s="1" t="inlineStr">
         <is>
-          <t>[ko.ɾeˈɐ̃.nu] 韩语&lt;名&gt;</t>
+          <t>[/ko.ɾeˈɐ̃.nu/] 韩国的&lt;形&gt;；韩国人&lt;名&gt;；韩语&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1438" s="1" t="inlineStr">
@@ -46325,7 +46429,7 @@
       </c>
       <c r="D1438" s="1" t="inlineStr">
         <is>
-          <t>韩语</t>
+          <t>韩国的&lt;形&gt;；韩国人&lt;名&gt;；韩语&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1438" s="1" t="inlineStr">
@@ -46544,7 +46648,7 @@
       </c>
       <c r="C1445" s="1" t="inlineStr">
         <is>
-          <t>tɾa.ʒe.ˈtɔ.ɾi.ə</t>
+          <t>/tɾa.ʒe.ˈtɔ.ɾi.ə/</t>
         </is>
       </c>
       <c r="D1445" s="1" t="inlineStr">
@@ -46672,7 +46776,7 @@
       </c>
       <c r="C1449" s="1" t="inlineStr">
         <is>
-          <t>ẽ.ʒu.ˈa.dʊ</t>
+          <t>/ẽ.ʒu.ˈa.dʊ/</t>
         </is>
       </c>
       <c r="D1449" s="1" t="inlineStr">
@@ -46795,7 +46899,7 @@
       </c>
       <c r="B1453" s="1" t="inlineStr">
         <is>
-          <t>[kõ.vuwˈsɐ̃w̃] 癫痫发作&lt;名&gt;</t>
+          <t>[/kõ.vuwˈsɐ̃w̃/] 抽搐；痉挛&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1453" s="1" t="inlineStr">
@@ -46805,7 +46909,7 @@
       </c>
       <c r="D1453" s="1" t="inlineStr">
         <is>
-          <t>癫痫发作</t>
+          <t>抽搐；痉挛&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1453" s="1" t="inlineStr">
@@ -47083,7 +47187,7 @@
       </c>
       <c r="B1462" s="1" t="inlineStr">
         <is>
-          <t>[meʁˈse] 怜悯&lt;名&gt;</t>
+          <t>[/meʁˈse/] 恩惠；由于（mercê de）&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1462" s="1" t="inlineStr">
@@ -47093,7 +47197,7 @@
       </c>
       <c r="D1462" s="1" t="inlineStr">
         <is>
-          <t>怜悯</t>
+          <t>恩惠；由于（mercê de）&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1462" s="1" t="inlineStr">
@@ -47115,7 +47219,7 @@
       </c>
       <c r="B1463" s="1" t="inlineStr">
         <is>
-          <t>[ˈtɛ.tɐ] 山雀&lt;名&gt;</t>
+          <t>[ˈtɛ.tɐ] 乳头；乳房&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1463" s="1" t="inlineStr">
@@ -47125,7 +47229,7 @@
       </c>
       <c r="D1463" s="1" t="inlineStr">
         <is>
-          <t>山雀</t>
+          <t>乳头；乳房</t>
         </is>
       </c>
       <c r="E1463" s="1" t="inlineStr">
@@ -47147,7 +47251,7 @@
       </c>
       <c r="B1464" s="1" t="inlineStr">
         <is>
-          <t>[ˈkas.tɾu] 卡斯特罗&lt;名&gt;</t>
+          <t>[ˈkas.tɾu] 史前山寨；设防村落&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1464" s="1" t="inlineStr">
@@ -47157,7 +47261,7 @@
       </c>
       <c r="D1464" s="1" t="inlineStr">
         <is>
-          <t>卡斯特罗</t>
+          <t>史前山寨；设防村落</t>
         </is>
       </c>
       <c r="E1464" s="1" t="inlineStr">
@@ -47371,7 +47475,7 @@
       </c>
       <c r="B1471" s="1" t="inlineStr">
         <is>
-          <t>[ˈʃa.ʁu] 联合&lt;名&gt;</t>
+          <t>[ˈʃa.ʁu] 牛车；西班牙人（贬称）&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1471" s="1" t="inlineStr">
@@ -47381,7 +47485,7 @@
       </c>
       <c r="D1471" s="1" t="inlineStr">
         <is>
-          <t>联合</t>
+          <t>牛车；西班牙人（贬称）</t>
         </is>
       </c>
       <c r="E1471" s="1" t="inlineStr">
@@ -47851,7 +47955,7 @@
       </c>
       <c r="B1486" s="1" t="inlineStr">
         <is>
-          <t>[ka.beˈdaw] 皮革&lt;名&gt;</t>
+          <t>[/ka.beˈdaw/] 鞋类；储备；财富&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1486" s="1" t="inlineStr">
@@ -47861,7 +47965,7 @@
       </c>
       <c r="D1486" s="1" t="inlineStr">
         <is>
-          <t>皮革</t>
+          <t>鞋类；储备；财富&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1486" s="1" t="inlineStr">
@@ -47886,7 +47990,11 @@
           <t>自尊&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1487" s="1" t="inlineStr"/>
+      <c r="C1487" s="1" t="inlineStr">
+        <is>
+          <t>/aw.tu.esˈtʃi.mɐ/</t>
+        </is>
+      </c>
       <c r="D1487" s="1" t="inlineStr">
         <is>
           <t>自尊</t>
@@ -48263,7 +48371,7 @@
       </c>
       <c r="B1499" s="1" t="inlineStr">
         <is>
-          <t>[baˈu] 胸部&lt;名&gt;</t>
+          <t>[baˈu] 箱子；衣箱；（汽车）后备箱&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1499" s="1" t="inlineStr">
@@ -48273,7 +48381,7 @@
       </c>
       <c r="D1499" s="1" t="inlineStr">
         <is>
-          <t>胸部</t>
+          <t>箱子；衣箱；（汽车）后备箱</t>
         </is>
       </c>
       <c r="E1499" s="1" t="inlineStr">
@@ -48295,7 +48403,7 @@
       </c>
       <c r="B1500" s="1" t="inlineStr">
         <is>
-          <t>[neˈva(ʁ)] 雪&lt;动&gt;</t>
+          <t>[neˈva(ʁ)] 下雪&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1500" s="1" t="inlineStr">
@@ -48305,7 +48413,7 @@
       </c>
       <c r="D1500" s="1" t="inlineStr">
         <is>
-          <t>雪</t>
+          <t>下雪</t>
         </is>
       </c>
       <c r="E1500" s="1" t="inlineStr">
@@ -48327,7 +48435,7 @@
       </c>
       <c r="B1501" s="1" t="inlineStr">
         <is>
-          <t>[aw.kaˈtɛj.ɐ] 包&lt;名&gt;</t>
+          <t>[/aw.kaˈtɛj.ɐ/] 狼群&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1501" s="1" t="inlineStr">
@@ -48337,7 +48445,7 @@
       </c>
       <c r="D1501" s="1" t="inlineStr">
         <is>
-          <t>包</t>
+          <t>狼群&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1501" s="1" t="inlineStr">
@@ -48455,7 +48563,7 @@
       </c>
       <c r="B1505" s="1" t="inlineStr">
         <is>
-          <t>[de.ʁaˈma(ʁ)] 泄漏&lt;动&gt;</t>
+          <t>[/de.ʁaˈma(ʁ)/] 洒,倒出&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1505" s="1" t="inlineStr">
@@ -48465,7 +48573,7 @@
       </c>
       <c r="D1505" s="1" t="inlineStr">
         <is>
-          <t>泄漏</t>
+          <t>洒,倒出&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1505" s="1" t="inlineStr">
@@ -48647,17 +48755,17 @@
       </c>
       <c r="B1511" s="1" t="inlineStr">
         <is>
-          <t>[ka] 加州&lt;名&gt;</t>
+          <t>[ka] 这里；此处&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1511" s="1" t="inlineStr">
         <is>
-          <t>ka</t>
+          <t>/ka/</t>
         </is>
       </c>
       <c r="D1511" s="1" t="inlineStr">
         <is>
-          <t>加州</t>
+          <t>这里；此处</t>
         </is>
       </c>
       <c r="E1511" s="1" t="inlineStr">
@@ -48775,17 +48883,17 @@
       </c>
       <c r="B1515" s="1" t="inlineStr">
         <is>
-          <t>[ko.me.ˈte.ɾãʊ̃] 致力于&lt;动&gt;</t>
+          <t>[ko.me.ˈte.ɾãʊ̃] 犯（罪、错误）&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1515" s="1" t="inlineStr">
         <is>
-          <t>ko.me.ˈte.ɾãʊ̃</t>
+          <t>/ko.me.ˈte.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1515" s="1" t="inlineStr">
         <is>
-          <t>致力于</t>
+          <t>犯（罪、错误）</t>
         </is>
       </c>
       <c r="E1515" s="1" t="inlineStr">
@@ -48812,7 +48920,7 @@
       </c>
       <c r="C1516" s="1" t="inlineStr">
         <is>
-          <t>ba.ˈte.ɾãʊ̃</t>
+          <t>/ba.ˈte.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1516" s="1" t="inlineStr">
@@ -48871,7 +48979,7 @@
       </c>
       <c r="B1518" s="1" t="inlineStr">
         <is>
-          <t>[poˈla.ku] 波兰语&lt;名&gt;</t>
+          <t>[poˈla.ku] 波兰人；波兰语&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1518" s="1" t="inlineStr">
@@ -48881,7 +48989,7 @@
       </c>
       <c r="D1518" s="1" t="inlineStr">
         <is>
-          <t>波兰语</t>
+          <t>波兰人；波兰语</t>
         </is>
       </c>
       <c r="E1518" s="1" t="inlineStr">
@@ -48967,7 +49075,7 @@
       </c>
       <c r="B1521" s="1" t="inlineStr">
         <is>
-          <t>[ba.t͡ʃiˈmẽ.tu] 击败&lt;名&gt;</t>
+          <t>[ba.t͡ʃiˈmẽ.tu] 跳动；搏动；拍打&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1521" s="1" t="inlineStr">
@@ -48977,7 +49085,7 @@
       </c>
       <c r="D1521" s="1" t="inlineStr">
         <is>
-          <t>击败</t>
+          <t>跳动；搏动；拍打</t>
         </is>
       </c>
       <c r="E1521" s="1" t="inlineStr">
@@ -49287,7 +49395,7 @@
       </c>
       <c r="B1531" s="1" t="inlineStr">
         <is>
-          <t>[meˈdɾi.kɐs] 梅德里卡斯&lt;名&gt;</t>
+          <t>[meˈdɾi.kɐs] 装病；无病呻吟&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1531" s="1" t="inlineStr">
@@ -49297,7 +49405,7 @@
       </c>
       <c r="D1531" s="1" t="inlineStr">
         <is>
-          <t>梅德里卡斯</t>
+          <t>装病；无病呻吟</t>
         </is>
       </c>
       <c r="E1531" s="1" t="inlineStr">
@@ -49351,7 +49459,7 @@
       </c>
       <c r="B1533" s="1" t="inlineStr">
         <is>
-          <t>[ˈpɾo.ɐ] 弓&lt;名&gt;</t>
+          <t>[ˈpɾo.ɐ] 船头；船首&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1533" s="1" t="inlineStr">
@@ -49361,7 +49469,7 @@
       </c>
       <c r="D1533" s="1" t="inlineStr">
         <is>
-          <t>弓</t>
+          <t>船头；船首</t>
         </is>
       </c>
       <c r="E1533" s="1" t="inlineStr">
@@ -49388,7 +49496,7 @@
       </c>
       <c r="C1534" s="1" t="inlineStr">
         <is>
-          <t>ĩ.va.ˈdʒi.ɾãʊ̃</t>
+          <t>/ĩ.va.ˈdʒi.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1534" s="1" t="inlineStr">
@@ -49511,7 +49619,7 @@
       </c>
       <c r="B1538" s="1" t="inlineStr">
         <is>
-          <t>[d͡ʒisˈpẽ.sɐ] 解雇&lt;名&gt;</t>
+          <t>[/d͡ʒisˈpẽ.sɐ/] 免除；食品储藏室&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1538" s="1" t="inlineStr">
@@ -49521,7 +49629,7 @@
       </c>
       <c r="D1538" s="1" t="inlineStr">
         <is>
-          <t>解雇</t>
+          <t>免除；食品储藏室</t>
         </is>
       </c>
       <c r="E1538" s="1" t="inlineStr">
@@ -49735,7 +49843,7 @@
       </c>
       <c r="B1545" s="1" t="inlineStr">
         <is>
-          <t>[no.me.aˈsɐ̃w̃] 预约&lt;名&gt;</t>
+          <t>[no.me.aˈsɐ̃w̃] 任命；提名；命名&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1545" s="1" t="inlineStr">
@@ -49745,7 +49853,7 @@
       </c>
       <c r="D1545" s="1" t="inlineStr">
         <is>
-          <t>预约</t>
+          <t>任命；提名；命名</t>
         </is>
       </c>
       <c r="E1545" s="1" t="inlineStr">
@@ -49831,7 +49939,7 @@
       </c>
       <c r="B1548" s="1" t="inlineStr">
         <is>
-          <t>[ˈpɾaj.mi] 素数&lt;名&gt;</t>
+          <t>[/ˈpɾaj.mi/] 最初的；首要的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1548" s="1" t="inlineStr">
@@ -49841,7 +49949,7 @@
       </c>
       <c r="D1548" s="1" t="inlineStr">
         <is>
-          <t>素数</t>
+          <t>最初的；首要的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E1548" s="1" t="inlineStr">
@@ -49895,7 +50003,7 @@
       </c>
       <c r="B1550" s="1" t="inlineStr">
         <is>
-          <t>[a.seˈna(ʁ)] 波&lt;动&gt;</t>
+          <t>[a.seˈna(ʁ)] 挥手；招手；示意&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1550" s="1" t="inlineStr">
@@ -49905,7 +50013,7 @@
       </c>
       <c r="D1550" s="1" t="inlineStr">
         <is>
-          <t>波</t>
+          <t>挥手；招手；示意</t>
         </is>
       </c>
       <c r="E1550" s="1" t="inlineStr">
@@ -49927,17 +50035,17 @@
       </c>
       <c r="B1551" s="1" t="inlineStr">
         <is>
-          <t>[vuw.ˈkã.nʊ] 火神&lt;名&gt;</t>
+          <t>[vuw.ˈkã.nʊ] 火山&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1551" s="1" t="inlineStr">
         <is>
-          <t>vuw.ˈkã.nʊ</t>
+          <t>/vuw.ˈkã.nʊ/</t>
         </is>
       </c>
       <c r="D1551" s="1" t="inlineStr">
         <is>
-          <t>火神</t>
+          <t>火山</t>
         </is>
       </c>
       <c r="E1551" s="1" t="inlineStr">
@@ -50055,17 +50163,17 @@
       </c>
       <c r="B1555" s="1" t="inlineStr">
         <is>
-          <t>[sẽ.ˈtʃi.ɾãʊ̃] 毛毡&lt;动&gt;</t>
+          <t>[sẽ.ˈtʃi.ɾãʊ̃] 感觉到；感到&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1555" s="1" t="inlineStr">
         <is>
-          <t>sẽ.ˈtʃi.ɾãʊ̃</t>
+          <t>/sẽ.ˈtʃi.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1555" s="1" t="inlineStr">
         <is>
-          <t>毛毡</t>
+          <t>感觉到；感到</t>
         </is>
       </c>
       <c r="E1555" s="1" t="inlineStr">
@@ -50407,7 +50515,7 @@
       </c>
       <c r="B1566" s="1" t="inlineStr">
         <is>
-          <t>[ʁe.fejˈtɔ.ɾju] 自助餐厅&lt;名&gt;</t>
+          <t>[/ʁe.fejˈtɔ.ɾju/] 食堂；餐厅&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1566" s="1" t="inlineStr">
@@ -50417,7 +50525,7 @@
       </c>
       <c r="D1566" s="1" t="inlineStr">
         <is>
-          <t>自助餐厅</t>
+          <t>食堂；餐厅&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1566" s="1" t="inlineStr">
@@ -50567,7 +50675,7 @@
       </c>
       <c r="B1571" s="1" t="inlineStr">
         <is>
-          <t>[ˈnɛ.t͡ʃi] 网&lt;名&gt;</t>
+          <t>[/ˈnɛ.t͡ʃi/] 网络&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1571" s="1" t="inlineStr">
@@ -50577,7 +50685,7 @@
       </c>
       <c r="D1571" s="1" t="inlineStr">
         <is>
-          <t>网</t>
+          <t>网络&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1571" s="1" t="inlineStr">
@@ -50636,7 +50744,7 @@
       </c>
       <c r="C1573" s="1" t="inlineStr">
         <is>
-          <t>e.fe.tu.ˈax</t>
+          <t>/e.fe.tu.ˈax/</t>
         </is>
       </c>
       <c r="D1573" s="1" t="inlineStr">
@@ -50663,7 +50771,7 @@
       </c>
       <c r="B1574" s="1" t="inlineStr">
         <is>
-          <t>[ẽˈpa.t͡ʃi] 画&lt;名&gt;</t>
+          <t>[ẽˈpa.t͡ʃi] 平局；不分胜负&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1574" s="1" t="inlineStr">
@@ -50673,7 +50781,7 @@
       </c>
       <c r="D1574" s="1" t="inlineStr">
         <is>
-          <t>画</t>
+          <t>平局；不分胜负</t>
         </is>
       </c>
       <c r="E1574" s="1" t="inlineStr">
@@ -50919,7 +51027,7 @@
       </c>
       <c r="B1582" s="1" t="inlineStr">
         <is>
-          <t>[ˈɐ̃.ni.mu] 欢呼&lt;名&gt;</t>
+          <t>[ˈɐ̃.ni.mu] 精神；情绪；勇气；士气&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1582" s="1" t="inlineStr">
@@ -50929,7 +51037,7 @@
       </c>
       <c r="D1582" s="1" t="inlineStr">
         <is>
-          <t>欢呼</t>
+          <t>精神；情绪；勇气；士气</t>
         </is>
       </c>
       <c r="E1582" s="1" t="inlineStr">
@@ -51084,7 +51192,7 @@
       </c>
       <c r="C1587" s="1" t="inlineStr">
         <is>
-          <t>suɣ.ˈʒi.ɾãʊ̃</t>
+          <t>/suɣ.ˈʒi.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1587" s="1" t="inlineStr">
@@ -51527,7 +51635,7 @@
       </c>
       <c r="B1601" s="1" t="inlineStr">
         <is>
-          <t>[ɡaˈla(ʁ)] 伽勒尔&lt;动&gt;</t>
+          <t>[/ɡaˈla(ʁ)/] 饰以花环；授予桂冠&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1601" s="1" t="inlineStr">
@@ -51537,7 +51645,7 @@
       </c>
       <c r="D1601" s="1" t="inlineStr">
         <is>
-          <t>伽勒尔</t>
+          <t>饰以花环；授予桂冠</t>
         </is>
       </c>
       <c r="E1601" s="1" t="inlineStr">
@@ -51559,7 +51667,7 @@
       </c>
       <c r="B1602" s="1" t="inlineStr">
         <is>
-          <t>[ʁe.faˈze(ʁ)] 翻拍&lt;动&gt;</t>
+          <t>[/ʁe.faˈze(ʁ)/] 重做；重制&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1602" s="1" t="inlineStr">
@@ -51569,7 +51677,7 @@
       </c>
       <c r="D1602" s="1" t="inlineStr">
         <is>
-          <t>翻拍</t>
+          <t>重做；重制&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1602" s="1" t="inlineStr">
@@ -51879,7 +51987,7 @@
       </c>
       <c r="B1612" s="1" t="inlineStr">
         <is>
-          <t>[aˈpɔ.li.si] 政策&lt;名&gt;</t>
+          <t>[aˈpɔ.li.si] 保险单；保单&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1612" s="1" t="inlineStr">
@@ -51889,7 +51997,7 @@
       </c>
       <c r="D1612" s="1" t="inlineStr">
         <is>
-          <t>政策</t>
+          <t>保险单；保单</t>
         </is>
       </c>
       <c r="E1612" s="1" t="inlineStr">
@@ -51943,7 +52051,7 @@
       </c>
       <c r="B1614" s="1" t="inlineStr">
         <is>
-          <t>[bõˈbis.tɐ] 轰炸机&lt;名&gt;</t>
+          <t>[/bõˈbis.tɐ/] 炸弹客；放置炸弹的人&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1614" s="1" t="inlineStr">
@@ -51953,7 +52061,7 @@
       </c>
       <c r="D1614" s="1" t="inlineStr">
         <is>
-          <t>轰炸机</t>
+          <t>炸弹客；放置炸弹的人&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1614" s="1" t="inlineStr">
@@ -52167,7 +52275,7 @@
       </c>
       <c r="B1621" s="1" t="inlineStr">
         <is>
-          <t>[deˈli.tu] 冒犯&lt;名&gt;</t>
+          <t>[deˈli.tu] 罪行；犯罪&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1621" s="1" t="inlineStr">
@@ -52177,7 +52285,7 @@
       </c>
       <c r="D1621" s="1" t="inlineStr">
         <is>
-          <t>冒犯</t>
+          <t>罪行；犯罪</t>
         </is>
       </c>
       <c r="E1621" s="1" t="inlineStr">
@@ -52199,7 +52307,7 @@
       </c>
       <c r="B1622" s="1" t="inlineStr">
         <is>
-          <t>[seˈla(ʁ)] 密封件&lt;动&gt;</t>
+          <t>[/seˈla(ʁ)/] 给（马）装鞍&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1622" s="1" t="inlineStr">
@@ -52209,7 +52317,7 @@
       </c>
       <c r="D1622" s="1" t="inlineStr">
         <is>
-          <t>密封件</t>
+          <t>给（马）装鞍&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1622" s="1" t="inlineStr">
@@ -52231,7 +52339,7 @@
       </c>
       <c r="B1623" s="1" t="inlineStr">
         <is>
-          <t>[li.ɡaˈdu.ɾɐ] 结字&lt;名&gt;</t>
+          <t>[li.ɡaˈdu.ɾɐ] 绑扎；绷带；连结线；连字&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1623" s="1" t="inlineStr">
@@ -52241,7 +52349,7 @@
       </c>
       <c r="D1623" s="1" t="inlineStr">
         <is>
-          <t>结字</t>
+          <t>绑扎；绷带；连结线；连字</t>
         </is>
       </c>
       <c r="E1623" s="1" t="inlineStr">
@@ -52458,7 +52566,11 @@
           <t>电子的&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C1630" s="1" t="inlineStr"/>
+      <c r="C1630" s="1" t="inlineStr">
+        <is>
+          <t>/e.lekˈtɾɔ.ni.ku/</t>
+        </is>
+      </c>
       <c r="D1630" s="1" t="inlineStr">
         <is>
           <t>电子的</t>
@@ -52483,7 +52595,7 @@
       </c>
       <c r="B1631" s="1" t="inlineStr">
         <is>
-          <t>[paˈpa(ʁ)] 帕帕尔&lt;动&gt;</t>
+          <t>[paˈpa(ʁ)] 狼吞虎咽地吃；大口吃&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1631" s="1" t="inlineStr">
@@ -52493,7 +52605,7 @@
       </c>
       <c r="D1631" s="1" t="inlineStr">
         <is>
-          <t>帕帕尔</t>
+          <t>狼吞虎咽地吃；大口吃</t>
         </is>
       </c>
       <c r="E1631" s="1" t="inlineStr">
@@ -52771,7 +52883,7 @@
       </c>
       <c r="B1640" s="1" t="inlineStr">
         <is>
-          <t>[ˈto.ɐ] 什么都没有&lt;名&gt;</t>
+          <t>[/ˈto.ɐ/] 拖缆；闲散地&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1640" s="1" t="inlineStr">
@@ -52781,7 +52893,7 @@
       </c>
       <c r="D1640" s="1" t="inlineStr">
         <is>
-          <t>什么都没有</t>
+          <t>拖缆；闲散地</t>
         </is>
       </c>
       <c r="E1640" s="1" t="inlineStr">
@@ -53731,7 +53843,7 @@
       </c>
       <c r="B1670" s="1" t="inlineStr">
         <is>
-          <t>[bõˈbɔʁ.du] 港口&lt;名&gt;</t>
+          <t>[bõˈbɔʁ.du] 左舷&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1670" s="1" t="inlineStr">
@@ -53741,7 +53853,7 @@
       </c>
       <c r="D1670" s="1" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>左舷</t>
         </is>
       </c>
       <c r="E1670" s="1" t="inlineStr">
@@ -53896,7 +54008,7 @@
       </c>
       <c r="C1675" s="1" t="inlineStr">
         <is>
-          <t>ĩ.vẽ.ˈta.ɾãʊ̃</t>
+          <t>/ĩ.vẽ.ˈta.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1675" s="1" t="inlineStr">
@@ -53926,7 +54038,11 @@
           <t>劳尔&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1676" s="1" t="inlineStr"/>
+      <c r="C1676" s="1" t="inlineStr">
+        <is>
+          <t>/ʁaˈul/</t>
+        </is>
+      </c>
       <c r="D1676" s="1" t="inlineStr">
         <is>
           <t>劳尔</t>
@@ -54116,7 +54232,7 @@
       </c>
       <c r="C1682" s="1" t="inlineStr">
         <is>
-          <t>de.za.tʃi.ˈvax</t>
+          <t>/de.za.tʃi.ˈvax/</t>
         </is>
       </c>
       <c r="D1682" s="1" t="inlineStr">
@@ -54399,7 +54515,7 @@
       </c>
       <c r="B1691" s="1" t="inlineStr">
         <is>
-          <t>[so.leˈtɾa(ʁ)] 咒语&lt;动&gt;</t>
+          <t>[so.leˈtɾa(ʁ)] 拼写；逐字母拼读&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1691" s="1" t="inlineStr">
@@ -54409,7 +54525,7 @@
       </c>
       <c r="D1691" s="1" t="inlineStr">
         <is>
-          <t>咒语</t>
+          <t>拼写；逐字母拼读</t>
         </is>
       </c>
       <c r="E1691" s="1" t="inlineStr">
@@ -54431,7 +54547,7 @@
       </c>
       <c r="B1692" s="1" t="inlineStr">
         <is>
-          <t>[de.liˈɾa(ʁ)] 狂欢&lt;动&gt;</t>
+          <t>[de.liˈɾa(ʁ)] 胡言乱语；神志不清；狂热&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1692" s="1" t="inlineStr">
@@ -54441,7 +54557,7 @@
       </c>
       <c r="D1692" s="1" t="inlineStr">
         <is>
-          <t>狂欢</t>
+          <t>胡言乱语；神志不清；狂热</t>
         </is>
       </c>
       <c r="E1692" s="1" t="inlineStr">
@@ -54463,13 +54579,17 @@
       </c>
       <c r="B1693" s="1" t="inlineStr">
         <is>
-          <t>别墅&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C1693" s="1" t="inlineStr"/>
+          <t>[[ˈvi.lɐ]] vila：别墅&lt;名&gt;&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C1693" s="1" t="inlineStr">
+        <is>
+          <t>/ˈvi.lɐ/</t>
+        </is>
+      </c>
       <c r="D1693" s="1" t="inlineStr">
         <is>
-          <t>别墅</t>
+          <t>vila：别墅&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1693" s="1" t="inlineStr">
@@ -54587,7 +54707,7 @@
       </c>
       <c r="B1697" s="1" t="inlineStr">
         <is>
-          <t>[oˈɾa.ku.lu] 甲骨文&lt;名&gt;</t>
+          <t>[oˈɾa.ku.lu] 神谕；预言者；神示所&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1697" s="1" t="inlineStr">
@@ -54597,7 +54717,7 @@
       </c>
       <c r="D1697" s="1" t="inlineStr">
         <is>
-          <t>甲骨文</t>
+          <t>神谕；预言者；神示所</t>
         </is>
       </c>
       <c r="E1697" s="1" t="inlineStr">
@@ -54907,7 +55027,7 @@
       </c>
       <c r="B1707" s="1" t="inlineStr">
         <is>
-          <t>[boˈʁa.ʃu] 宝贝&lt;名&gt;</t>
+          <t>[boˈʁa.ʃu] 醉的；醉汉&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1707" s="1" t="inlineStr">
@@ -54917,7 +55037,7 @@
       </c>
       <c r="D1707" s="1" t="inlineStr">
         <is>
-          <t>宝贝</t>
+          <t>醉的；醉汉</t>
         </is>
       </c>
       <c r="E1707" s="1" t="inlineStr">
@@ -55040,7 +55160,7 @@
       </c>
       <c r="C1711" s="1" t="inlineStr">
         <is>
-          <t>o.ˈxo.ɾɪs</t>
+          <t>/o.ˈxo.ɾɪs/</t>
         </is>
       </c>
       <c r="D1711" s="1" t="inlineStr">
@@ -55136,7 +55256,7 @@
       </c>
       <c r="C1714" s="1" t="inlineStr">
         <is>
-          <t>su.peɣ.vi.zi.o.ˈnax</t>
+          <t>/su.peɣ.vi.zi.o.ˈnax/</t>
         </is>
       </c>
       <c r="D1714" s="1" t="inlineStr">
@@ -55163,7 +55283,7 @@
       </c>
       <c r="B1715" s="1" t="inlineStr">
         <is>
-          <t>[pẽˈdẽ.t͡ʃi] 待定&lt;名&gt;</t>
+          <t>[pẽˈdẽ.t͡ʃi] 吊坠；垂饰（悬挂的珠宝饰物）&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1715" s="1" t="inlineStr">
@@ -55173,7 +55293,7 @@
       </c>
       <c r="D1715" s="1" t="inlineStr">
         <is>
-          <t>待定</t>
+          <t>吊坠；垂饰（悬挂的珠宝饰物）</t>
         </is>
       </c>
       <c r="E1715" s="1" t="inlineStr">
@@ -55232,7 +55352,7 @@
       </c>
       <c r="C1717" s="1" t="inlineStr">
         <is>
-          <t>xe.fle.ˈtʃix</t>
+          <t>/xe.fle.ˈtʃix/</t>
         </is>
       </c>
       <c r="D1717" s="1" t="inlineStr">
@@ -55422,7 +55542,11 @@
           <t>lda。&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1723" s="1" t="inlineStr"/>
+      <c r="C1723" s="1" t="inlineStr">
+        <is>
+          <t>/ˈɛl.dɐ/</t>
+        </is>
+      </c>
       <c r="D1723" s="1" t="inlineStr">
         <is>
           <t>lda。</t>
@@ -55703,7 +55827,7 @@
       </c>
       <c r="B1732" s="1" t="inlineStr">
         <is>
-          <t>[pũˈɲa.du] 少数&lt;名&gt;</t>
+          <t>[/pũˈɲa.du/] 一把；少量；少数&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1732" s="1" t="inlineStr">
@@ -55713,7 +55837,7 @@
       </c>
       <c r="D1732" s="1" t="inlineStr">
         <is>
-          <t>少数</t>
+          <t>一把；少量；少数</t>
         </is>
       </c>
       <c r="E1732" s="1" t="inlineStr">
@@ -55932,7 +56056,7 @@
       </c>
       <c r="C1739" s="1" t="inlineStr">
         <is>
-          <t>ˈa.gwə</t>
+          <t>/ˈa.gwə/</t>
         </is>
       </c>
       <c r="D1739" s="1" t="inlineStr">
@@ -56028,7 +56152,7 @@
       </c>
       <c r="C1742" s="1" t="inlineStr">
         <is>
-          <t>a.sey.ˈta.ɾãʊ̃</t>
+          <t>/a.sey.ˈta.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1742" s="1" t="inlineStr">
@@ -56247,7 +56371,7 @@
       </c>
       <c r="B1749" s="1" t="inlineStr">
         <is>
-          <t>[ˈma.ɾɐ] 马拉&lt;名&gt;</t>
+          <t>[/ˈma.ɾɐ/] 南美啮齿动物（巴塔哥尼亚野兔）&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1749" s="1" t="inlineStr">
@@ -56257,7 +56381,7 @@
       </c>
       <c r="D1749" s="1" t="inlineStr">
         <is>
-          <t>马拉</t>
+          <t>南美啮齿动物（巴塔哥尼亚野兔）&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1749" s="1" t="inlineStr">
@@ -56316,7 +56440,7 @@
       </c>
       <c r="C1751" s="1" t="inlineStr">
         <is>
-          <t>ˈpa.ɾa.bɾi.zəs</t>
+          <t>/ˈpa.ɾa.bɾi.zəs/</t>
         </is>
       </c>
       <c r="D1751" s="1" t="inlineStr">
@@ -56375,7 +56499,7 @@
       </c>
       <c r="B1753" s="1" t="inlineStr">
         <is>
-          <t>[ve.ʒeˈta(ʁ)] 植物人&lt;动&gt;</t>
+          <t>[ve.ʒeˈta(ʁ)] 过单调呆板的生活；生长；生存&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1753" s="1" t="inlineStr">
@@ -56385,7 +56509,7 @@
       </c>
       <c r="D1753" s="1" t="inlineStr">
         <is>
-          <t>植物人</t>
+          <t>过单调呆板的生活；生长；生存</t>
         </is>
       </c>
       <c r="E1753" s="1" t="inlineStr">
@@ -56604,7 +56728,7 @@
       </c>
       <c r="C1760" s="1" t="inlineStr">
         <is>
-          <t>kõ.koɣ.ˈda.ɾãʊ̃</t>
+          <t>/kõ.koɣ.ˈda.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1760" s="1" t="inlineStr">
@@ -56698,7 +56822,11 @@
           <t>档案&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1763" s="1" t="inlineStr"/>
+      <c r="C1763" s="1" t="inlineStr">
+        <is>
+          <t>/dɔ.siˈeʁ/</t>
+        </is>
+      </c>
       <c r="D1763" s="1" t="inlineStr">
         <is>
           <t>档案</t>
@@ -56787,7 +56915,7 @@
       </c>
       <c r="B1766" s="1" t="inlineStr">
         <is>
-          <t>[o(w)ˈza.du] 粗体&lt;形&gt;</t>
+          <t>[o(w)ˈza.du] 大胆的；勇敢的；放肆的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C1766" s="1" t="inlineStr">
@@ -56797,7 +56925,7 @@
       </c>
       <c r="D1766" s="1" t="inlineStr">
         <is>
-          <t>粗体</t>
+          <t>大胆的；勇敢的；放肆的</t>
         </is>
       </c>
       <c r="E1766" s="1" t="inlineStr">
@@ -57139,7 +57267,7 @@
       </c>
       <c r="B1777" s="1" t="inlineStr">
         <is>
-          <t>[de.puˈta.du] 副手&lt;名&gt;</t>
+          <t>[de.puˈta.du] 议员；众议员&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1777" s="1" t="inlineStr">
@@ -57149,7 +57277,7 @@
       </c>
       <c r="D1777" s="1" t="inlineStr">
         <is>
-          <t>副手</t>
+          <t>议员；众议员</t>
         </is>
       </c>
       <c r="E1777" s="1" t="inlineStr">
@@ -57368,7 +57496,7 @@
       </c>
       <c r="C1784" s="1" t="inlineStr">
         <is>
-          <t>ʃe.ga.ˈɾãʊ̃</t>
+          <t>/ʃe.ga.ˈɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1784" s="1" t="inlineStr">
@@ -58003,7 +58131,7 @@
       </c>
       <c r="B1804" s="1" t="inlineStr">
         <is>
-          <t>[ma.ʃuˈka(ʁ)] 受伤&lt;动&gt;</t>
+          <t>[/ma.ʃuˈka(ʁ)/] 打伤，使受伤&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1804" s="1" t="inlineStr">
@@ -58013,7 +58141,7 @@
       </c>
       <c r="D1804" s="1" t="inlineStr">
         <is>
-          <t>受伤</t>
+          <t>打伤，使受伤&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1804" s="1" t="inlineStr">
@@ -58867,7 +58995,7 @@
       </c>
       <c r="B1831" s="1" t="inlineStr">
         <is>
-          <t>[d͡ʒi.ploˈma.t͡ʃi.kɐ] 外交的&lt;名&gt;</t>
+          <t>[/d͡ʒi.ploˈma.t͡ʃi.kɐ/] 外交的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1831" s="1" t="inlineStr">
@@ -58877,7 +59005,7 @@
       </c>
       <c r="D1831" s="1" t="inlineStr">
         <is>
-          <t>外交的</t>
+          <t>外交的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E1831" s="1" t="inlineStr">
@@ -58931,7 +59059,7 @@
       </c>
       <c r="B1833" s="1" t="inlineStr">
         <is>
-          <t>[kɾɨʃˈsẽ.du] 成长中&lt;名&gt;</t>
+          <t>[kɾɨʃˈsẽ.du] 增长；成长&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1833" s="1" t="inlineStr">
@@ -58941,7 +59069,7 @@
       </c>
       <c r="D1833" s="1" t="inlineStr">
         <is>
-          <t>成长中</t>
+          <t>增长；成长</t>
         </is>
       </c>
       <c r="E1833" s="1" t="inlineStr">
@@ -59283,7 +59411,7 @@
       </c>
       <c r="B1844" s="1" t="inlineStr">
         <is>
-          <t>[isˈklujʁ] 删除&lt;动&gt;</t>
+          <t>[/isˈklujʁ/] 排除；开除&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1844" s="1" t="inlineStr">
@@ -59293,7 +59421,7 @@
       </c>
       <c r="D1844" s="1" t="inlineStr">
         <is>
-          <t>删除</t>
+          <t>排除；开除</t>
         </is>
       </c>
       <c r="E1844" s="1" t="inlineStr">
@@ -59411,7 +59539,7 @@
       </c>
       <c r="B1848" s="1" t="inlineStr">
         <is>
-          <t>[d͡ʒisˈt͡ʃĩ.tu] 独特的&lt;形&gt;</t>
+          <t>[/d͡ʒisˈt͡ʃĩ.tu/] 不同的；有区别的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C1848" s="1" t="inlineStr">
@@ -59421,7 +59549,7 @@
       </c>
       <c r="D1848" s="1" t="inlineStr">
         <is>
-          <t>独特的</t>
+          <t>不同的；有区别的</t>
         </is>
       </c>
       <c r="E1848" s="1" t="inlineStr">
@@ -59539,7 +59667,7 @@
       </c>
       <c r="B1852" s="1" t="inlineStr">
         <is>
-          <t>[laˈdɾa(ʁ)] 树皮&lt;动&gt;</t>
+          <t>[laˈdɾa(ʁ)] 吠叫；狗吠&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1852" s="1" t="inlineStr">
@@ -59549,7 +59677,7 @@
       </c>
       <c r="D1852" s="1" t="inlineStr">
         <is>
-          <t>树皮</t>
+          <t>吠叫；狗吠</t>
         </is>
       </c>
       <c r="E1852" s="1" t="inlineStr">
@@ -59859,7 +59987,7 @@
       </c>
       <c r="B1862" s="1" t="inlineStr">
         <is>
-          <t>[maʁˈɡa(ʁ)] 玛加尔&lt;动&gt;</t>
+          <t>[maʁˈɡa(ʁ)] 擦洗；擦亮&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1862" s="1" t="inlineStr">
@@ -59869,7 +59997,7 @@
       </c>
       <c r="D1862" s="1" t="inlineStr">
         <is>
-          <t>玛加尔</t>
+          <t>擦洗；擦亮</t>
         </is>
       </c>
       <c r="E1862" s="1" t="inlineStr">
@@ -59990,7 +60118,11 @@
           <t>TC&lt;动&gt;</t>
         </is>
       </c>
-      <c r="C1866" s="1" t="inlineStr"/>
+      <c r="C1866" s="1" t="inlineStr">
+        <is>
+          <t>/tk/</t>
+        </is>
+      </c>
       <c r="D1866" s="1" t="inlineStr">
         <is>
           <t>TC</t>
@@ -60079,7 +60211,7 @@
       </c>
       <c r="B1869" s="1" t="inlineStr">
         <is>
-          <t>[ˈtɾi.a.d͡ʒi] 三合会&lt;名&gt;</t>
+          <t>[ˈtɾi.a.d͡ʒi] 三和弦；三位一体；三个一组&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1869" s="1" t="inlineStr">
@@ -60089,7 +60221,7 @@
       </c>
       <c r="D1869" s="1" t="inlineStr">
         <is>
-          <t>三合会</t>
+          <t>三和弦；三位一体；三个一组</t>
         </is>
       </c>
       <c r="E1869" s="1" t="inlineStr">
@@ -60495,7 +60627,7 @@
       </c>
       <c r="B1882" s="1" t="inlineStr">
         <is>
-          <t>[pɾi.zi.oˈnaw] 监狱&lt;形&gt;</t>
+          <t>[pɾi.zi.oˈnaw] 监狱的；监禁的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C1882" s="1" t="inlineStr">
@@ -60505,7 +60637,7 @@
       </c>
       <c r="D1882" s="1" t="inlineStr">
         <is>
-          <t>监狱</t>
+          <t>监狱的；监禁的</t>
         </is>
       </c>
       <c r="E1882" s="1" t="inlineStr">
@@ -60687,7 +60819,7 @@
       </c>
       <c r="B1888" s="1" t="inlineStr">
         <is>
-          <t>[ˈɔ.sju] 骨瘦如柴&lt;形&gt;</t>
+          <t>[ˈɔ.sju] 骨的；骨骼的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C1888" s="1" t="inlineStr">
@@ -60697,7 +60829,7 @@
       </c>
       <c r="D1888" s="1" t="inlineStr">
         <is>
-          <t>骨瘦如柴</t>
+          <t>骨的；骨骼的</t>
         </is>
       </c>
       <c r="E1888" s="1" t="inlineStr">
@@ -60847,7 +60979,7 @@
       </c>
       <c r="B1893" s="1" t="inlineStr">
         <is>
-          <t>[fiˈa.du] 纺成的&lt;形&gt;</t>
+          <t>[/fiˈa.du/] 赊账的（comprar fiado）；纺成的&lt;形&gt;&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C1893" s="1" t="inlineStr">
@@ -60857,7 +60989,7 @@
       </c>
       <c r="D1893" s="1" t="inlineStr">
         <is>
-          <t>纺成的</t>
+          <t>赊账的（comprar fiado）；纺成的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E1893" s="1" t="inlineStr">
@@ -61231,7 +61363,7 @@
       </c>
       <c r="B1905" s="1" t="inlineStr">
         <is>
-          <t>[ˈsɛ.t͡ʃi] 设置&lt;名&gt;</t>
+          <t>[/ˈsɛ.t͡ʃi/] 一套；一组；布景&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1905" s="1" t="inlineStr">
@@ -61241,7 +61373,7 @@
       </c>
       <c r="D1905" s="1" t="inlineStr">
         <is>
-          <t>设置</t>
+          <t>一套；一组；布景&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1905" s="1" t="inlineStr">
@@ -61327,7 +61459,7 @@
       </c>
       <c r="B1908" s="1" t="inlineStr">
         <is>
-          <t>[ˈkɔ.mi.ku] 漫画&lt;形&gt;</t>
+          <t>[ˈkɔ.mi.ku] 滑稽的；喜剧的；可笑的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C1908" s="1" t="inlineStr">
@@ -61337,7 +61469,7 @@
       </c>
       <c r="D1908" s="1" t="inlineStr">
         <is>
-          <t>漫画</t>
+          <t>滑稽的；喜剧的；可笑的</t>
         </is>
       </c>
       <c r="E1908" s="1" t="inlineStr">
@@ -61615,7 +61747,7 @@
       </c>
       <c r="B1917" s="1" t="inlineStr">
         <is>
-          <t>[a.pa.ɾẽˈta(ʁ)] 出现&lt;动&gt;</t>
+          <t>[a.pa.ɾẽˈta(ʁ)] 显得；看似；貌似&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1917" s="1" t="inlineStr">
@@ -61625,7 +61757,7 @@
       </c>
       <c r="D1917" s="1" t="inlineStr">
         <is>
-          <t>出现</t>
+          <t>显得；看似；貌似</t>
         </is>
       </c>
       <c r="E1917" s="1" t="inlineStr">
@@ -61652,7 +61784,7 @@
       </c>
       <c r="C1918" s="1" t="inlineStr">
         <is>
-          <t>a.dʒi.ã.ta.ˈmẽ.tʊ</t>
+          <t>/a.dʒi.ã.ta.ˈmẽ.tʊ/</t>
         </is>
       </c>
       <c r="D1918" s="1" t="inlineStr">
@@ -61716,7 +61848,7 @@
       </c>
       <c r="C1920" s="1" t="inlineStr">
         <is>
-          <t>es.ke.ˈse.ɾãʊ̃</t>
+          <t>/es.ke.ˈse.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1920" s="1" t="inlineStr">
@@ -62226,7 +62358,11 @@
           <t>三&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1936" s="1" t="inlineStr"/>
+      <c r="C1936" s="1" t="inlineStr">
+        <is>
+          <t>/tɾɛs/</t>
+        </is>
+      </c>
       <c r="D1936" s="1" t="inlineStr">
         <is>
           <t>三</t>
@@ -62955,7 +63091,7 @@
       </c>
       <c r="B1959" s="1" t="inlineStr">
         <is>
-          <t>[ˈfu.lu] 富洛&lt;形&gt;</t>
+          <t>[ˈfu.lu] 暴怒的；狂怒的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C1959" s="1" t="inlineStr">
@@ -62965,7 +63101,7 @@
       </c>
       <c r="D1959" s="1" t="inlineStr">
         <is>
-          <t>富洛</t>
+          <t>暴怒的；狂怒的</t>
         </is>
       </c>
       <c r="E1959" s="1" t="inlineStr">
@@ -63086,7 +63222,11 @@
           <t>兰特&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1963" s="1" t="inlineStr"/>
+      <c r="C1963" s="1" t="inlineStr">
+        <is>
+          <t>/ʁɐ̃d/</t>
+        </is>
+      </c>
       <c r="D1963" s="1" t="inlineStr">
         <is>
           <t>兰特</t>
@@ -63719,7 +63859,7 @@
       </c>
       <c r="B1983" s="1" t="inlineStr">
         <is>
-          <t>[a.pɾe.ẽˈsɐ̃w̃] 癫痫发作&lt;名&gt;</t>
+          <t>[a.pɾe.ẽˈsɐ̃w̃] 忧虑；不安；扣押；没收&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1983" s="1" t="inlineStr">
@@ -63729,7 +63869,7 @@
       </c>
       <c r="D1983" s="1" t="inlineStr">
         <is>
-          <t>癫痫发作</t>
+          <t>忧虑；不安；扣押；没收</t>
         </is>
       </c>
       <c r="E1983" s="1" t="inlineStr">
@@ -63751,7 +63891,7 @@
       </c>
       <c r="B1984" s="1" t="inlineStr">
         <is>
-          <t>[isˈta.lu] 快照&lt;名&gt;</t>
+          <t>[isˈta.lu] 爆裂声；咔嚓声&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1984" s="1" t="inlineStr">
@@ -63761,7 +63901,7 @@
       </c>
       <c r="D1984" s="1" t="inlineStr">
         <is>
-          <t>快照</t>
+          <t>爆裂声；咔嚓声</t>
         </is>
       </c>
       <c r="E1984" s="1" t="inlineStr">
@@ -63879,7 +64019,7 @@
       </c>
       <c r="B1988" s="1" t="inlineStr">
         <is>
-          <t>[ʒuˈdaj.ku] 犹太人&lt;形&gt;</t>
+          <t>[ʒuˈdaj.ku] 犹太的；犹太教的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C1988" s="1" t="inlineStr">
@@ -63889,7 +64029,7 @@
       </c>
       <c r="D1988" s="1" t="inlineStr">
         <is>
-          <t>犹太人</t>
+          <t>犹太的；犹太教的</t>
         </is>
       </c>
       <c r="E1988" s="1" t="inlineStr">
@@ -63943,7 +64083,7 @@
       </c>
       <c r="B1990" s="1" t="inlineStr">
         <is>
-          <t>[ɡo.veʁ.na.mẽˈtaw] 政府&lt;形&gt;</t>
+          <t>[ɡo.veʁ.na.mẽˈtaw] 政府的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C1990" s="1" t="inlineStr">
@@ -63953,7 +64093,7 @@
       </c>
       <c r="D1990" s="1" t="inlineStr">
         <is>
-          <t>政府</t>
+          <t>政府的</t>
         </is>
       </c>
       <c r="E1990" s="1" t="inlineStr">
@@ -64039,7 +64179,7 @@
       </c>
       <c r="B1993" s="1" t="inlineStr">
         <is>
-          <t>[ˈpi.kɐ] 迪克&lt;名&gt;</t>
+          <t>[ˈpi.kɐ] 刺；扎；刺孔；注射&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1993" s="1" t="inlineStr">
@@ -64049,7 +64189,7 @@
       </c>
       <c r="D1993" s="1" t="inlineStr">
         <is>
-          <t>迪克</t>
+          <t>刺；扎；刺孔；注射</t>
         </is>
       </c>
       <c r="E1993" s="1" t="inlineStr">
@@ -64204,7 +64344,7 @@
       </c>
       <c r="C1998" s="1" t="inlineStr">
         <is>
-          <t>tɾã.za.ˈsãʊ̃</t>
+          <t>/tɾã.za.ˈsãʊ̃/</t>
         </is>
       </c>
       <c r="D1998" s="1" t="inlineStr">
@@ -64455,7 +64595,7 @@
       </c>
       <c r="B2006" s="1" t="inlineStr">
         <is>
-          <t>[kõ.doˈmĩ.nju] 公寓&lt;名&gt;</t>
+          <t>[/kõ.doˈmĩ.nju/] 共管公寓；公寓管理&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2006" s="1" t="inlineStr">
@@ -64465,7 +64605,7 @@
       </c>
       <c r="D2006" s="1" t="inlineStr">
         <is>
-          <t>公寓</t>
+          <t>共管公寓；公寓管理</t>
         </is>
       </c>
       <c r="E2006" s="1" t="inlineStr">
@@ -64679,7 +64819,7 @@
       </c>
       <c r="B2013" s="1" t="inlineStr">
         <is>
-          <t>[laˈt͡ʃĩ.nu] 拉丁语&lt;名&gt;</t>
+          <t>[laˈt͡ʃĩ.nu] 拉丁的；拉丁人&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2013" s="1" t="inlineStr">
@@ -64689,7 +64829,7 @@
       </c>
       <c r="D2013" s="1" t="inlineStr">
         <is>
-          <t>拉丁语</t>
+          <t>拉丁的；拉丁人</t>
         </is>
       </c>
       <c r="E2013" s="1" t="inlineStr">
@@ -64746,7 +64886,11 @@
           <t>出租车&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2015" s="1" t="inlineStr"/>
+      <c r="C2015" s="1" t="inlineStr">
+        <is>
+          <t>/ˈta.k.si/</t>
+        </is>
+      </c>
       <c r="D2015" s="1" t="inlineStr">
         <is>
           <t>出租车</t>
@@ -64803,7 +64947,7 @@
       </c>
       <c r="B2017" s="1" t="inlineStr">
         <is>
-          <t>[tɾa.fiˈka(ʁ)] 交通&lt;动&gt;</t>
+          <t>[tɾa.fiˈka(ʁ)] 贩运；非法买卖；贩毒&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2017" s="1" t="inlineStr">
@@ -64813,7 +64957,7 @@
       </c>
       <c r="D2017" s="1" t="inlineStr">
         <is>
-          <t>交通</t>
+          <t>贩运；非法买卖；贩毒</t>
         </is>
       </c>
       <c r="E2017" s="1" t="inlineStr">
@@ -65032,7 +65176,7 @@
       </c>
       <c r="C2024" s="1" t="inlineStr">
         <is>
-          <t>mi.kɾo.ˈõ.dəs</t>
+          <t>/mi.kɾo.ˈõ.dəs/</t>
         </is>
       </c>
       <c r="D2024" s="1" t="inlineStr">
@@ -65123,17 +65267,17 @@
       </c>
       <c r="B2027" s="1" t="inlineStr">
         <is>
-          <t>[kõ.tʃi.nu.ˈa.ɾãʊ̃] 继续&lt;动&gt;</t>
+          <t>[kõ.tʃi.nu.ˈa.ɾãʊ̃] 继续（动词 continuar 的第三人称复数过去完成时形式）&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2027" s="1" t="inlineStr">
         <is>
-          <t>kõ.tʃi.nu.ˈa.ɾãʊ̃</t>
+          <t>/kõ.tʃi.nu.ˈa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2027" s="1" t="inlineStr">
         <is>
-          <t>继续</t>
+          <t>继续（动词 continuar 的第三人称复数过去完成时形式）</t>
         </is>
       </c>
       <c r="E2027" s="1" t="inlineStr">
@@ -65411,7 +65555,7 @@
       </c>
       <c r="B2036" s="1" t="inlineStr">
         <is>
-          <t>[ma.fiˈo.zu] 流氓&lt;名&gt;</t>
+          <t>[ma.fiˈo.zu] 黑手党成员；黑手党的&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2036" s="1" t="inlineStr">
@@ -65421,7 +65565,7 @@
       </c>
       <c r="D2036" s="1" t="inlineStr">
         <is>
-          <t>流氓</t>
+          <t>黑手党成员；黑手党的</t>
         </is>
       </c>
       <c r="E2036" s="1" t="inlineStr">
@@ -65544,7 +65688,7 @@
       </c>
       <c r="C2040" s="1" t="inlineStr">
         <is>
-          <t>as.tɛ.ˈɾɔy.dʒɪ</t>
+          <t>/as.tɛ.ˈɾɔy.dʒɪ/</t>
         </is>
       </c>
       <c r="D2040" s="1" t="inlineStr">
@@ -65832,7 +65976,7 @@
       </c>
       <c r="C2049" s="1" t="inlineStr">
         <is>
-          <t>xap.ˈta.ɾãʊ̃</t>
+          <t>/xap.ˈta.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2049" s="1" t="inlineStr">
@@ -65955,7 +66099,7 @@
       </c>
       <c r="B2053" s="1" t="inlineStr">
         <is>
-          <t>[fluˈi(ʁ)] 流量&lt;动&gt;</t>
+          <t>[fluˈi(ʁ)] 流动；流出&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2053" s="1" t="inlineStr">
@@ -65965,7 +66109,7 @@
       </c>
       <c r="D2053" s="1" t="inlineStr">
         <is>
-          <t>流量</t>
+          <t>流动；流出</t>
         </is>
       </c>
       <c r="E2053" s="1" t="inlineStr">
@@ -66083,7 +66227,7 @@
       </c>
       <c r="B2057" s="1" t="inlineStr">
         <is>
-          <t>[isˈto.ʒu] 案例&lt;名&gt;</t>
+          <t>[isˈto.ʒu] 盒子；匣子；文具盒&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2057" s="1" t="inlineStr">
@@ -66093,7 +66237,7 @@
       </c>
       <c r="D2057" s="1" t="inlineStr">
         <is>
-          <t>案例</t>
+          <t>盒子；匣子；文具盒</t>
         </is>
       </c>
       <c r="E2057" s="1" t="inlineStr">
@@ -66472,7 +66616,7 @@
       </c>
       <c r="C2069" s="1" t="inlineStr">
         <is>
-          <t>e.ɾe.ˈsãʊ̃</t>
+          <t>/e.ɾe.ˈsãʊ̃/</t>
         </is>
       </c>
       <c r="D2069" s="1" t="inlineStr">
@@ -66851,7 +66995,7 @@
       </c>
       <c r="B2081" s="1" t="inlineStr">
         <is>
-          <t>[ˈʁas.kɐ] 从头开始&lt;名&gt;</t>
+          <t>[ˈʁas.kɐ] 拖网；劣质货；乌合之众&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2081" s="1" t="inlineStr">
@@ -66861,7 +67005,7 @@
       </c>
       <c r="D2081" s="1" t="inlineStr">
         <is>
-          <t>从头开始</t>
+          <t>拖网；劣质货；乌合之众</t>
         </is>
       </c>
       <c r="E2081" s="1" t="inlineStr">
@@ -66915,7 +67059,7 @@
       </c>
       <c r="B2083" s="1" t="inlineStr">
         <is>
-          <t>[ʁoˈʃe.du] 摇滚&lt;名&gt;</t>
+          <t>[ʁoˈʃe.du] 岩石；礁石；峭壁&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2083" s="1" t="inlineStr">
@@ -66925,7 +67069,7 @@
       </c>
       <c r="D2083" s="1" t="inlineStr">
         <is>
-          <t>摇滚</t>
+          <t>岩石；礁石；峭壁</t>
         </is>
       </c>
       <c r="E2083" s="1" t="inlineStr">
@@ -67075,7 +67219,7 @@
       </c>
       <c r="B2088" s="1" t="inlineStr">
         <is>
-          <t>[ˈdaʁ.du] 标枪&lt;名&gt;</t>
+          <t>[/ˈdaʁ.du/] 镖、飞镖&lt;名&gt;（小箭，非标枪）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2088" s="1" t="inlineStr">
@@ -67085,7 +67229,7 @@
       </c>
       <c r="D2088" s="1" t="inlineStr">
         <is>
-          <t>标枪</t>
+          <t>镖、飞镖&lt;名&gt;（小箭，非标枪）</t>
         </is>
       </c>
       <c r="E2088" s="1" t="inlineStr">
@@ -67240,7 +67384,7 @@
       </c>
       <c r="C2093" s="1" t="inlineStr">
         <is>
-          <t>ˈxɛ.tə</t>
+          <t>/ˈxɛ.tə/</t>
         </is>
       </c>
       <c r="D2093" s="1" t="inlineStr">
@@ -67304,7 +67448,7 @@
       </c>
       <c r="C2095" s="1" t="inlineStr">
         <is>
-          <t>o.ko.ˈxe.ɾãʊ̃</t>
+          <t>/o.ko.ˈxe.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2095" s="1" t="inlineStr">
@@ -67427,7 +67571,7 @@
       </c>
       <c r="B2099" s="1" t="inlineStr">
         <is>
-          <t>[pɾe.ɡaˈdoʁ] 传教士&lt;名&gt;</t>
+          <t>[/pɾe.ɡaˈdoʁ/] 布道者&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2099" s="1" t="inlineStr">
@@ -67437,7 +67581,7 @@
       </c>
       <c r="D2099" s="1" t="inlineStr">
         <is>
-          <t>传教士</t>
+          <t>布道者&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2099" s="1" t="inlineStr">
@@ -67654,7 +67798,11 @@
           <t>下摆&lt;叹&gt;</t>
         </is>
       </c>
-      <c r="C2106" s="1" t="inlineStr"/>
+      <c r="C2106" s="1" t="inlineStr">
+        <is>
+          <t>/ẽj̃/</t>
+        </is>
+      </c>
       <c r="D2106" s="1" t="inlineStr">
         <is>
           <t>下摆</t>
@@ -67874,7 +68022,11 @@
           <t>兼职&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2113" s="1" t="inlineStr"/>
+      <c r="C2113" s="1" t="inlineStr">
+        <is>
+          <t>/ˌpaʁˈtajm/</t>
+        </is>
+      </c>
       <c r="D2113" s="1" t="inlineStr">
         <is>
           <t>兼职</t>
@@ -67899,7 +68051,7 @@
       </c>
       <c r="B2114" s="1" t="inlineStr">
         <is>
-          <t>[ˌkeˈɔ] 科&lt;名&gt;</t>
+          <t>[ˌkeˈɔ] 击倒；惨败&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2114" s="1" t="inlineStr">
@@ -67909,7 +68061,7 @@
       </c>
       <c r="D2114" s="1" t="inlineStr">
         <is>
-          <t>科</t>
+          <t>击倒；惨败</t>
         </is>
       </c>
       <c r="E2114" s="1" t="inlineStr">
@@ -68096,7 +68248,7 @@
       </c>
       <c r="C2120" s="1" t="inlineStr">
         <is>
-          <t>ka.ˈza.ɾãʊ̃</t>
+          <t>/ka.ˈza.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2120" s="1" t="inlineStr">
@@ -68187,7 +68339,7 @@
       </c>
       <c r="B2123" s="1" t="inlineStr">
         <is>
-          <t>[ˈloj.sɐ] 菜肴&lt;名&gt;</t>
+          <t>[ˈloj.sɐ] 餐具；碗碟&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2123" s="1" t="inlineStr">
@@ -68197,7 +68349,7 @@
       </c>
       <c r="D2123" s="1" t="inlineStr">
         <is>
-          <t>菜肴</t>
+          <t>餐具；碗碟</t>
         </is>
       </c>
       <c r="E2123" s="1" t="inlineStr">
@@ -68224,7 +68376,7 @@
       </c>
       <c r="C2124" s="1" t="inlineStr">
         <is>
-          <t>o.fe.ɾe.ˈse.ɾãʊ̃</t>
+          <t>/o.fe.ɾe.ˈse.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2124" s="1" t="inlineStr">
@@ -68507,7 +68659,7 @@
       </c>
       <c r="B2133" s="1" t="inlineStr">
         <is>
-          <t>[ˈtɾũ.fu] 特朗普&lt;名&gt;</t>
+          <t>[ˈtɾũ.fu] 王牌；将牌&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2133" s="1" t="inlineStr">
@@ -68517,7 +68669,7 @@
       </c>
       <c r="D2133" s="1" t="inlineStr">
         <is>
-          <t>特朗普</t>
+          <t>王牌；将牌</t>
         </is>
       </c>
       <c r="E2133" s="1" t="inlineStr">
@@ -68699,7 +68851,7 @@
       </c>
       <c r="B2139" s="1" t="inlineStr">
         <is>
-          <t>[plaˈni.si] 普通的&lt;名&gt;</t>
+          <t>[plaˈni.si] 平原&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2139" s="1" t="inlineStr">
@@ -68709,7 +68861,7 @@
       </c>
       <c r="D2139" s="1" t="inlineStr">
         <is>
-          <t>普通的</t>
+          <t>平原</t>
         </is>
       </c>
       <c r="E2139" s="1" t="inlineStr">
@@ -68795,7 +68947,7 @@
       </c>
       <c r="B2142" s="1" t="inlineStr">
         <is>
-          <t>[puˈʃa.du] 拉&lt;名&gt;</t>
+          <t>[/puˈʃa.du/] 拉（puxar 的过去分词）&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2142" s="1" t="inlineStr">
@@ -68805,7 +68957,7 @@
       </c>
       <c r="D2142" s="1" t="inlineStr">
         <is>
-          <t>拉</t>
+          <t>拉（puxar 的过去分词）&lt;形&gt;</t>
         </is>
       </c>
       <c r="E2142" s="1" t="inlineStr">
@@ -69051,7 +69203,7 @@
       </c>
       <c r="B2150" s="1" t="inlineStr">
         <is>
-          <t>[sẽ.suˈɾa(ʁ)] 审查员&lt;动&gt;</t>
+          <t>[sẽ.suˈɾa(ʁ)] 审查；删剪；谴责&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2150" s="1" t="inlineStr">
@@ -69061,7 +69213,7 @@
       </c>
       <c r="D2150" s="1" t="inlineStr">
         <is>
-          <t>审查员</t>
+          <t>审查；删剪；谴责</t>
         </is>
       </c>
       <c r="E2150" s="1" t="inlineStr">
@@ -69088,7 +69240,7 @@
       </c>
       <c r="C2151" s="1" t="inlineStr">
         <is>
-          <t>xe.gɾi.ˈsa.ɾãʊ̃</t>
+          <t>/xe.gɾi.ˈsa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2151" s="1" t="inlineStr">
@@ -69115,7 +69267,7 @@
       </c>
       <c r="B2152" s="1" t="inlineStr">
         <is>
-          <t>[fuˈɾa.du] 无聊&lt;形&gt;</t>
+          <t>[fuˈɾa.du] 穿孔的；有洞的；身无分文的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C2152" s="1" t="inlineStr">
@@ -69125,7 +69277,7 @@
       </c>
       <c r="D2152" s="1" t="inlineStr">
         <is>
-          <t>无聊</t>
+          <t>穿孔的；有洞的；身无分文的</t>
         </is>
       </c>
       <c r="E2152" s="1" t="inlineStr">
@@ -69211,7 +69363,7 @@
       </c>
       <c r="B2155" s="1" t="inlineStr">
         <is>
-          <t>[ʁeˈsĩ.tu] 外壳&lt;名&gt;</t>
+          <t>[ʁeˈsĩ.tu] 场所；场地；围地&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2155" s="1" t="inlineStr">
@@ -69221,7 +69373,7 @@
       </c>
       <c r="D2155" s="1" t="inlineStr">
         <is>
-          <t>外壳</t>
+          <t>场所；场地；围地</t>
         </is>
       </c>
       <c r="E2155" s="1" t="inlineStr">
@@ -69435,7 +69587,7 @@
       </c>
       <c r="B2162" s="1" t="inlineStr">
         <is>
-          <t>[to(w)ˈpe(j).ɾɐ] 摩尔&lt;名&gt;</t>
+          <t>[to(w)ˈpe(j).ɾɐ] 鼹鼠&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2162" s="1" t="inlineStr">
@@ -69445,7 +69597,7 @@
       </c>
       <c r="D2162" s="1" t="inlineStr">
         <is>
-          <t>摩尔</t>
+          <t>鼹鼠</t>
         </is>
       </c>
       <c r="E2162" s="1" t="inlineStr">
@@ -69499,7 +69651,7 @@
       </c>
       <c r="B2164" s="1" t="inlineStr">
         <is>
-          <t>[ˈpõ.ʃi] 冲孔&lt;名&gt;</t>
+          <t>[ˈpõ.ʃi] 潘趣酒；宾治酒&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2164" s="1" t="inlineStr">
@@ -69509,7 +69661,7 @@
       </c>
       <c r="D2164" s="1" t="inlineStr">
         <is>
-          <t>冲孔</t>
+          <t>潘趣酒；宾治酒</t>
         </is>
       </c>
       <c r="E2164" s="1" t="inlineStr">
@@ -69598,7 +69750,11 @@
           <t>那里&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C2167" s="1" t="inlineStr"/>
+      <c r="C2167" s="1" t="inlineStr">
+        <is>
+          <t>/la/</t>
+        </is>
+      </c>
       <c r="D2167" s="1" t="inlineStr">
         <is>
           <t>那里</t>
@@ -70167,7 +70323,7 @@
       </c>
       <c r="B2185" s="1" t="inlineStr">
         <is>
-          <t>[fuˈma.sɐ] 抽烟&lt;名&gt;</t>
+          <t>[fuˈma.sɐ] 烟；烟雾&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2185" s="1" t="inlineStr">
@@ -70177,7 +70333,7 @@
       </c>
       <c r="D2185" s="1" t="inlineStr">
         <is>
-          <t>抽烟</t>
+          <t>烟；烟雾</t>
         </is>
       </c>
       <c r="E2185" s="1" t="inlineStr">
@@ -70295,17 +70451,17 @@
       </c>
       <c r="B2189" s="1" t="inlineStr">
         <is>
-          <t>[su.ˈbi.ɾãʊ̃] 玫瑰&lt;动&gt;</t>
+          <t>[su.ˈbi.ɾãʊ̃] 上升；登上；爬上&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2189" s="1" t="inlineStr">
         <is>
-          <t>su.ˈbi.ɾãʊ̃</t>
+          <t>/su.ˈbi.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2189" s="1" t="inlineStr">
         <is>
-          <t>玫瑰</t>
+          <t>上升；登上；爬上</t>
         </is>
       </c>
       <c r="E2189" s="1" t="inlineStr">
@@ -70460,7 +70616,7 @@
       </c>
       <c r="C2194" s="1" t="inlineStr">
         <is>
-          <t>kõ.tɾa.ˈta.ɾãʊ̃</t>
+          <t>/kõ.tɾa.ˈta.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2194" s="1" t="inlineStr">
@@ -70972,7 +71128,7 @@
       </c>
       <c r="C2210" s="1" t="inlineStr">
         <is>
-          <t>ĩ.dẽ.ni.za.ˈsãʊ̃</t>
+          <t>/ĩ.dẽ.ni.za.ˈsãʊ̃/</t>
         </is>
       </c>
       <c r="D2210" s="1" t="inlineStr">
@@ -71031,7 +71187,7 @@
       </c>
       <c r="B2212" s="1" t="inlineStr">
         <is>
-          <t>[ɐ̃.ɡa.ɾiˈa(ʁ)] 提高&lt;动&gt;</t>
+          <t>[ɐ̃.ɡa.ɾiˈa(ʁ)] 筹集；募集；争取&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2212" s="1" t="inlineStr">
@@ -71041,7 +71197,7 @@
       </c>
       <c r="D2212" s="1" t="inlineStr">
         <is>
-          <t>提高</t>
+          <t>筹集；募集；争取</t>
         </is>
       </c>
       <c r="E2212" s="1" t="inlineStr">
@@ -71228,7 +71384,7 @@
       </c>
       <c r="C2218" s="1" t="inlineStr">
         <is>
-          <t>de.mo.ˈɾa.ɾãʊ̃</t>
+          <t>/de.mo.ˈɾa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2218" s="1" t="inlineStr">
@@ -71356,7 +71512,7 @@
       </c>
       <c r="C2222" s="1" t="inlineStr">
         <is>
-          <t>to.ˈka.ɾãʊ̃</t>
+          <t>/to.ˈka.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2222" s="1" t="inlineStr">
@@ -71484,7 +71640,7 @@
       </c>
       <c r="C2226" s="1" t="inlineStr">
         <is>
-          <t>kõˈtɾak.tu</t>
+          <t>/kõˈtɾak.tu/</t>
         </is>
       </c>
       <c r="D2226" s="1" t="inlineStr">
@@ -71772,7 +71928,7 @@
       </c>
       <c r="C2235" s="1" t="inlineStr">
         <is>
-          <t>ax.ki.te.ˈtu.ɾə</t>
+          <t>/ax.ki.te.ˈtu.ɾə/</t>
         </is>
       </c>
       <c r="D2235" s="1" t="inlineStr">
@@ -71932,7 +72088,7 @@
       </c>
       <c r="C2240" s="1" t="inlineStr">
         <is>
-          <t>saw.ˈva.ɾãʊ̃</t>
+          <t>/saw.ˈva.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2240" s="1" t="inlineStr">
@@ -72407,7 +72563,7 @@
       </c>
       <c r="B2255" s="1" t="inlineStr">
         <is>
-          <t>[bɐ̃ˈka.dɐ] 长凳&lt;名&gt;</t>
+          <t>[/bɐ̃ˈka.dɐ/] 工作台；柜台；操作台&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2255" s="1" t="inlineStr">
@@ -72417,7 +72573,7 @@
       </c>
       <c r="D2255" s="1" t="inlineStr">
         <is>
-          <t>长凳</t>
+          <t>工作台；柜台；操作台&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2255" s="1" t="inlineStr">
@@ -72476,7 +72632,7 @@
       </c>
       <c r="C2257" s="1" t="inlineStr">
         <is>
-          <t>a.tu.a.li.ˈzax</t>
+          <t>/a.tu.a.li.ˈzax/</t>
         </is>
       </c>
       <c r="D2257" s="1" t="inlineStr">
@@ -72599,7 +72755,7 @@
       </c>
       <c r="B2261" s="1" t="inlineStr">
         <is>
-          <t>[des.tɾu.iˈdoʁ] 驱逐舰&lt;名&gt;</t>
+          <t>[/des.tɾu.iˈdoʁ/] 破坏者；毁灭性的&lt;名/形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2261" s="1" t="inlineStr">
@@ -72609,7 +72765,7 @@
       </c>
       <c r="D2261" s="1" t="inlineStr">
         <is>
-          <t>驱逐舰</t>
+          <t>破坏者；毁灭性的&lt;名/形&gt;</t>
         </is>
       </c>
       <c r="E2261" s="1" t="inlineStr">
@@ -73148,7 +73304,7 @@
       </c>
       <c r="C2278" s="1" t="inlineStr">
         <is>
-          <t>ˌwajˈfaj</t>
+          <t>/ˌwajˈfaj/</t>
         </is>
       </c>
       <c r="D2278" s="1" t="inlineStr">
@@ -73623,7 +73779,7 @@
       </c>
       <c r="B2293" s="1" t="inlineStr">
         <is>
-          <t>[ˌaʁ.dwaˈmẽ.t͡ʃi] 硬&lt;副&gt;</t>
+          <t>[ˌaʁ.dwaˈmẽ.t͡ʃi] 艰苦地；费力地&lt;副&gt;</t>
         </is>
       </c>
       <c r="C2293" s="1" t="inlineStr">
@@ -73633,7 +73789,7 @@
       </c>
       <c r="D2293" s="1" t="inlineStr">
         <is>
-          <t>硬</t>
+          <t>艰苦地；费力地</t>
         </is>
       </c>
       <c r="E2293" s="1" t="inlineStr">
@@ -73722,7 +73878,11 @@
           <t>棒球&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2296" s="1" t="inlineStr"/>
+      <c r="C2296" s="1" t="inlineStr">
+        <is>
+          <t>/ˈbeɪs.bɔːl/</t>
+        </is>
+      </c>
       <c r="D2296" s="1" t="inlineStr">
         <is>
           <t>棒球</t>
@@ -73747,7 +73907,7 @@
       </c>
       <c r="B2297" s="1" t="inlineStr">
         <is>
-          <t>[ˈpi.sɐ] 公鸡&lt;名&gt;</t>
+          <t>[/ˈpi.sɐ/] （马德拉群岛旧制）液体容量单位&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2297" s="1" t="inlineStr">
@@ -73757,7 +73917,7 @@
       </c>
       <c r="D2297" s="1" t="inlineStr">
         <is>
-          <t>公鸡</t>
+          <t>（马德拉群岛旧制）液体容量单位</t>
         </is>
       </c>
       <c r="E2297" s="1" t="inlineStr">
@@ -74168,7 +74328,7 @@
       </c>
       <c r="C2310" s="1" t="inlineStr">
         <is>
-          <t>ˈlĩ.gwə</t>
+          <t>/ˈlĩ.gwə/</t>
         </is>
       </c>
       <c r="D2310" s="1" t="inlineStr">
@@ -74387,7 +74547,7 @@
       </c>
       <c r="B2317" s="1" t="inlineStr">
         <is>
-          <t>[ʁeˈʒẽ.t͡ʃi] 导体&lt;名&gt;</t>
+          <t>[ʁeˈʒẽ.t͡ʃi] 指挥；摄政者&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2317" s="1" t="inlineStr">
@@ -74397,7 +74557,7 @@
       </c>
       <c r="D2317" s="1" t="inlineStr">
         <is>
-          <t>导体</t>
+          <t>指挥；摄政者</t>
         </is>
       </c>
       <c r="E2317" s="1" t="inlineStr">
@@ -74419,7 +74579,7 @@
       </c>
       <c r="B2318" s="1" t="inlineStr">
         <is>
-          <t>[o(w)ˈvĩ.t͡ʃi] 听众&lt;名&gt;</t>
+          <t>[/o(w)ˈvĩ.t͡ʃi/] 听者&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2318" s="1" t="inlineStr">
@@ -74429,7 +74589,7 @@
       </c>
       <c r="D2318" s="1" t="inlineStr">
         <is>
-          <t>听众</t>
+          <t>听者&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2318" s="1" t="inlineStr">
@@ -74611,7 +74771,7 @@
       </c>
       <c r="B2324" s="1" t="inlineStr">
         <is>
-          <t>[ˈte.zu] 欲火中烧&lt;名&gt;</t>
+          <t>[/ˈte.zu/] 绷紧的；拉紧的&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2324" s="1" t="inlineStr">
@@ -74621,7 +74781,7 @@
       </c>
       <c r="D2324" s="1" t="inlineStr">
         <is>
-          <t>欲火中烧</t>
+          <t>绷紧的；拉紧的</t>
         </is>
       </c>
       <c r="E2324" s="1" t="inlineStr">
@@ -74643,7 +74803,7 @@
       </c>
       <c r="B2325" s="1" t="inlineStr">
         <is>
-          <t>[bɾõ.zeˈa.du] 晒黑&lt;名&gt;</t>
+          <t>[/bɾõ.zeˈa.du/] 晒黑的&lt;形&gt;；晒黑的皮肤&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2325" s="1" t="inlineStr">
@@ -74653,7 +74813,7 @@
       </c>
       <c r="D2325" s="1" t="inlineStr">
         <is>
-          <t>晒黑</t>
+          <t>晒黑的&lt;形&gt;；晒黑的皮肤&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2325" s="1" t="inlineStr">
@@ -74803,7 +74963,7 @@
       </c>
       <c r="B2330" s="1" t="inlineStr">
         <is>
-          <t>[stɾɛˈsa.du] 强调&lt;形&gt;</t>
+          <t>[stɾɛˈsa.du] 紧张的；有压力的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C2330" s="1" t="inlineStr">
@@ -74813,7 +74973,7 @@
       </c>
       <c r="D2330" s="1" t="inlineStr">
         <is>
-          <t>强调</t>
+          <t>紧张的；有压力的</t>
         </is>
       </c>
       <c r="E2330" s="1" t="inlineStr">
@@ -74840,7 +75000,7 @@
       </c>
       <c r="C2331" s="1" t="inlineStr">
         <is>
-          <t>o.ˈku.pə</t>
+          <t>/o.ˈku.pə/</t>
         </is>
       </c>
       <c r="D2331" s="1" t="inlineStr">
@@ -75123,7 +75283,7 @@
       </c>
       <c r="B2340" s="1" t="inlineStr">
         <is>
-          <t>[ẽ.se.naˈsɐ̃w̃] 分期&lt;名&gt;</t>
+          <t>[ẽ.se.naˈsɐ̃w̃] 演出；上演；编排&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2340" s="1" t="inlineStr">
@@ -75133,7 +75293,7 @@
       </c>
       <c r="D2340" s="1" t="inlineStr">
         <is>
-          <t>分期</t>
+          <t>演出；上演；编排</t>
         </is>
       </c>
       <c r="E2340" s="1" t="inlineStr">
@@ -75187,7 +75347,7 @@
       </c>
       <c r="B2342" s="1" t="inlineStr">
         <is>
-          <t>[ˈkɾu] 原始的&lt;形&gt;</t>
+          <t>[/ˈkɾu/] 生的；未煮熟的&lt;形&gt;&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C2342" s="1" t="inlineStr">
@@ -75197,7 +75357,7 @@
       </c>
       <c r="D2342" s="1" t="inlineStr">
         <is>
-          <t>原始的</t>
+          <t>生的；未煮熟的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E2342" s="1" t="inlineStr">
@@ -75443,7 +75603,7 @@
       </c>
       <c r="B2350" s="1" t="inlineStr">
         <is>
-          <t>[isˈta.t͡ʃi.kɐ] 静态的&lt;名&gt;</t>
+          <t>[/isˈta.t͡ʃi.kɐ/] 静力学&lt;名&gt;；静态&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2350" s="1" t="inlineStr">
@@ -75453,7 +75613,7 @@
       </c>
       <c r="D2350" s="1" t="inlineStr">
         <is>
-          <t>静态的</t>
+          <t>静力学&lt;名&gt;；静态&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2350" s="1" t="inlineStr">
@@ -75608,7 +75768,7 @@
       </c>
       <c r="C2355" s="1" t="inlineStr">
         <is>
-          <t>pɾo.ku.ˈɾa.ɾãʊ̃</t>
+          <t>/pɾo.ku.ˈɾa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2355" s="1" t="inlineStr">
@@ -75704,7 +75864,7 @@
       </c>
       <c r="C2358" s="1" t="inlineStr">
         <is>
-          <t>pɾo.me.ˈte.ɾãʊ̃</t>
+          <t>/pɾo.me.ˈte.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2358" s="1" t="inlineStr">
@@ -75923,7 +76083,7 @@
       </c>
       <c r="B2365" s="1" t="inlineStr">
         <is>
-          <t>[peˈnaw] 罪犯&lt;名&gt;</t>
+          <t>[peˈnaw] 刑罚的；刑法的&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2365" s="1" t="inlineStr">
@@ -75933,7 +76093,7 @@
       </c>
       <c r="D2365" s="1" t="inlineStr">
         <is>
-          <t>罪犯</t>
+          <t>刑罚的；刑法的</t>
         </is>
       </c>
       <c r="E2365" s="1" t="inlineStr">
@@ -76019,7 +76179,7 @@
       </c>
       <c r="B2368" s="1" t="inlineStr">
         <is>
-          <t>[koˈsa(ʁ)] 从头开始&lt;动&gt;</t>
+          <t>[koˈsa(ʁ)] 抓；挠；发痒&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2368" s="1" t="inlineStr">
@@ -76029,7 +76189,7 @@
       </c>
       <c r="D2368" s="1" t="inlineStr">
         <is>
-          <t>从头开始</t>
+          <t>抓；挠；发痒</t>
         </is>
       </c>
       <c r="E2368" s="1" t="inlineStr">
@@ -76051,7 +76211,7 @@
       </c>
       <c r="B2369" s="1" t="inlineStr">
         <is>
-          <t>[maˈɾĩ.ɲu] 海洋&lt;形&gt;</t>
+          <t>[maˈɾĩ.ɲu] 海的；海洋的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C2369" s="1" t="inlineStr">
@@ -76061,7 +76221,7 @@
       </c>
       <c r="D2369" s="1" t="inlineStr">
         <is>
-          <t>海洋</t>
+          <t>海的；海洋的</t>
         </is>
       </c>
       <c r="E2369" s="1" t="inlineStr">
@@ -76376,7 +76536,7 @@
       </c>
       <c r="C2379" s="1" t="inlineStr">
         <is>
-          <t>tɾa.ˈtox</t>
+          <t>/tɾa.ˈtox/</t>
         </is>
       </c>
       <c r="D2379" s="1" t="inlineStr">
@@ -76595,7 +76755,7 @@
       </c>
       <c r="B2386" s="1" t="inlineStr">
         <is>
-          <t>[po.li.t͡ʃiˈka(ʁ)] 政治的&lt;动&gt;</t>
+          <t>[po.li.t͡ʃiˈka(ʁ)] 从事政治；谈论政治&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2386" s="1" t="inlineStr">
@@ -76605,7 +76765,7 @@
       </c>
       <c r="D2386" s="1" t="inlineStr">
         <is>
-          <t>政治的</t>
+          <t>从事政治；谈论政治</t>
         </is>
       </c>
       <c r="E2386" s="1" t="inlineStr">
@@ -76920,7 +77080,7 @@
       </c>
       <c r="C2396" s="1" t="inlineStr">
         <is>
-          <t>ˈpɔ.ɾẽỹ</t>
+          <t>/ˈpɔ.ɾẽỹ/</t>
         </is>
       </c>
       <c r="D2396" s="1" t="inlineStr">
@@ -76947,7 +77107,7 @@
       </c>
       <c r="B2397" s="1" t="inlineStr">
         <is>
-          <t>[a.bɐ̃.doˈna.ɾɐ̃w̃] 被遗弃的&lt;动&gt;</t>
+          <t>[a.bɐ̃.doˈna.ɾɐ̃w̃] 抛弃；遗弃；放弃&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2397" s="1" t="inlineStr">
@@ -76957,7 +77117,7 @@
       </c>
       <c r="D2397" s="1" t="inlineStr">
         <is>
-          <t>被遗弃的</t>
+          <t>抛弃；遗弃；放弃</t>
         </is>
       </c>
       <c r="E2397" s="1" t="inlineStr">
@@ -77048,7 +77208,7 @@
       </c>
       <c r="C2400" s="1" t="inlineStr">
         <is>
-          <t>e.fe.tʃi.va.ˈmẽ.tʃɪ</t>
+          <t>/e.fe.tʃi.va.ˈmẽ.tʃɪ/</t>
         </is>
       </c>
       <c r="D2400" s="1" t="inlineStr">
@@ -77107,7 +77267,7 @@
       </c>
       <c r="B2402" s="1" t="inlineStr">
         <is>
-          <t>[ĩ.ka.pa.siˈda.d͡ʒi] 残疾&lt;名&gt;</t>
+          <t>[/ĩ.ka.pa.siˈda.d͡ʒi/] 无能力；无能&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2402" s="1" t="inlineStr">
@@ -77117,7 +77277,7 @@
       </c>
       <c r="D2402" s="1" t="inlineStr">
         <is>
-          <t>残疾</t>
+          <t>无能力；无能&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2402" s="1" t="inlineStr">
@@ -77144,7 +77304,7 @@
       </c>
       <c r="C2403" s="1" t="inlineStr">
         <is>
-          <t>fa.ˈtu.ɾə</t>
+          <t>/fa.ˈtu.ɾə/</t>
         </is>
       </c>
       <c r="D2403" s="1" t="inlineStr">
@@ -77208,7 +77368,7 @@
       </c>
       <c r="C2405" s="1" t="inlineStr">
         <is>
-          <t>ˈax.tʃi.kʊ</t>
+          <t>/ˈax.tʃi.kʊ/</t>
         </is>
       </c>
       <c r="D2405" s="1" t="inlineStr">
@@ -77619,7 +77779,7 @@
       </c>
       <c r="B2418" s="1" t="inlineStr">
         <is>
-          <t>[is.peˈta(ʁ)] 刺拳&lt;动&gt;</t>
+          <t>[is.peˈta(ʁ)] 刺穿；扎；叉住&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2418" s="1" t="inlineStr">
@@ -77629,7 +77789,7 @@
       </c>
       <c r="D2418" s="1" t="inlineStr">
         <is>
-          <t>刺拳</t>
+          <t>刺穿；扎；叉住</t>
         </is>
       </c>
       <c r="E2418" s="1" t="inlineStr">
@@ -77939,7 +78099,7 @@
       </c>
       <c r="B2428" s="1" t="inlineStr">
         <is>
-          <t>[veˈlɔ.ɾju] 醒来&lt;名&gt;</t>
+          <t>[veˈlɔ.ɾju] 守灵；灵堂；守灵仪式&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2428" s="1" t="inlineStr">
@@ -77949,7 +78109,7 @@
       </c>
       <c r="D2428" s="1" t="inlineStr">
         <is>
-          <t>醒来</t>
+          <t>守灵；灵堂；守灵仪式</t>
         </is>
       </c>
       <c r="E2428" s="1" t="inlineStr">
@@ -78163,7 +78323,7 @@
       </c>
       <c r="B2435" s="1" t="inlineStr">
         <is>
-          <t>[ˈpi.zɐ] 跺脚&lt;名&gt;</t>
+          <t>[/ˈpi.zɐ/] 踩踏；压榨&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2435" s="1" t="inlineStr">
@@ -78173,7 +78333,7 @@
       </c>
       <c r="D2435" s="1" t="inlineStr">
         <is>
-          <t>跺脚</t>
+          <t>踩踏；压榨&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2435" s="1" t="inlineStr">
@@ -78195,7 +78355,7 @@
       </c>
       <c r="B2436" s="1" t="inlineStr">
         <is>
-          <t>[vi.aˈsɐ̃w̃] 路&lt;名&gt;</t>
+          <t>[vi.aˈsɐ̃w̃] 运输；交通；运输公司&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2436" s="1" t="inlineStr">
@@ -78205,7 +78365,7 @@
       </c>
       <c r="D2436" s="1" t="inlineStr">
         <is>
-          <t>路</t>
+          <t>运输；交通；运输公司</t>
         </is>
       </c>
       <c r="E2436" s="1" t="inlineStr">
@@ -78227,7 +78387,7 @@
       </c>
       <c r="B2437" s="1" t="inlineStr">
         <is>
-          <t>[koˈzi.du] 煮熟的&lt;名&gt;</t>
+          <t>[/koˈzi.du/] 炖菜&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2437" s="1" t="inlineStr">
@@ -78237,7 +78397,7 @@
       </c>
       <c r="D2437" s="1" t="inlineStr">
         <is>
-          <t>煮熟的</t>
+          <t>炖菜&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2437" s="1" t="inlineStr">
@@ -78291,7 +78451,7 @@
       </c>
       <c r="B2439" s="1" t="inlineStr">
         <is>
-          <t>[bõ.baʁ.d͡ʒiˈa(ʁ)] 炸弹&lt;动&gt;</t>
+          <t>[bõ.baʁ.d͡ʒiˈa(ʁ)] 轰炸；炮击&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2439" s="1" t="inlineStr">
@@ -78301,7 +78461,7 @@
       </c>
       <c r="D2439" s="1" t="inlineStr">
         <is>
-          <t>炸弹</t>
+          <t>轰炸；炮击</t>
         </is>
       </c>
       <c r="E2439" s="1" t="inlineStr">
@@ -78387,7 +78547,7 @@
       </c>
       <c r="B2442" s="1" t="inlineStr">
         <is>
-          <t>[a.baˈla.dɐ] 动摇&lt;名&gt;</t>
+          <t>[/a.baˈla.dɐ/] 动摇；惊慌&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2442" s="1" t="inlineStr">
@@ -78397,7 +78557,7 @@
       </c>
       <c r="D2442" s="1" t="inlineStr">
         <is>
-          <t>动摇</t>
+          <t>动摇；惊慌&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2442" s="1" t="inlineStr">
@@ -78419,7 +78579,7 @@
       </c>
       <c r="B2443" s="1" t="inlineStr">
         <is>
-          <t>[be.ne.fi.siˈa(ʁ)] 好处&lt;动&gt;</t>
+          <t>[be.ne.fi.siˈa(ʁ)] 使受益；有益于；受益&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2443" s="1" t="inlineStr">
@@ -78429,7 +78589,7 @@
       </c>
       <c r="D2443" s="1" t="inlineStr">
         <is>
-          <t>好处</t>
+          <t>使受益；有益于；受益</t>
         </is>
       </c>
       <c r="E2443" s="1" t="inlineStr">
@@ -78515,7 +78675,7 @@
       </c>
       <c r="B2446" s="1" t="inlineStr">
         <is>
-          <t>[maˈnĩ.ɲu] 小兄弟&lt;名&gt;</t>
+          <t>[/maˈnĩ.ɲu/] 休耕的；荒芜的；未开垦的&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2446" s="1" t="inlineStr">
@@ -78525,7 +78685,7 @@
       </c>
       <c r="D2446" s="1" t="inlineStr">
         <is>
-          <t>小兄弟</t>
+          <t>休耕的；荒芜的；未开垦的</t>
         </is>
       </c>
       <c r="E2446" s="1" t="inlineStr">
@@ -78643,7 +78803,7 @@
       </c>
       <c r="B2450" s="1" t="inlineStr">
         <is>
-          <t>[pɾoˈd͡ʒi.ʒju] 神童&lt;名&gt;</t>
+          <t>[/pɾoˈd͡ʒi.ʒju/] 奇迹；奇才&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2450" s="1" t="inlineStr">
@@ -78653,7 +78813,7 @@
       </c>
       <c r="D2450" s="1" t="inlineStr">
         <is>
-          <t>神童</t>
+          <t>奇迹；奇才&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2450" s="1" t="inlineStr">
@@ -78744,7 +78904,7 @@
       </c>
       <c r="C2453" s="1" t="inlineStr">
         <is>
-          <t>pɾo.ʒe.ˈsãʊ̃</t>
+          <t>/pɾo.ʒe.ˈsãʊ̃/</t>
         </is>
       </c>
       <c r="D2453" s="1" t="inlineStr">
@@ -78902,7 +79062,11 @@
           <t>汉堡&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2458" s="1" t="inlineStr"/>
+      <c r="C2458" s="1" t="inlineStr">
+        <is>
+          <t>/ˈbʊʁ.ɡeʁ/</t>
+        </is>
+      </c>
       <c r="D2458" s="1" t="inlineStr">
         <is>
           <t>汉堡</t>
@@ -79503,7 +79667,7 @@
       </c>
       <c r="B2477" s="1" t="inlineStr">
         <is>
-          <t>[ĩ.foʁˈma.t͡ʃi.ku] 信息技术&lt;名&gt;</t>
+          <t>[ĩ.foʁˈma.t͡ʃi.ku] 信息技术的；计算机的；信息学&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2477" s="1" t="inlineStr">
@@ -79513,7 +79677,7 @@
       </c>
       <c r="D2477" s="1" t="inlineStr">
         <is>
-          <t>信息技术</t>
+          <t>信息技术的；计算机的；信息学</t>
         </is>
       </c>
       <c r="E2477" s="1" t="inlineStr">
@@ -79791,7 +79955,7 @@
       </c>
       <c r="B2486" s="1" t="inlineStr">
         <is>
-          <t>[ˈmɔ.kɐ] 高&lt;名&gt;</t>
+          <t>[/ˈmɔ.kɐ/] 少女；姑娘（moça 的变体）&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2486" s="1" t="inlineStr">
@@ -79801,7 +79965,7 @@
       </c>
       <c r="D2486" s="1" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>少女；姑娘（moça 的变体）&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2486" s="1" t="inlineStr">
@@ -79855,7 +80019,7 @@
       </c>
       <c r="B2488" s="1" t="inlineStr">
         <is>
-          <t>[aˈʎa.dɐ] 阿尔哈达&lt;名&gt;</t>
+          <t>[aˈʎa.dɐ] 一对耕畜；一犋牲口&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2488" s="1" t="inlineStr">
@@ -79865,7 +80029,7 @@
       </c>
       <c r="D2488" s="1" t="inlineStr">
         <is>
-          <t>阿尔哈达</t>
+          <t>一对耕畜；一犋牲口</t>
         </is>
       </c>
       <c r="E2488" s="1" t="inlineStr">
@@ -80148,7 +80312,7 @@
       </c>
       <c r="C2497" s="1" t="inlineStr">
         <is>
-          <t>e.ˈtɛ.ɾʊ</t>
+          <t>/e.ˈtɛ.ɾʊ/</t>
         </is>
       </c>
       <c r="D2497" s="1" t="inlineStr">
@@ -80271,7 +80435,7 @@
       </c>
       <c r="B2501" s="1" t="inlineStr">
         <is>
-          <t>[ko.oʁ.deˈna(ʁ)] 坐标&lt;动&gt;</t>
+          <t>[ko.oʁ.deˈna(ʁ)] 协调；配合&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2501" s="1" t="inlineStr">
@@ -80281,7 +80445,7 @@
       </c>
       <c r="D2501" s="1" t="inlineStr">
         <is>
-          <t>坐标</t>
+          <t>协调；配合</t>
         </is>
       </c>
       <c r="E2501" s="1" t="inlineStr">
@@ -80335,7 +80499,7 @@
       </c>
       <c r="B2503" s="1" t="inlineStr">
         <is>
-          <t>[ɐ̃ˈsej.u] 我长&lt;名&gt;</t>
+          <t>[ɐ̃ˈsej.u] 渴望；热望；焦虑&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2503" s="1" t="inlineStr">
@@ -80345,7 +80509,7 @@
       </c>
       <c r="D2503" s="1" t="inlineStr">
         <is>
-          <t>我长</t>
+          <t>渴望；热望；焦虑</t>
         </is>
       </c>
       <c r="E2503" s="1" t="inlineStr">
@@ -80399,7 +80563,7 @@
       </c>
       <c r="B2505" s="1" t="inlineStr">
         <is>
-          <t>[aˈɡɾa.du] 请&lt;名&gt;</t>
+          <t>[aˈɡɾa.du] 满意；高兴；好感&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2505" s="1" t="inlineStr">
@@ -80409,7 +80573,7 @@
       </c>
       <c r="D2505" s="1" t="inlineStr">
         <is>
-          <t>请</t>
+          <t>满意；高兴；好感</t>
         </is>
       </c>
       <c r="E2505" s="1" t="inlineStr">
@@ -80468,7 +80632,7 @@
       </c>
       <c r="C2507" s="1" t="inlineStr">
         <is>
-          <t>tɾa.ˈta.ɾãʊ̃</t>
+          <t>/tɾa.ˈta.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2507" s="1" t="inlineStr">
@@ -80719,7 +80883,7 @@
       </c>
       <c r="B2515" s="1" t="inlineStr">
         <is>
-          <t>[ʁaˈla(ʁ)] 炉排&lt;动&gt;</t>
+          <t>[ʁaˈla(ʁ)] 擦碎；磨碎&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2515" s="1" t="inlineStr">
@@ -80729,7 +80893,7 @@
       </c>
       <c r="D2515" s="1" t="inlineStr">
         <is>
-          <t>炉排</t>
+          <t>擦碎；磨碎</t>
         </is>
       </c>
       <c r="E2515" s="1" t="inlineStr">
@@ -80911,7 +81075,7 @@
       </c>
       <c r="B2521" s="1" t="inlineStr">
         <is>
-          <t>[fũ.daˈmẽ.tu] 基金会&lt;名&gt;</t>
+          <t>[fũ.daˈmẽ.tu] 基础；根据；理由&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2521" s="1" t="inlineStr">
@@ -80921,7 +81085,7 @@
       </c>
       <c r="D2521" s="1" t="inlineStr">
         <is>
-          <t>基金会</t>
+          <t>基础；根据；理由</t>
         </is>
       </c>
       <c r="E2521" s="1" t="inlineStr">
@@ -81106,7 +81270,11 @@
           <t>自助餐&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2527" s="1" t="inlineStr"/>
+      <c r="C2527" s="1" t="inlineStr">
+        <is>
+          <t>/bu.ˈfɛ/</t>
+        </is>
+      </c>
       <c r="D2527" s="1" t="inlineStr">
         <is>
           <t>自助餐</t>
@@ -81163,17 +81331,17 @@
       </c>
       <c r="B2529" s="1" t="inlineStr">
         <is>
-          <t>[li.ˈgã.dʊ] 呼叫&lt;名&gt;</t>
+          <t>[li.ˈgã.dʊ] 连接（ligar 的动名词形式）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2529" s="1" t="inlineStr">
         <is>
-          <t>li.ˈgã.dʊ</t>
+          <t>/li.ˈgã.dʊ/</t>
         </is>
       </c>
       <c r="D2529" s="1" t="inlineStr">
         <is>
-          <t>呼叫</t>
+          <t>连接（ligar 的动名词形式）</t>
         </is>
       </c>
       <c r="E2529" s="1" t="inlineStr">
@@ -81262,7 +81430,11 @@
           <t>议员&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2532" s="1" t="inlineStr"/>
+      <c r="C2532" s="1" t="inlineStr">
+        <is>
+          <t>/mp/</t>
+        </is>
+      </c>
       <c r="D2532" s="1" t="inlineStr">
         <is>
           <t>议员</t>
@@ -81287,7 +81459,7 @@
       </c>
       <c r="B2533" s="1" t="inlineStr">
         <is>
-          <t>[kõ.d͡ʒiˈze(ʁ)] 比赛&lt;动&gt;</t>
+          <t>[kõ.d͡ʒiˈze(ʁ)] 相称；适合；相配&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2533" s="1" t="inlineStr">
@@ -81297,7 +81469,7 @@
       </c>
       <c r="D2533" s="1" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>相称；适合；相配</t>
         </is>
       </c>
       <c r="E2533" s="1" t="inlineStr">
@@ -81415,7 +81587,7 @@
       </c>
       <c r="B2537" s="1" t="inlineStr">
         <is>
-          <t>[ĩ.tɾo.meˈte(ʁ)] 内测仪&lt;动&gt;</t>
+          <t>[ĩ.tɾo.meˈte(ʁ)] 干涉；干预&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2537" s="1" t="inlineStr">
@@ -81425,7 +81597,7 @@
       </c>
       <c r="D2537" s="1" t="inlineStr">
         <is>
-          <t>内测仪</t>
+          <t>干涉；干预</t>
         </is>
       </c>
       <c r="E2537" s="1" t="inlineStr">
@@ -81447,7 +81619,7 @@
       </c>
       <c r="B2538" s="1" t="inlineStr">
         <is>
-          <t>[is.tẽˈde(ʁ)] 埃斯坦德&lt;动&gt;</t>
+          <t>[is.tẽˈde(ʁ)] 伸展；延伸；铺开&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2538" s="1" t="inlineStr">
@@ -81457,7 +81629,7 @@
       </c>
       <c r="D2538" s="1" t="inlineStr">
         <is>
-          <t>埃斯坦德</t>
+          <t>伸展；延伸；铺开</t>
         </is>
       </c>
       <c r="E2538" s="1" t="inlineStr">
@@ -81671,7 +81843,7 @@
       </c>
       <c r="B2545" s="1" t="inlineStr">
         <is>
-          <t>[a.d͡ʒi.vo.kaˈsi.ɐ] 倡导者&lt;名&gt;</t>
+          <t>[a.d͡ʒi.vo.kaˈsi.ɐ] 律师职业；律师界&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2545" s="1" t="inlineStr">
@@ -81681,7 +81853,7 @@
       </c>
       <c r="D2545" s="1" t="inlineStr">
         <is>
-          <t>倡导者</t>
+          <t>律师职业；律师界</t>
         </is>
       </c>
       <c r="E2545" s="1" t="inlineStr">
@@ -81735,7 +81907,7 @@
       </c>
       <c r="B2547" s="1" t="inlineStr">
         <is>
-          <t>[foʁ.ma.liˈda.d͡ʒi] 福尔马利达&lt;名&gt;</t>
+          <t>[foʁ.ma.liˈda.d͡ʒi] 形式；手续；礼节&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2547" s="1" t="inlineStr">
@@ -81745,7 +81917,7 @@
       </c>
       <c r="D2547" s="1" t="inlineStr">
         <is>
-          <t>福尔马利达</t>
+          <t>形式；手续；礼节</t>
         </is>
       </c>
       <c r="E2547" s="1" t="inlineStr">
@@ -81767,7 +81939,7 @@
       </c>
       <c r="B2548" s="1" t="inlineStr">
         <is>
-          <t>[ma.ni.fesˈtɐ̃.t͡ʃi] 宣言&lt;名&gt;</t>
+          <t>[ma.ni.fesˈtɐ̃.t͡ʃi] 示威者；游行示威者&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2548" s="1" t="inlineStr">
@@ -81777,7 +81949,7 @@
       </c>
       <c r="D2548" s="1" t="inlineStr">
         <is>
-          <t>宣言</t>
+          <t>示威者；游行示威者</t>
         </is>
       </c>
       <c r="E2548" s="1" t="inlineStr">
@@ -82279,7 +82451,7 @@
       </c>
       <c r="B2564" s="1" t="inlineStr">
         <is>
-          <t>[paˈʎe(j).ɾu] 帕莱罗&lt;名&gt;</t>
+          <t>[paˈʎe(j).ɾu] 干草堆；干草棚&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2564" s="1" t="inlineStr">
@@ -82289,7 +82461,7 @@
       </c>
       <c r="D2564" s="1" t="inlineStr">
         <is>
-          <t>帕莱罗</t>
+          <t>干草堆；干草棚</t>
         </is>
       </c>
       <c r="E2564" s="1" t="inlineStr">
@@ -82375,7 +82547,7 @@
       </c>
       <c r="B2567" s="1" t="inlineStr">
         <is>
-          <t>[tɐ̃ˈpo(w).ku] 坦普科&lt;副&gt;</t>
+          <t>[tɐ̃ˈpo(w).ku] 也不；亦不&lt;副&gt;</t>
         </is>
       </c>
       <c r="C2567" s="1" t="inlineStr">
@@ -82385,7 +82557,7 @@
       </c>
       <c r="D2567" s="1" t="inlineStr">
         <is>
-          <t>坦普科</t>
+          <t>也不；亦不</t>
         </is>
       </c>
       <c r="E2567" s="1" t="inlineStr">
@@ -82407,7 +82579,7 @@
       </c>
       <c r="B2568" s="1" t="inlineStr">
         <is>
-          <t>[kõ.pa.ɾeˈse(ʁ)] 比较器&lt;动&gt;</t>
+          <t>[kõ.pa.ɾeˈse(ʁ)] 出席；到场&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2568" s="1" t="inlineStr">
@@ -82417,7 +82589,7 @@
       </c>
       <c r="D2568" s="1" t="inlineStr">
         <is>
-          <t>比较器</t>
+          <t>出席；到场</t>
         </is>
       </c>
       <c r="E2568" s="1" t="inlineStr">
@@ -82503,7 +82675,7 @@
       </c>
       <c r="B2571" s="1" t="inlineStr">
         <is>
-          <t>[isˈki] 滑雪&lt;名&gt;</t>
+          <t>[/isˈki/] 滑雪板；滑雪运动&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2571" s="1" t="inlineStr">
@@ -82513,7 +82685,7 @@
       </c>
       <c r="D2571" s="1" t="inlineStr">
         <is>
-          <t>滑雪</t>
+          <t>滑雪板；滑雪运动</t>
         </is>
       </c>
       <c r="E2571" s="1" t="inlineStr">
@@ -82535,7 +82707,7 @@
       </c>
       <c r="B2572" s="1" t="inlineStr">
         <is>
-          <t>[ˈne.ɡu] 尼戈&lt;名&gt;</t>
+          <t>[/ˈne.ɡu/] 否认（动词 negar 的第一人称单数现在时）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2572" s="1" t="inlineStr">
@@ -82545,7 +82717,7 @@
       </c>
       <c r="D2572" s="1" t="inlineStr">
         <is>
-          <t>尼戈</t>
+          <t>否认（动词 negar 的第一人称单数现在时）</t>
         </is>
       </c>
       <c r="E2572" s="1" t="inlineStr">
@@ -82599,7 +82771,7 @@
       </c>
       <c r="B2574" s="1" t="inlineStr">
         <is>
-          <t>[pɾe.zũˈso.zu] 普雷松索索&lt;形&gt;</t>
+          <t>[pɾe.zũˈso.zu] 傲慢的；自负的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C2574" s="1" t="inlineStr">
@@ -82609,7 +82781,7 @@
       </c>
       <c r="D2574" s="1" t="inlineStr">
         <is>
-          <t>普雷松索索</t>
+          <t>傲慢的；自负的</t>
         </is>
       </c>
       <c r="E2574" s="1" t="inlineStr">
@@ -82631,7 +82803,7 @@
       </c>
       <c r="B2575" s="1" t="inlineStr">
         <is>
-          <t>[kojˈɔ.t͡ʃi] 科伊特&lt;名&gt;</t>
+          <t>[kojˈɔ.t͡ʃi] 郊狼&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2575" s="1" t="inlineStr">
@@ -82641,7 +82813,7 @@
       </c>
       <c r="D2575" s="1" t="inlineStr">
         <is>
-          <t>科伊特</t>
+          <t>郊狼</t>
         </is>
       </c>
       <c r="E2575" s="1" t="inlineStr">
@@ -82695,7 +82867,7 @@
       </c>
       <c r="B2577" s="1" t="inlineStr">
         <is>
-          <t>[ˈpɾɛs.tu] 急板&lt;形&gt;</t>
+          <t>[/ˈpɾɛs.tu/] 敏捷的；迅速的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C2577" s="1" t="inlineStr">
@@ -82705,7 +82877,7 @@
       </c>
       <c r="D2577" s="1" t="inlineStr">
         <is>
-          <t>急板</t>
+          <t>敏捷的；迅速的</t>
         </is>
       </c>
       <c r="E2577" s="1" t="inlineStr">
@@ -82791,7 +82963,7 @@
       </c>
       <c r="B2580" s="1" t="inlineStr">
         <is>
-          <t>[iˈdẽ.t͡ʃi.ku] 身份&lt;形&gt;</t>
+          <t>[iˈdẽ.t͡ʃi.ku] 相同的；完全一样的；同一的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C2580" s="1" t="inlineStr">
@@ -82801,7 +82973,7 @@
       </c>
       <c r="D2580" s="1" t="inlineStr">
         <is>
-          <t>身份</t>
+          <t>相同的；完全一样的；同一的</t>
         </is>
       </c>
       <c r="E2580" s="1" t="inlineStr">
@@ -82823,7 +82995,7 @@
       </c>
       <c r="B2581" s="1" t="inlineStr">
         <is>
-          <t>[ˈfũ.ne.bɾi] 富内布雷&lt;形&gt;</t>
+          <t>[ˈfũ.ne.bɾi] 葬礼的；悲哀的；阴森的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C2581" s="1" t="inlineStr">
@@ -82833,7 +83005,7 @@
       </c>
       <c r="D2581" s="1" t="inlineStr">
         <is>
-          <t>富内布雷</t>
+          <t>葬礼的；悲哀的；阴森的</t>
         </is>
       </c>
       <c r="E2581" s="1" t="inlineStr">
@@ -83052,7 +83224,7 @@
       </c>
       <c r="C2588" s="1" t="inlineStr">
         <is>
-          <t>ĩs.pe.si.o.ˈnax</t>
+          <t>/ĩs.pe.si.o.ˈnax/</t>
         </is>
       </c>
       <c r="D2588" s="1" t="inlineStr">
@@ -83082,7 +83254,11 @@
           <t>公元前&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C2589" s="1" t="inlineStr"/>
+      <c r="C2589" s="1" t="inlineStr">
+        <is>
+          <t>/a ˈse/</t>
+        </is>
+      </c>
       <c r="D2589" s="1" t="inlineStr">
         <is>
           <t>公元前</t>
@@ -83112,7 +83288,7 @@
       </c>
       <c r="C2590" s="1" t="inlineStr">
         <is>
-          <t>a.tʃĩ.ˈʒi.ɾãʊ̃</t>
+          <t>/a.tʃĩ.ˈʒi.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2590" s="1" t="inlineStr">
@@ -83491,7 +83667,7 @@
       </c>
       <c r="B2602" s="1" t="inlineStr">
         <is>
-          <t>[ˈbɾu.ʃu] 向导&lt;名&gt;</t>
+          <t>[ˈbɾu.ʃu] 巫师；男巫&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2602" s="1" t="inlineStr">
@@ -83501,7 +83677,7 @@
       </c>
       <c r="D2602" s="1" t="inlineStr">
         <is>
-          <t>向导</t>
+          <t>巫师；男巫</t>
         </is>
       </c>
       <c r="E2602" s="1" t="inlineStr">
@@ -84360,7 +84536,7 @@
       </c>
       <c r="C2629" s="1" t="inlineStr">
         <is>
-          <t>aw.mẽ.ˈta.ɾãʊ̃</t>
+          <t>/aw.mẽ.ˈta.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2629" s="1" t="inlineStr">
@@ -84488,7 +84664,7 @@
       </c>
       <c r="C2633" s="1" t="inlineStr">
         <is>
-          <t>xe.pa.ˈɾa.ɾãʊ̃</t>
+          <t>/xe.pa.ˈɾa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2633" s="1" t="inlineStr">
@@ -84742,7 +84918,11 @@
           <t>他&lt;代&gt;</t>
         </is>
       </c>
-      <c r="C2641" s="1" t="inlineStr"/>
+      <c r="C2641" s="1" t="inlineStr">
+        <is>
+          <t>/ˈelle/</t>
+        </is>
+      </c>
       <c r="D2641" s="1" t="inlineStr">
         <is>
           <t>他</t>
@@ -84863,7 +85043,7 @@
       </c>
       <c r="B2645" s="1" t="inlineStr">
         <is>
-          <t>[ˈzẽj̃] 禅宗&lt;名&gt;</t>
+          <t>[/ˈzẽj̃/] 禅的；宁静平和的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2645" s="1" t="inlineStr">
@@ -84873,7 +85053,7 @@
       </c>
       <c r="D2645" s="1" t="inlineStr">
         <is>
-          <t>禅宗</t>
+          <t>禅的；宁静平和的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E2645" s="1" t="inlineStr">
@@ -85151,7 +85331,7 @@
       </c>
       <c r="B2654" s="1" t="inlineStr">
         <is>
-          <t>[ɡɾaˈsĩ.ɲɐ] 可爱&lt;名&gt;</t>
+          <t>[/ɡɾaˈsĩ.ɲɐ/] 可爱的人（或物）；讨人喜欢的言行&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2654" s="1" t="inlineStr">
@@ -85161,7 +85341,7 @@
       </c>
       <c r="D2654" s="1" t="inlineStr">
         <is>
-          <t>可爱</t>
+          <t>可爱的人（或物）；讨人喜欢的言行&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2654" s="1" t="inlineStr">
@@ -85380,7 +85560,7 @@
       </c>
       <c r="C2661" s="1" t="inlineStr">
         <is>
-          <t>key.ˈma.ɾãʊ̃</t>
+          <t>/key.ˈma.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2661" s="1" t="inlineStr">
@@ -85535,7 +85715,7 @@
       </c>
       <c r="B2666" s="1" t="inlineStr">
         <is>
-          <t>[tɾaˈsa(ʁ)] 痕迹&lt;动&gt;</t>
+          <t>[tɾaˈsa(ʁ)] 画；描绘；制定；拟定&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2666" s="1" t="inlineStr">
@@ -85545,7 +85725,7 @@
       </c>
       <c r="D2666" s="1" t="inlineStr">
         <is>
-          <t>痕迹</t>
+          <t>画；描绘；制定；拟定</t>
         </is>
       </c>
       <c r="E2666" s="1" t="inlineStr">
@@ -85602,7 +85782,11 @@
           <t>王八蛋&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2668" s="1" t="inlineStr"/>
+      <c r="C2668" s="1" t="inlineStr">
+        <is>
+          <t>/ˈfi.ʎu dɐ ˈpu.tɐ/</t>
+        </is>
+      </c>
       <c r="D2668" s="1" t="inlineStr">
         <is>
           <t>王八蛋</t>
@@ -86046,7 +86230,11 @@
           <t>巨魔&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2682" s="1" t="inlineStr"/>
+      <c r="C2682" s="1" t="inlineStr">
+        <is>
+          <t>/tɾɔw/</t>
+        </is>
+      </c>
       <c r="D2682" s="1" t="inlineStr">
         <is>
           <t>巨魔</t>
@@ -86076,7 +86264,7 @@
       </c>
       <c r="C2683" s="1" t="inlineStr">
         <is>
-          <t>ĩ.ʒe.ˈtax</t>
+          <t>/ĩ.ʒe.ˈtax/</t>
         </is>
       </c>
       <c r="D2683" s="1" t="inlineStr">
@@ -86106,7 +86294,11 @@
           <t>我拒绝&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2684" s="1" t="inlineStr"/>
+      <c r="C2684" s="1" t="inlineStr">
+        <is>
+          <t>/ʁeˈku.zu/</t>
+        </is>
+      </c>
       <c r="D2684" s="1" t="inlineStr">
         <is>
           <t>我拒绝</t>
@@ -86488,7 +86680,7 @@
       </c>
       <c r="C2696" s="1" t="inlineStr">
         <is>
-          <t>kõ.fiɣ.ˈma.ɾãʊ̃</t>
+          <t>/kõ.fiɣ.ˈma.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2696" s="1" t="inlineStr">
@@ -86616,7 +86808,7 @@
       </c>
       <c r="C2700" s="1" t="inlineStr">
         <is>
-          <t>go.ˈli.əs</t>
+          <t>/go.ˈli.əs/</t>
         </is>
       </c>
       <c r="D2700" s="1" t="inlineStr">
@@ -86675,7 +86867,7 @@
       </c>
       <c r="B2702" s="1" t="inlineStr">
         <is>
-          <t>[pɾo.viˈdẽ.sjɐ] 普罗维登斯&lt;名&gt;</t>
+          <t>[pɾo.viˈdẽ.sjɐ] 措施；预防办法；天意&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2702" s="1" t="inlineStr">
@@ -86685,7 +86877,7 @@
       </c>
       <c r="D2702" s="1" t="inlineStr">
         <is>
-          <t>普罗维登斯</t>
+          <t>措施；预防办法；天意</t>
         </is>
       </c>
       <c r="E2702" s="1" t="inlineStr">
@@ -87000,7 +87192,7 @@
       </c>
       <c r="C2712" s="1" t="inlineStr">
         <is>
-          <t>kõ.du.ˈzi.dʊ</t>
+          <t>/kõ.du.ˈzi.dʊ/</t>
         </is>
       </c>
       <c r="D2712" s="1" t="inlineStr">
@@ -87251,13 +87443,17 @@
       </c>
       <c r="B2720" s="1" t="inlineStr">
         <is>
-          <t>极客&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C2720" s="1" t="inlineStr"/>
+          <t>狗狗&lt;名&gt;</t>
+        </is>
+      </c>
+      <c r="C2720" s="1" t="inlineStr">
+        <is>
+          <t>/ˈtɔ.tuʃ/</t>
+        </is>
+      </c>
       <c r="D2720" s="1" t="inlineStr">
         <is>
-          <t>极客</t>
+          <t>狗狗</t>
         </is>
       </c>
       <c r="E2720" s="1" t="inlineStr">
@@ -87828,7 +88024,7 @@
       </c>
       <c r="C2738" s="1" t="inlineStr">
         <is>
-          <t>xes.põ.ˈde.ɾãʊ̃</t>
+          <t>/xes.põ.ˈde.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2738" s="1" t="inlineStr">
@@ -87887,7 +88083,7 @@
       </c>
       <c r="B2740" s="1" t="inlineStr">
         <is>
-          <t>[piˈna(ʁ)] 针&lt;动&gt;</t>
+          <t>[piˈna(ʁ)] 交尾；交配&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2740" s="1" t="inlineStr">
@@ -87897,7 +88093,7 @@
       </c>
       <c r="D2740" s="1" t="inlineStr">
         <is>
-          <t>针</t>
+          <t>交尾；交配</t>
         </is>
       </c>
       <c r="E2740" s="1" t="inlineStr">
@@ -87951,13 +88147,17 @@
       </c>
       <c r="B2742" s="1" t="inlineStr">
         <is>
-          <t>科尔特斯&lt;形&gt;</t>
-        </is>
-      </c>
-      <c r="C2742" s="1" t="inlineStr"/>
+          <t>有礼貌的；殷勤的&lt;形&gt;</t>
+        </is>
+      </c>
+      <c r="C2742" s="1" t="inlineStr">
+        <is>
+          <t>/koʁˈtɛj̯s/</t>
+        </is>
+      </c>
       <c r="D2742" s="1" t="inlineStr">
         <is>
-          <t>科尔特斯</t>
+          <t>有礼貌的；殷勤的</t>
         </is>
       </c>
       <c r="E2742" s="1" t="inlineStr">
@@ -88107,7 +88307,7 @@
       </c>
       <c r="B2747" s="1" t="inlineStr">
         <is>
-          <t>[maˈt͡ʃi.ʎɐ] 包&lt;名&gt;</t>
+          <t>[maˈt͡ʃi.ʎɐ] 狗群；猎犬群&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2747" s="1" t="inlineStr">
@@ -88117,7 +88317,7 @@
       </c>
       <c r="D2747" s="1" t="inlineStr">
         <is>
-          <t>包</t>
+          <t>狗群；猎犬群</t>
         </is>
       </c>
       <c r="E2747" s="1" t="inlineStr">
@@ -88171,7 +88371,7 @@
       </c>
       <c r="B2749" s="1" t="inlineStr">
         <is>
-          <t>[ka.ɾaˈi.bɐ] 加勒比海&lt;名&gt;</t>
+          <t>[ka.ɾaˈi.bɐ] 加勒比人；白人&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2749" s="1" t="inlineStr">
@@ -88181,7 +88381,7 @@
       </c>
       <c r="D2749" s="1" t="inlineStr">
         <is>
-          <t>加勒比海</t>
+          <t>加勒比人；白人</t>
         </is>
       </c>
       <c r="E2749" s="1" t="inlineStr">
@@ -88395,7 +88595,7 @@
       </c>
       <c r="B2756" s="1" t="inlineStr">
         <is>
-          <t>[ɡwaʁ.niˈsɐ̃w̃] 修剪&lt;名&gt;</t>
+          <t>[ɡwaʁ.niˈsɐ̃w̃] 配菜；饰边；驻军；全体乘员&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2756" s="1" t="inlineStr">
@@ -88405,7 +88605,7 @@
       </c>
       <c r="D2756" s="1" t="inlineStr">
         <is>
-          <t>修剪</t>
+          <t>配菜；饰边；驻军；全体乘员</t>
         </is>
       </c>
       <c r="E2756" s="1" t="inlineStr">
@@ -89003,7 +89203,7 @@
       </c>
       <c r="B2775" s="1" t="inlineStr">
         <is>
-          <t>[de.li.kaˈde.zɐ] 美味佳肴&lt;名&gt;</t>
+          <t>[de.li.kaˈde.zɐ] 温柔；体贴；精致；文雅&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2775" s="1" t="inlineStr">
@@ -89013,7 +89213,7 @@
       </c>
       <c r="D2775" s="1" t="inlineStr">
         <is>
-          <t>美味佳肴</t>
+          <t>温柔；体贴；精致；文雅</t>
         </is>
       </c>
       <c r="E2775" s="1" t="inlineStr">
@@ -89067,7 +89267,7 @@
       </c>
       <c r="B2777" s="1" t="inlineStr">
         <is>
-          <t>[ʁiˈbe(j).ɾu] 布鲁克&lt;名&gt;</t>
+          <t>[ʁiˈbe(j).ɾu] 小溪；溪流&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2777" s="1" t="inlineStr">
@@ -89077,7 +89277,7 @@
       </c>
       <c r="D2777" s="1" t="inlineStr">
         <is>
-          <t>布鲁克</t>
+          <t>小溪；溪流</t>
         </is>
       </c>
       <c r="E2777" s="1" t="inlineStr">
@@ -89264,7 +89464,7 @@
       </c>
       <c r="C2783" s="1" t="inlineStr">
         <is>
-          <t>ˈlɛ.ɾãʊ̃</t>
+          <t>/ˈlɛ.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2783" s="1" t="inlineStr">
@@ -89547,13 +89747,17 @@
       </c>
       <c r="B2792" s="1" t="inlineStr">
         <is>
-          <t>卡&lt;叹&gt;</t>
-        </is>
-      </c>
-      <c r="C2792" s="1" t="inlineStr"/>
+          <t>表示笑声或嘲弄的感叹声&lt;叹&gt;</t>
+        </is>
+      </c>
+      <c r="C2792" s="1" t="inlineStr">
+        <is>
+          <t>/kˈa/</t>
+        </is>
+      </c>
       <c r="D2792" s="1" t="inlineStr">
         <is>
-          <t>卡</t>
+          <t>表示笑声或嘲弄的感叹声</t>
         </is>
       </c>
       <c r="E2792" s="1" t="inlineStr">
@@ -89575,7 +89779,7 @@
       </c>
       <c r="B2793" s="1" t="inlineStr">
         <is>
-          <t>[ˈnõ.nɐ] 第九&lt;名&gt;</t>
+          <t>[/ˈnõ.nɐ/] 第九的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2793" s="1" t="inlineStr">
@@ -89585,7 +89789,7 @@
       </c>
       <c r="D2793" s="1" t="inlineStr">
         <is>
-          <t>第九</t>
+          <t>第九的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E2793" s="1" t="inlineStr">
@@ -89639,7 +89843,7 @@
       </c>
       <c r="B2795" s="1" t="inlineStr">
         <is>
-          <t>[ma.tuˈlɐ̃w̃] 大个子&lt;名&gt;</t>
+          <t>[/ma.tuˈlɐ̃w̃/] 无赖；粗鲁的人&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2795" s="1" t="inlineStr">
@@ -89649,7 +89853,7 @@
       </c>
       <c r="D2795" s="1" t="inlineStr">
         <is>
-          <t>大个子</t>
+          <t>无赖；粗鲁的人&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2795" s="1" t="inlineStr">
@@ -90311,7 +90515,7 @@
       </c>
       <c r="B2816" s="1" t="inlineStr">
         <is>
-          <t>[ko.loˈɾi.du] 色彩缤纷&lt;名&gt;</t>
+          <t>[/ko.loˈɾi.du/] 色彩缤纷的&lt;形&gt;；彩色&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2816" s="1" t="inlineStr">
@@ -90321,7 +90525,7 @@
       </c>
       <c r="D2816" s="1" t="inlineStr">
         <is>
-          <t>色彩缤纷</t>
+          <t>色彩缤纷的&lt;形&gt;；彩色&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2816" s="1" t="inlineStr">
@@ -91431,7 +91635,7 @@
       </c>
       <c r="B2851" s="1" t="inlineStr">
         <is>
-          <t>[foˈsĩ.ɲu] 枪口&lt;名&gt;</t>
+          <t>[foˈsĩ.ɲu] （动物的）口鼻部；吻部；嘴脸（贬义）&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2851" s="1" t="inlineStr">
@@ -91441,7 +91645,7 @@
       </c>
       <c r="D2851" s="1" t="inlineStr">
         <is>
-          <t>枪口</t>
+          <t>（动物的）口鼻部；吻部；嘴脸（贬义）</t>
         </is>
       </c>
       <c r="E2851" s="1" t="inlineStr">
@@ -91719,7 +91923,7 @@
       </c>
       <c r="B2860" s="1" t="inlineStr">
         <is>
-          <t>[tɾɐ̃s.poʁˈta.du] 运输的&lt;形&gt;</t>
+          <t>[/tɾɐ̃s.poʁˈta.du/] 被运送的；运输到的（过去分词）&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C2860" s="1" t="inlineStr">
@@ -91729,7 +91933,7 @@
       </c>
       <c r="D2860" s="1" t="inlineStr">
         <is>
-          <t>运输的</t>
+          <t>被运送的；运输到的（过去分词）</t>
         </is>
       </c>
       <c r="E2860" s="1" t="inlineStr">
@@ -91815,7 +92019,7 @@
       </c>
       <c r="B2863" s="1" t="inlineStr">
         <is>
-          <t>[a.ʁe.ka.daˈsɐ̃w̃] 收藏&lt;名&gt;</t>
+          <t>[a.ʁe.ka.daˈsɐ̃w̃] 征收；募集；税收&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2863" s="1" t="inlineStr">
@@ -91825,7 +92029,7 @@
       </c>
       <c r="D2863" s="1" t="inlineStr">
         <is>
-          <t>收藏</t>
+          <t>征收；募集；税收</t>
         </is>
       </c>
       <c r="E2863" s="1" t="inlineStr">
@@ -92044,7 +92248,7 @@
       </c>
       <c r="C2870" s="1" t="inlineStr">
         <is>
-          <t>mẽ.ˈtʃi.ɾãʊ̃</t>
+          <t>/mẽ.ˈtʃi.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2870" s="1" t="inlineStr">
@@ -92103,7 +92307,7 @@
       </c>
       <c r="B2872" s="1" t="inlineStr">
         <is>
-          <t>[o.ɾaˈdoʁ] 扬声器&lt;名&gt;</t>
+          <t>[o.ɾaˈdoʁ] 演讲者；发言人；演说家&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2872" s="1" t="inlineStr">
@@ -92113,7 +92317,7 @@
       </c>
       <c r="D2872" s="1" t="inlineStr">
         <is>
-          <t>扬声器</t>
+          <t>演讲者；发言人；演说家</t>
         </is>
       </c>
       <c r="E2872" s="1" t="inlineStr">
@@ -92426,7 +92630,11 @@
           <t>孟买&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2882" s="1" t="inlineStr"/>
+      <c r="C2882" s="1" t="inlineStr">
+        <is>
+          <t>/bõ.ˈbɐ̃j/</t>
+        </is>
+      </c>
       <c r="D2882" s="1" t="inlineStr">
         <is>
           <t>孟买</t>
@@ -92552,7 +92760,7 @@
       </c>
       <c r="C2886" s="1" t="inlineStr">
         <is>
-          <t>e.ˈɾɔy.kʊ</t>
+          <t>/e.ˈɾɔy.kʊ/</t>
         </is>
       </c>
       <c r="D2886" s="1" t="inlineStr">
@@ -92840,7 +93048,7 @@
       </c>
       <c r="C2895" s="1" t="inlineStr">
         <is>
-          <t>ã.pli.ˈax</t>
+          <t>/ã.pli.ˈax/</t>
         </is>
       </c>
       <c r="D2895" s="1" t="inlineStr">
@@ -93187,7 +93395,7 @@
       </c>
       <c r="B2906" s="1" t="inlineStr">
         <is>
-          <t>[ajˈɾa(ʁ)] 空气&lt;动&gt;</t>
+          <t>[ajˈɾa(ʁ)] 激怒；使愤怒&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2906" s="1" t="inlineStr">
@@ -93197,7 +93405,7 @@
       </c>
       <c r="D2906" s="1" t="inlineStr">
         <is>
-          <t>空气</t>
+          <t>激怒；使愤怒</t>
         </is>
       </c>
       <c r="E2906" s="1" t="inlineStr">
@@ -93347,7 +93555,7 @@
       </c>
       <c r="B2911" s="1" t="inlineStr">
         <is>
-          <t>[luˈkɾa(ʁ)] 利润&lt;动&gt;</t>
+          <t>[luˈkɾa(ʁ)] 获利；盈利；赚钱&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2911" s="1" t="inlineStr">
@@ -93357,7 +93565,7 @@
       </c>
       <c r="D2911" s="1" t="inlineStr">
         <is>
-          <t>利润</t>
+          <t>获利；盈利；赚钱</t>
         </is>
       </c>
       <c r="E2911" s="1" t="inlineStr">
@@ -93379,7 +93587,7 @@
       </c>
       <c r="B2912" s="1" t="inlineStr">
         <is>
-          <t>[buˈzĩ.nɐ] 号角&lt;名&gt;</t>
+          <t>[/buˈzĩ.nɐ/] 喇叭&lt;名&gt;；汽车喇叭&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2912" s="1" t="inlineStr">
@@ -93389,7 +93597,7 @@
       </c>
       <c r="D2912" s="1" t="inlineStr">
         <is>
-          <t>号角</t>
+          <t>喇叭&lt;名&gt;；汽车喇叭&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2912" s="1" t="inlineStr">
@@ -93475,7 +93683,7 @@
       </c>
       <c r="B2915" s="1" t="inlineStr">
         <is>
-          <t>[kõ.pa.tɾiˈɔ.tɐ] 乡下人&lt;名&gt;</t>
+          <t>[kõ.pa.tɾiˈɔ.tɐ] 同胞；同国人&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2915" s="1" t="inlineStr">
@@ -93485,7 +93693,7 @@
       </c>
       <c r="D2915" s="1" t="inlineStr">
         <is>
-          <t>乡下人</t>
+          <t>同胞；同国人</t>
         </is>
       </c>
       <c r="E2915" s="1" t="inlineStr">
@@ -93571,7 +93779,7 @@
       </c>
       <c r="B2918" s="1" t="inlineStr">
         <is>
-          <t>[pas.te.laˈɾi.ɐ] 糕点&lt;名&gt;</t>
+          <t>[/pas.te.laˈɾi.ɐ/] 糕点店&lt;名&gt;；糕点&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2918" s="1" t="inlineStr">
@@ -93581,7 +93789,7 @@
       </c>
       <c r="D2918" s="1" t="inlineStr">
         <is>
-          <t>糕点</t>
+          <t>糕点店&lt;名&gt;；糕点&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2918" s="1" t="inlineStr">
@@ -93763,7 +93971,7 @@
       </c>
       <c r="B2924" s="1" t="inlineStr">
         <is>
-          <t>[ˈt͡ʃi.ku] 蒂科&lt;名&gt;</t>
+          <t>[ˈt͡ʃi.ku] 哥斯达黎加人；塞阿拉州人&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2924" s="1" t="inlineStr">
@@ -93773,7 +93981,7 @@
       </c>
       <c r="D2924" s="1" t="inlineStr">
         <is>
-          <t>蒂科</t>
+          <t>哥斯达黎加人；塞阿拉州人</t>
         </is>
       </c>
       <c r="E2924" s="1" t="inlineStr">
@@ -94440,7 +94648,7 @@
       </c>
       <c r="C2945" s="1" t="inlineStr">
         <is>
-          <t>lã.ˈsa.ɾãʊ̃</t>
+          <t>/lã.ˈsa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2945" s="1" t="inlineStr">
@@ -94627,13 +94835,17 @@
       </c>
       <c r="B2951" s="1" t="inlineStr">
         <is>
-          <t>塔玛拉&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C2951" s="1" t="inlineStr"/>
+          <t>[[tɐˈmaɾɐ]] tâmara（椰枣）&lt;名&gt;&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C2951" s="1" t="inlineStr">
+        <is>
+          <t>/taˈma.ɾɐ/</t>
+        </is>
+      </c>
       <c r="D2951" s="1" t="inlineStr">
         <is>
-          <t>塔玛拉</t>
+          <t>tâmara（椰枣）&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2951" s="1" t="inlineStr">
@@ -94850,7 +95062,11 @@
           <t>最优的&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C2958" s="1" t="inlineStr"/>
+      <c r="C2958" s="1" t="inlineStr">
+        <is>
+          <t>/ˈɔ.t͡ʃi.mu/</t>
+        </is>
+      </c>
       <c r="D2958" s="1" t="inlineStr">
         <is>
           <t>最优的</t>
@@ -95259,7 +95475,7 @@
       </c>
       <c r="B2971" s="1" t="inlineStr">
         <is>
-          <t>[ˈni] 你&lt;名&gt;</t>
+          <t>[ˈni] 也不&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2971" s="1" t="inlineStr">
@@ -95269,7 +95485,7 @@
       </c>
       <c r="D2971" s="1" t="inlineStr">
         <is>
-          <t>你</t>
+          <t>也不</t>
         </is>
       </c>
       <c r="E2971" s="1" t="inlineStr">
@@ -95584,7 +95800,7 @@
       </c>
       <c r="C2981" s="1" t="inlineStr">
         <is>
-          <t>ba.ˈloy.sʊ</t>
+          <t>/ba.ˈloy.sʊ/</t>
         </is>
       </c>
       <c r="D2981" s="1" t="inlineStr">
@@ -95648,7 +95864,7 @@
       </c>
       <c r="C2983" s="1" t="inlineStr">
         <is>
-          <t>kaw.ˈza.ɾãʊ̃</t>
+          <t>/kaw.ˈza.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2983" s="1" t="inlineStr">
@@ -95867,13 +96083,17 @@
       </c>
       <c r="B2990" s="1" t="inlineStr">
         <is>
-          <t>莫伊拉&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C2990" s="1" t="inlineStr"/>
+          <t>命运女神；摩尔女人；少女&lt;名&gt;</t>
+        </is>
+      </c>
+      <c r="C2990" s="1" t="inlineStr">
+        <is>
+          <t>/moˈiʁa/</t>
+        </is>
+      </c>
       <c r="D2990" s="1" t="inlineStr">
         <is>
-          <t>莫伊拉</t>
+          <t>命运女神；摩尔女人；少女</t>
         </is>
       </c>
       <c r="E2990" s="1" t="inlineStr">
@@ -96154,7 +96374,11 @@
           <t>安卓&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2999" s="1" t="inlineStr"/>
+      <c r="C2999" s="1" t="inlineStr">
+        <is>
+          <t>/andʁɔˈide/</t>
+        </is>
+      </c>
       <c r="D2999" s="1" t="inlineStr">
         <is>
           <t>安卓</t>
